--- a/jogos_2026-03-15.xlsx
+++ b/jogos_2026-03-15.xlsx
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,22 +1932,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Melbourne Victory FC</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Macarthur</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>4.08</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2051,22 +2051,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Melbourne Victory FC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Macarthur</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2646,22 +2646,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2884,22 +2884,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Port FC</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,22 +3360,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,22 +3836,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4907,22 +4907,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5026,22 +5026,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5264,22 +5264,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Port FC</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5978,22 +5978,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>4.48</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>6.17</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>4.48</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>6.17</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6454,22 +6454,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>NorthEast United</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Jamshedpur</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Kanchanaburi</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6767,10 +6767,10 @@
         <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA53" t="n">
         <v>0</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7005,10 +7005,10 @@
         <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z55" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA55" t="n">
         <v>0</v>
@@ -7168,22 +7168,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Kanchanaburi</t>
+          <t>NorthEast United</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Jamshedpur</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9667,22 +9667,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Balestier Khalsa</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Home United</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9786,22 +9786,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10024,22 +10024,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Balestier Khalsa</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Home United</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="M99" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N99" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="M100" t="n">
-        <v>5.97</v>
+        <v>0</v>
       </c>
       <c r="N100" t="n">
-        <v>10.3</v>
+        <v>0</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="M101" t="n">
-        <v>5.58</v>
+        <v>0</v>
       </c>
       <c r="N101" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12523,22 +12523,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="M102" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="N102" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Johor Darul Ta'zim</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13154,13 +13154,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="M107" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N107" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13273,13 +13273,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="M108" t="n">
-        <v>0</v>
+        <v>5.97</v>
       </c>
       <c r="N108" t="n">
-        <v>0</v>
+        <v>10.3</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -13356,22 +13356,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13392,13 +13392,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="M109" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="N109" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13511,13 +13511,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="M110" t="n">
-        <v>0</v>
+        <v>5.58</v>
       </c>
       <c r="N110" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Johor Darul Ta'zim</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13951,7 +13951,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -13987,13 +13987,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M114" t="n">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="N114" t="n">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -14032,10 +14032,10 @@
         <v>0</v>
       </c>
       <c r="AA114" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB114" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC114" t="n">
         <v>0</v>
@@ -14070,7 +14070,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14106,13 +14106,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="M115" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="N115" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -14151,10 +14151,10 @@
         <v>0</v>
       </c>
       <c r="AA115" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB115" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC115" t="n">
         <v>0</v>
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>1.79</v>
+        <v>2.64</v>
       </c>
       <c r="M116" t="n">
-        <v>4.06</v>
+        <v>3.38</v>
       </c>
       <c r="N116" t="n">
-        <v>4.77</v>
+        <v>2.52</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -14270,10 +14270,10 @@
         <v>0</v>
       </c>
       <c r="AA116" t="n">
-        <v>1.8</v>
+        <v>2.03</v>
       </c>
       <c r="AB116" t="n">
-        <v>1.97</v>
+        <v>1.83</v>
       </c>
       <c r="AC116" t="n">
         <v>0</v>
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14344,13 +14344,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>2.19</v>
+        <v>1.79</v>
       </c>
       <c r="M117" t="n">
-        <v>3.58</v>
+        <v>4.06</v>
       </c>
       <c r="N117" t="n">
-        <v>3.58</v>
+        <v>4.77</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -14389,10 +14389,10 @@
         <v>0</v>
       </c>
       <c r="AA117" t="n">
-        <v>1.96</v>
+        <v>1.8</v>
       </c>
       <c r="AB117" t="n">
-        <v>1.75</v>
+        <v>1.97</v>
       </c>
       <c r="AC117" t="n">
         <v>0</v>
@@ -14427,22 +14427,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Inter Kashi</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Mumbai City</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14820,13 +14820,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="M121" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="N121" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -14865,10 +14865,10 @@
         <v>0</v>
       </c>
       <c r="AA121" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB121" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC121" t="n">
         <v>0</v>
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -14939,13 +14939,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="M122" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N122" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -14984,10 +14984,10 @@
         <v>0</v>
       </c>
       <c r="AA122" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB122" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC122" t="n">
         <v>0</v>
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15058,13 +15058,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="M123" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N123" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -15103,10 +15103,10 @@
         <v>0</v>
       </c>
       <c r="AA123" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB123" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC123" t="n">
         <v>0</v>
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Inter Kashi</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Mumbai City</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15415,13 +15415,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="M126" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="N126" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -15460,10 +15460,10 @@
         <v>0</v>
       </c>
       <c r="AA126" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB126" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC126" t="n">
         <v>0</v>
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15653,13 +15653,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="M128" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="N128" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -15698,10 +15698,10 @@
         <v>0</v>
       </c>
       <c r="AA128" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB128" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC128" t="n">
         <v>0</v>
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15772,13 +15772,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M129" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="N129" t="n">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -15817,10 +15817,10 @@
         <v>0</v>
       </c>
       <c r="AA129" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB129" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC129" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16010,13 +16010,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="M131" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="N131" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -16055,10 +16055,10 @@
         <v>0</v>
       </c>
       <c r="AA131" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB131" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC131" t="n">
         <v>0</v>
@@ -16093,22 +16093,22 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16367,13 +16367,13 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M134" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="N134" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -16412,10 +16412,10 @@
         <v>0</v>
       </c>
       <c r="AA134" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB134" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC134" t="n">
         <v>0</v>
@@ -16450,7 +16450,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16724,13 +16724,13 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="M137" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N137" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="O137" t="n">
         <v>0</v>
@@ -16769,10 +16769,10 @@
         <v>0</v>
       </c>
       <c r="AA137" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB137" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC137" t="n">
         <v>0</v>
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16843,13 +16843,13 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="M138" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N138" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -16888,10 +16888,10 @@
         <v>0</v>
       </c>
       <c r="AA138" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB138" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC138" t="n">
         <v>0</v>
@@ -16926,7 +16926,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Eléctrico</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -17045,7 +17045,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17164,22 +17164,22 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -17283,22 +17283,22 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17402,7 +17402,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17521,7 +17521,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17640,22 +17640,22 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17759,7 +17759,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>AR São Martinho</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17878,7 +17878,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>Monção</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -17997,7 +17997,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -18007,12 +18007,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18235,7 +18235,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -18245,12 +18245,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Chaves II</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Mirandela</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -18364,12 +18364,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Gouveia</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -18473,7 +18473,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -18483,12 +18483,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -18592,7 +18592,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -18602,12 +18602,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -18711,7 +18711,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -18721,12 +18721,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Monção</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -18830,22 +18830,22 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>AR São Martinho</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -18949,7 +18949,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -18959,12 +18959,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Machico</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -19068,7 +19068,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -19078,12 +19078,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -19187,7 +19187,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Clube Oriental de Lisboa</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -19306,22 +19306,22 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Eléctrico</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -19425,22 +19425,22 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19544,22 +19544,22 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -19663,7 +19663,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -19673,12 +19673,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -19782,7 +19782,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -19792,12 +19792,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -19901,7 +19901,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -19911,12 +19911,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -20020,7 +20020,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -20030,12 +20030,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -20149,12 +20149,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -20258,7 +20258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -20268,12 +20268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -20387,12 +20387,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -20496,22 +20496,22 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -20615,7 +20615,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -20625,12 +20625,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -20734,7 +20734,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -20744,12 +20744,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -20853,7 +20853,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -20863,12 +20863,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Clube Oriental de Lisboa</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -20972,7 +20972,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -20982,12 +20982,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Machico</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -21091,22 +21091,22 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -21210,7 +21210,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -21220,12 +21220,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>Chaves II</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>Mirandela</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -21329,7 +21329,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -21339,12 +21339,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Lajense</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -21448,7 +21448,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -21458,12 +21458,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -21567,22 +21567,22 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -21686,7 +21686,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -21696,12 +21696,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -22043,7 +22043,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -22053,12 +22053,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -22079,13 +22079,13 @@
         </is>
       </c>
       <c r="L182" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="M182" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="N182" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="O182" t="n">
         <v>0</v>
@@ -22162,7 +22162,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -22172,12 +22172,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -22281,7 +22281,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -22291,12 +22291,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -22529,12 +22529,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -22638,7 +22638,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -22648,12 +22648,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -22674,13 +22674,13 @@
         </is>
       </c>
       <c r="L187" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="M187" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="N187" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="O187" t="n">
         <v>0</v>
@@ -22757,7 +22757,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -22767,12 +22767,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -22876,7 +22876,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -22886,12 +22886,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -22908,17 +22908,17 @@
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L189" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="M189" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N189" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O189" t="n">
         <v>0</v>
@@ -22957,10 +22957,10 @@
         <v>0</v>
       </c>
       <c r="AA189" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB189" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC189" t="n">
         <v>0</v>
@@ -23005,12 +23005,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -23243,12 +23243,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -23352,7 +23352,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -23362,12 +23362,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -23384,17 +23384,17 @@
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L193" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="M193" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N193" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O193" t="n">
         <v>0</v>
@@ -23433,10 +23433,10 @@
         <v>0</v>
       </c>
       <c r="AA193" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB193" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC193" t="n">
         <v>0</v>
@@ -23590,7 +23590,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -23600,12 +23600,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -23947,7 +23947,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -23957,12 +23957,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -23983,13 +23983,13 @@
         </is>
       </c>
       <c r="L198" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="M198" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="N198" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O198" t="n">
         <v>0</v>
@@ -24066,7 +24066,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -24076,12 +24076,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -24195,12 +24195,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -24304,7 +24304,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -24314,12 +24314,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -24423,7 +24423,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -24433,12 +24433,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -24542,22 +24542,22 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -24578,13 +24578,13 @@
         </is>
       </c>
       <c r="L203" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M203" t="n">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="N203" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="O203" t="n">
         <v>0</v>
@@ -24629,10 +24629,10 @@
         <v>0</v>
       </c>
       <c r="AC203" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD203" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE203" t="n">
         <v>0</v>
@@ -24661,7 +24661,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -24671,12 +24671,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -24780,7 +24780,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -24790,12 +24790,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -24899,22 +24899,22 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -24935,13 +24935,13 @@
         </is>
       </c>
       <c r="L206" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M206" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N206" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O206" t="n">
         <v>0</v>
@@ -25018,7 +25018,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -25028,12 +25028,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -25137,7 +25137,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -25147,12 +25147,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -25173,13 +25173,13 @@
         </is>
       </c>
       <c r="L208" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="M208" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="N208" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O208" t="n">
         <v>0</v>
@@ -25256,22 +25256,22 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -25292,13 +25292,13 @@
         </is>
       </c>
       <c r="L209" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M209" t="n">
-        <v>4.19</v>
+        <v>0</v>
       </c>
       <c r="N209" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="O209" t="n">
         <v>0</v>
@@ -25343,10 +25343,10 @@
         <v>0</v>
       </c>
       <c r="AC209" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD209" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE209" t="n">
         <v>0</v>
@@ -25375,22 +25375,22 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -25411,13 +25411,13 @@
         </is>
       </c>
       <c r="L210" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M210" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N210" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O210" t="n">
         <v>0</v>
@@ -25494,22 +25494,22 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -25530,13 +25530,13 @@
         </is>
       </c>
       <c r="L211" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="M211" t="n">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="N211" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="O211" t="n">
         <v>0</v>
@@ -25613,7 +25613,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -25623,12 +25623,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -25732,22 +25732,22 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -25768,13 +25768,13 @@
         </is>
       </c>
       <c r="L213" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="M213" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="N213" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O213" t="n">
         <v>0</v>
@@ -25851,7 +25851,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -25861,12 +25861,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -25887,13 +25887,13 @@
         </is>
       </c>
       <c r="L214" t="n">
-        <v>0</v>
+        <v>4.57</v>
       </c>
       <c r="M214" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="N214" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="O214" t="n">
         <v>0</v>
@@ -25932,10 +25932,10 @@
         <v>0</v>
       </c>
       <c r="AA214" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB214" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC214" t="n">
         <v>0</v>
@@ -26089,7 +26089,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -26099,12 +26099,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -26125,13 +26125,13 @@
         </is>
       </c>
       <c r="L216" t="n">
-        <v>4.57</v>
+        <v>0</v>
       </c>
       <c r="M216" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="N216" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="O216" t="n">
         <v>0</v>
@@ -26170,10 +26170,10 @@
         <v>0</v>
       </c>
       <c r="AA216" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AB216" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC216" t="n">
         <v>0</v>
@@ -26208,7 +26208,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -26218,12 +26218,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -26327,7 +26327,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -26337,12 +26337,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -26363,13 +26363,13 @@
         </is>
       </c>
       <c r="L218" t="n">
-        <v>2.22</v>
+        <v>1.42</v>
       </c>
       <c r="M218" t="n">
-        <v>3.44</v>
+        <v>5.28</v>
       </c>
       <c r="N218" t="n">
-        <v>3.66</v>
+        <v>8.1</v>
       </c>
       <c r="O218" t="n">
         <v>0</v>
@@ -26408,16 +26408,16 @@
         <v>0</v>
       </c>
       <c r="AA218" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB218" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AC218" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD218" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE218" t="n">
         <v>0</v>
@@ -26446,7 +26446,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -26456,12 +26456,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -26482,13 +26482,13 @@
         </is>
       </c>
       <c r="L219" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="M219" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="N219" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="O219" t="n">
         <v>0</v>
@@ -26527,10 +26527,10 @@
         <v>0</v>
       </c>
       <c r="AA219" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB219" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC219" t="n">
         <v>0</v>
@@ -26565,7 +26565,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -26575,12 +26575,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -26684,7 +26684,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -26694,12 +26694,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -26803,7 +26803,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -26813,12 +26813,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -26839,13 +26839,13 @@
         </is>
       </c>
       <c r="L222" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="M222" t="n">
-        <v>5.28</v>
+        <v>0</v>
       </c>
       <c r="N222" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="O222" t="n">
         <v>0</v>
@@ -26890,10 +26890,10 @@
         <v>0</v>
       </c>
       <c r="AC222" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD222" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE222" t="n">
         <v>0</v>
@@ -26922,7 +26922,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -26932,12 +26932,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -27041,7 +27041,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -27051,12 +27051,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -27160,7 +27160,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -27170,12 +27170,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -27279,7 +27279,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -27289,12 +27289,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -27636,7 +27636,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -27646,12 +27646,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -27755,7 +27755,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -27765,12 +27765,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -27874,7 +27874,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -27884,12 +27884,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -27993,7 +27993,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -28003,12 +28003,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -28029,13 +28029,13 @@
         </is>
       </c>
       <c r="L232" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="M232" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="N232" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O232" t="n">
         <v>0</v>
@@ -28074,10 +28074,10 @@
         <v>0</v>
       </c>
       <c r="AA232" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB232" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC232" t="n">
         <v>0</v>
@@ -28112,7 +28112,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -28122,12 +28122,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -28148,13 +28148,13 @@
         </is>
       </c>
       <c r="L233" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="M233" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="N233" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O233" t="n">
         <v>0</v>
@@ -28193,10 +28193,10 @@
         <v>0</v>
       </c>
       <c r="AA233" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB233" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC233" t="n">
         <v>0</v>
@@ -28231,7 +28231,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -28241,12 +28241,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -28360,12 +28360,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -28469,7 +28469,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -28479,12 +28479,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -28707,7 +28707,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -28717,12 +28717,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -28743,13 +28743,13 @@
         </is>
       </c>
       <c r="L238" t="n">
-        <v>0</v>
+        <v>6.71</v>
       </c>
       <c r="M238" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N238" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="O238" t="n">
         <v>0</v>
@@ -28826,7 +28826,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -28836,12 +28836,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -28862,13 +28862,13 @@
         </is>
       </c>
       <c r="L239" t="n">
-        <v>6.71</v>
+        <v>0</v>
       </c>
       <c r="M239" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="N239" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="O239" t="n">
         <v>0</v>
@@ -28945,7 +28945,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -28955,12 +28955,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -29183,7 +29183,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -29193,12 +29193,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -29302,7 +29302,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -29312,12 +29312,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -29421,7 +29421,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -29431,12 +29431,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -29540,22 +29540,22 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -29659,22 +29659,22 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -29778,22 +29778,22 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -29814,13 +29814,13 @@
         </is>
       </c>
       <c r="L247" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="M247" t="n">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="N247" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O247" t="n">
         <v>0</v>
@@ -29897,22 +29897,22 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -29933,13 +29933,13 @@
         </is>
       </c>
       <c r="L248" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="M248" t="n">
-        <v>4.01</v>
+        <v>0</v>
       </c>
       <c r="N248" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O248" t="n">
         <v>0</v>
@@ -30016,7 +30016,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -30026,12 +30026,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -30135,22 +30135,22 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -30171,13 +30171,13 @@
         </is>
       </c>
       <c r="L250" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="M250" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="N250" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="O250" t="n">
         <v>0</v>
@@ -30222,10 +30222,10 @@
         <v>0</v>
       </c>
       <c r="AC250" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD250" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AE250" t="n">
         <v>0</v>
@@ -30254,7 +30254,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -30264,12 +30264,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -30373,22 +30373,22 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -30492,7 +30492,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -30502,12 +30502,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -30730,7 +30730,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -30740,12 +30740,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -30766,13 +30766,13 @@
         </is>
       </c>
       <c r="L255" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="M255" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="N255" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="O255" t="n">
         <v>0</v>
@@ -30817,10 +30817,10 @@
         <v>0</v>
       </c>
       <c r="AC255" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD255" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AE255" t="n">
         <v>0</v>
@@ -30849,7 +30849,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -30859,12 +30859,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Connecticut United</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -30885,13 +30885,13 @@
         </is>
       </c>
       <c r="L256" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M256" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="N256" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O256" t="n">
         <v>0</v>
@@ -30968,22 +30968,22 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -31004,13 +31004,13 @@
         </is>
       </c>
       <c r="L257" t="n">
-        <v>2.3</v>
+        <v>1.29</v>
       </c>
       <c r="M257" t="n">
-        <v>2.88</v>
+        <v>5.1</v>
       </c>
       <c r="N257" t="n">
-        <v>3.4</v>
+        <v>10.5</v>
       </c>
       <c r="O257" t="n">
         <v>0</v>
@@ -31049,10 +31049,10 @@
         <v>0</v>
       </c>
       <c r="AA257" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB257" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC257" t="n">
         <v>0</v>
@@ -31087,7 +31087,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -31097,12 +31097,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Connecticut United</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -31123,13 +31123,13 @@
         </is>
       </c>
       <c r="L258" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M258" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="N258" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O258" t="n">
         <v>0</v>
@@ -31206,22 +31206,22 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -31242,13 +31242,13 @@
         </is>
       </c>
       <c r="L259" t="n">
-        <v>1.29</v>
+        <v>2</v>
       </c>
       <c r="M259" t="n">
-        <v>5.1</v>
+        <v>2.88</v>
       </c>
       <c r="N259" t="n">
-        <v>10.5</v>
+        <v>4.2</v>
       </c>
       <c r="O259" t="n">
         <v>0</v>
@@ -31287,10 +31287,10 @@
         <v>0</v>
       </c>
       <c r="AA259" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB259" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC259" t="n">
         <v>0</v>
@@ -31325,7 +31325,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -31335,12 +31335,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -31361,13 +31361,13 @@
         </is>
       </c>
       <c r="L260" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M260" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="N260" t="n">
-        <v>4.94</v>
+        <v>0</v>
       </c>
       <c r="O260" t="n">
         <v>0</v>
@@ -31406,10 +31406,10 @@
         <v>0</v>
       </c>
       <c r="AA260" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB260" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC260" t="n">
         <v>0</v>
@@ -31454,12 +31454,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -31480,13 +31480,13 @@
         </is>
       </c>
       <c r="L261" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="M261" t="n">
-        <v>3.42</v>
+        <v>3.25</v>
       </c>
       <c r="N261" t="n">
-        <v>3.4</v>
+        <v>3.24</v>
       </c>
       <c r="O261" t="n">
         <v>0</v>
@@ -31525,10 +31525,10 @@
         <v>0</v>
       </c>
       <c r="AA261" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AB261" t="n">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="AC261" t="n">
         <v>0</v>
@@ -31573,12 +31573,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -31599,13 +31599,13 @@
         </is>
       </c>
       <c r="L262" t="n">
-        <v>2.35</v>
+        <v>1.75</v>
       </c>
       <c r="M262" t="n">
-        <v>3.25</v>
+        <v>3.74</v>
       </c>
       <c r="N262" t="n">
-        <v>3.24</v>
+        <v>4.94</v>
       </c>
       <c r="O262" t="n">
         <v>0</v>
@@ -31644,10 +31644,10 @@
         <v>0</v>
       </c>
       <c r="AA262" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AB262" t="n">
-        <v>1.63</v>
+        <v>1.8</v>
       </c>
       <c r="AC262" t="n">
         <v>0</v>
@@ -31682,7 +31682,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -31692,12 +31692,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -31718,13 +31718,13 @@
         </is>
       </c>
       <c r="L263" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M263" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="N263" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O263" t="n">
         <v>0</v>
@@ -31763,10 +31763,10 @@
         <v>0</v>
       </c>
       <c r="AA263" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB263" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC263" t="n">
         <v>0</v>
@@ -32039,7 +32039,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -32049,12 +32049,12 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="G266" t="n">
@@ -32075,13 +32075,13 @@
         </is>
       </c>
       <c r="L266" t="n">
-        <v>3.79</v>
+        <v>2.67</v>
       </c>
       <c r="M266" t="n">
         <v>3.38</v>
       </c>
       <c r="N266" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="O266" t="n">
         <v>0</v>
@@ -32120,10 +32120,10 @@
         <v>0</v>
       </c>
       <c r="AA266" t="n">
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="AB266" t="n">
-        <v>1.57</v>
+        <v>1.95</v>
       </c>
       <c r="AC266" t="n">
         <v>0</v>
@@ -32158,7 +32158,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -32168,12 +32168,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G267" t="n">
@@ -32194,13 +32194,13 @@
         </is>
       </c>
       <c r="L267" t="n">
-        <v>2.67</v>
+        <v>3.79</v>
       </c>
       <c r="M267" t="n">
         <v>3.38</v>
       </c>
       <c r="N267" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="O267" t="n">
         <v>0</v>
@@ -32239,10 +32239,10 @@
         <v>0</v>
       </c>
       <c r="AA267" t="n">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="AB267" t="n">
-        <v>1.95</v>
+        <v>1.57</v>
       </c>
       <c r="AC267" t="n">
         <v>0</v>
@@ -32277,7 +32277,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -32287,12 +32287,12 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="G268" t="n">
@@ -32396,7 +32396,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -32406,12 +32406,12 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G269" t="n">
@@ -32432,13 +32432,13 @@
         </is>
       </c>
       <c r="L269" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M269" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N269" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="O269" t="n">
         <v>0</v>
@@ -32515,7 +32515,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -32525,12 +32525,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G270" t="n">
@@ -32634,22 +32634,22 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G271" t="n">
@@ -32753,22 +32753,22 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G272" t="n">
@@ -32789,13 +32789,13 @@
         </is>
       </c>
       <c r="L272" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M272" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N272" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="O272" t="n">
         <v>0</v>
@@ -32991,7 +32991,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -33001,12 +33001,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G274" t="n">
@@ -33120,12 +33120,12 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G275" t="n">
@@ -33239,12 +33239,12 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G276" t="n">
@@ -33358,12 +33358,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G277" t="n">
@@ -33467,22 +33467,22 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G278" t="n">
@@ -33503,13 +33503,13 @@
         </is>
       </c>
       <c r="L278" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M278" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N278" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O278" t="n">
         <v>0</v>
@@ -33586,7 +33586,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -33596,12 +33596,12 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G279" t="n">
@@ -33705,22 +33705,22 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="G280" t="n">
@@ -33824,7 +33824,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -33834,12 +33834,12 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G281" t="n">
@@ -34062,7 +34062,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -34072,12 +34072,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="G283" t="n">
@@ -34181,7 +34181,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -34191,12 +34191,12 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Real Monarchs</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Los Angeles II</t>
         </is>
       </c>
       <c r="G284" t="n">
@@ -34217,13 +34217,13 @@
         </is>
       </c>
       <c r="L284" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="M284" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="N284" t="n">
-        <v>6.69</v>
+        <v>0</v>
       </c>
       <c r="O284" t="n">
         <v>0</v>
@@ -34262,10 +34262,10 @@
         <v>0</v>
       </c>
       <c r="AA284" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB284" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC284" t="n">
         <v>0</v>
@@ -34310,12 +34310,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G285" t="n">
@@ -34336,13 +34336,13 @@
         </is>
       </c>
       <c r="L285" t="n">
-        <v>1.83</v>
+        <v>1.51</v>
       </c>
       <c r="M285" t="n">
-        <v>3.46</v>
+        <v>4.32</v>
       </c>
       <c r="N285" t="n">
-        <v>4.84</v>
+        <v>6.69</v>
       </c>
       <c r="O285" t="n">
         <v>0</v>
@@ -34381,10 +34381,10 @@
         <v>0</v>
       </c>
       <c r="AA285" t="n">
-        <v>2.25</v>
+        <v>1.65</v>
       </c>
       <c r="AB285" t="n">
-        <v>1.57</v>
+        <v>2.1</v>
       </c>
       <c r="AC285" t="n">
         <v>0</v>
@@ -34419,7 +34419,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -34429,12 +34429,12 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Real Monarchs</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Los Angeles II</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G286" t="n">
@@ -34455,13 +34455,13 @@
         </is>
       </c>
       <c r="L286" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M286" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="N286" t="n">
-        <v>0</v>
+        <v>4.84</v>
       </c>
       <c r="O286" t="n">
         <v>0</v>
@@ -34500,10 +34500,10 @@
         <v>0</v>
       </c>
       <c r="AA286" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB286" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC286" t="n">
         <v>0</v>
@@ -34667,12 +34667,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Atlanta United II</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="G288" t="n">
@@ -34786,12 +34786,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>Atlanta United II</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="G289" t="n">
@@ -34905,12 +34905,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G290" t="n">
@@ -35288,13 +35288,13 @@
         </is>
       </c>
       <c r="L293" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="M293" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N293" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O293" t="n">
         <v>0</v>
@@ -35333,10 +35333,10 @@
         <v>0</v>
       </c>
       <c r="AA293" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB293" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC293" t="n">
         <v>0</v>
@@ -35371,7 +35371,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -35381,12 +35381,12 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G294" t="n">
@@ -35407,13 +35407,13 @@
         </is>
       </c>
       <c r="L294" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="M294" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N294" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="O294" t="n">
         <v>0</v>
@@ -35452,10 +35452,10 @@
         <v>0</v>
       </c>
       <c r="AA294" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB294" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC294" t="n">
         <v>0</v>
@@ -35609,7 +35609,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -35619,12 +35619,12 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G296" t="n">
@@ -35728,7 +35728,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -35738,12 +35738,12 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G297" t="n">
@@ -35764,13 +35764,13 @@
         </is>
       </c>
       <c r="L297" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="M297" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N297" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="O297" t="n">
         <v>0</v>
@@ -35809,10 +35809,10 @@
         <v>0</v>
       </c>
       <c r="AA297" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB297" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC297" t="n">
         <v>0</v>

--- a/jogos_2026-03-15.xlsx
+++ b/jogos_2026-03-15.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,22 +1932,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Melbourne Victory FC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Macarthur</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2051,22 +2051,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Melbourne Victory FC</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Macarthur</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>4.08</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2646,22 +2646,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2884,22 +2884,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Port FC</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,22 +3360,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,22 +3836,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Port FC</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5026,22 +5026,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5264,22 +5264,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,22 +5502,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5978,22 +5978,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>4.48</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>6.17</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>4.48</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>6.17</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6454,22 +6454,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6529,10 +6529,10 @@
         <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z51" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Kanchanaburi</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>NorthEast United</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Jamshedpur</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6767,10 +6767,10 @@
         <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z53" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA53" t="n">
         <v>0</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7168,22 +7168,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>NorthEast United</t>
+          <t>Kanchanaburi</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Jamshedpur</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Ayutthaya United</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ayutthaya United</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9191,22 +9191,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9310,22 +9310,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9548,22 +9548,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9905,22 +9905,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Balestier Khalsa</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Home United</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10024,22 +10024,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Balestier Khalsa</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Home United</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10381,22 +10381,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="M103" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N103" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Johor Darul Ta'zim</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13154,13 +13154,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>2.57</v>
+        <v>1.35</v>
       </c>
       <c r="M107" t="n">
-        <v>3.3</v>
+        <v>5.58</v>
       </c>
       <c r="N107" t="n">
-        <v>3.1</v>
+        <v>8.1</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13273,13 +13273,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="M108" t="n">
-        <v>5.97</v>
+        <v>0</v>
       </c>
       <c r="N108" t="n">
-        <v>10.3</v>
+        <v>0</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13511,13 +13511,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="M110" t="n">
-        <v>5.58</v>
+        <v>0</v>
       </c>
       <c r="N110" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13630,13 +13630,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="M111" t="n">
-        <v>0</v>
+        <v>5.97</v>
       </c>
       <c r="N111" t="n">
-        <v>0</v>
+        <v>10.3</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Johor Darul Ta'zim</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13951,7 +13951,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14070,7 +14070,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14106,13 +14106,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M115" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="N115" t="n">
-        <v>0</v>
+        <v>4.77</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -14151,10 +14151,10 @@
         <v>0</v>
       </c>
       <c r="AA115" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB115" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC115" t="n">
         <v>0</v>
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>2.64</v>
+        <v>2.29</v>
       </c>
       <c r="M116" t="n">
-        <v>3.38</v>
+        <v>3.62</v>
       </c>
       <c r="N116" t="n">
-        <v>2.52</v>
+        <v>3.31</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -14270,10 +14270,10 @@
         <v>0</v>
       </c>
       <c r="AA116" t="n">
-        <v>2.03</v>
+        <v>1.79</v>
       </c>
       <c r="AB116" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AC116" t="n">
         <v>0</v>
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14344,13 +14344,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M117" t="n">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="N117" t="n">
-        <v>4.77</v>
+        <v>0</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -14389,10 +14389,10 @@
         <v>0</v>
       </c>
       <c r="AA117" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB117" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AC117" t="n">
         <v>0</v>
@@ -14427,22 +14427,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14820,13 +14820,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>2.48</v>
+        <v>2.19</v>
       </c>
       <c r="M121" t="n">
-        <v>3.29</v>
+        <v>3.58</v>
       </c>
       <c r="N121" t="n">
-        <v>3.25</v>
+        <v>3.58</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -14865,10 +14865,10 @@
         <v>0</v>
       </c>
       <c r="AA121" t="n">
-        <v>2.3</v>
+        <v>1.96</v>
       </c>
       <c r="AB121" t="n">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="AC121" t="n">
         <v>0</v>
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15058,13 +15058,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="M123" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N123" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -15103,10 +15103,10 @@
         <v>0</v>
       </c>
       <c r="AA123" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB123" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC123" t="n">
         <v>0</v>
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15177,13 +15177,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="M124" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="N124" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -15222,10 +15222,10 @@
         <v>0</v>
       </c>
       <c r="AA124" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB124" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC124" t="n">
         <v>0</v>
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Inter Kashi</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Mumbai City</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15653,13 +15653,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="M128" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="N128" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -15698,10 +15698,10 @@
         <v>0</v>
       </c>
       <c r="AA128" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB128" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC128" t="n">
         <v>0</v>
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15772,13 +15772,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M129" t="n">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="N129" t="n">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -15817,10 +15817,10 @@
         <v>0</v>
       </c>
       <c r="AA129" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB129" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC129" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="M130" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="N130" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -15936,10 +15936,10 @@
         <v>0</v>
       </c>
       <c r="AA130" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB130" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC130" t="n">
         <v>0</v>
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Inter Kashi</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Mumbai City</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16129,13 +16129,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="M132" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N132" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -16174,10 +16174,10 @@
         <v>0</v>
       </c>
       <c r="AA132" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB132" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC132" t="n">
         <v>0</v>
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16248,13 +16248,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M133" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="N133" t="n">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -16293,10 +16293,10 @@
         <v>0</v>
       </c>
       <c r="AA133" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB133" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC133" t="n">
         <v>0</v>
@@ -16331,22 +16331,22 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16367,13 +16367,13 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="M134" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="N134" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -16412,10 +16412,10 @@
         <v>0</v>
       </c>
       <c r="AA134" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB134" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC134" t="n">
         <v>0</v>
@@ -16450,7 +16450,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16926,22 +16926,22 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -17045,22 +17045,22 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17164,22 +17164,22 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17402,7 +17402,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Chaves II</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Mirandela</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17640,22 +17640,22 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Lajense</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17759,7 +17759,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>AR São Martinho</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17878,7 +17878,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Monção</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -17997,7 +17997,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -18007,12 +18007,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Clube Oriental de Lisboa</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -18116,7 +18116,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Gouveia</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18235,7 +18235,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -18245,12 +18245,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -18354,7 +18354,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -18364,12 +18364,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -18473,7 +18473,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -18483,12 +18483,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -18592,7 +18592,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -18602,12 +18602,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -18711,7 +18711,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -18721,12 +18721,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -18830,7 +18830,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -18840,12 +18840,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -18949,7 +18949,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -18959,12 +18959,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -19068,22 +19068,22 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -19187,7 +19187,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -19306,7 +19306,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -19316,12 +19316,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Machico</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Eléctrico</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -19435,12 +19435,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19554,12 +19554,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -19663,22 +19663,22 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -19782,7 +19782,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -19792,12 +19792,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -19901,22 +19901,22 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -20020,7 +20020,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -20030,12 +20030,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -20139,7 +20139,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -20149,12 +20149,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -20258,7 +20258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -20268,12 +20268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -20377,7 +20377,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -20387,12 +20387,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -20496,7 +20496,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -20506,12 +20506,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -20615,7 +20615,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -20625,12 +20625,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -20734,7 +20734,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -20744,12 +20744,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -20853,7 +20853,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -20863,12 +20863,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Clube Oriental de Lisboa</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -20972,7 +20972,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -20982,12 +20982,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Machico</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -21091,7 +21091,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -21101,12 +21101,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Monção</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -21210,7 +21210,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -21220,12 +21220,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Chaves II</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Mirandela</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -21339,12 +21339,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -21448,7 +21448,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -21458,12 +21458,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>AR São Martinho</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -21567,22 +21567,22 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -21686,7 +21686,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -21696,12 +21696,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Eléctrico</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -22053,12 +22053,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -22400,7 +22400,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -22410,12 +22410,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -22432,7 +22432,7 @@
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L185" t="n">
@@ -22519,7 +22519,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -22529,12 +22529,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -22551,7 +22551,7 @@
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L186" t="n">
@@ -22638,7 +22638,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -22648,12 +22648,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -22674,13 +22674,13 @@
         </is>
       </c>
       <c r="L187" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="M187" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="N187" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="O187" t="n">
         <v>0</v>
@@ -22757,7 +22757,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -22767,12 +22767,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -22793,13 +22793,13 @@
         </is>
       </c>
       <c r="L188" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="M188" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="N188" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="O188" t="n">
         <v>0</v>
@@ -23005,12 +23005,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -23124,12 +23124,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -23471,7 +23471,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -23481,12 +23481,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -23507,13 +23507,13 @@
         </is>
       </c>
       <c r="L194" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="M194" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="N194" t="n">
-        <v>7.19</v>
+        <v>0</v>
       </c>
       <c r="O194" t="n">
         <v>0</v>
@@ -23590,22 +23590,22 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -23626,13 +23626,13 @@
         </is>
       </c>
       <c r="L195" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="M195" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="N195" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O195" t="n">
         <v>0</v>
@@ -23709,7 +23709,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -23719,12 +23719,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -23745,13 +23745,13 @@
         </is>
       </c>
       <c r="L196" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="M196" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="N196" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O196" t="n">
         <v>0</v>
@@ -23828,7 +23828,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -23838,12 +23838,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -23860,7 +23860,7 @@
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L197" t="n">
@@ -23947,22 +23947,22 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -23983,13 +23983,13 @@
         </is>
       </c>
       <c r="L198" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M198" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N198" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O198" t="n">
         <v>0</v>
@@ -24066,22 +24066,22 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -24102,13 +24102,13 @@
         </is>
       </c>
       <c r="L199" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M199" t="n">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="N199" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="O199" t="n">
         <v>0</v>
@@ -24153,10 +24153,10 @@
         <v>0</v>
       </c>
       <c r="AC199" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD199" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE199" t="n">
         <v>0</v>
@@ -24195,12 +24195,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -24314,12 +24314,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -24423,7 +24423,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -24433,12 +24433,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -24542,22 +24542,22 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -24578,13 +24578,13 @@
         </is>
       </c>
       <c r="L203" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M203" t="n">
-        <v>4.19</v>
+        <v>0</v>
       </c>
       <c r="N203" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="O203" t="n">
         <v>0</v>
@@ -24629,10 +24629,10 @@
         <v>0</v>
       </c>
       <c r="AC203" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD203" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE203" t="n">
         <v>0</v>
@@ -24661,7 +24661,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -24671,12 +24671,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -24790,12 +24790,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -24899,22 +24899,22 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -24931,17 +24931,17 @@
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L206" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M206" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N206" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O206" t="n">
         <v>0</v>
@@ -25018,7 +25018,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -25028,12 +25028,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -25137,7 +25137,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -25147,12 +25147,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -25173,13 +25173,13 @@
         </is>
       </c>
       <c r="L208" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="M208" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="N208" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O208" t="n">
         <v>0</v>
@@ -25256,7 +25256,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -25266,12 +25266,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -25375,7 +25375,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -25385,12 +25385,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -25494,7 +25494,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -25504,12 +25504,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -25613,7 +25613,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -25623,12 +25623,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -25649,13 +25649,13 @@
         </is>
       </c>
       <c r="L212" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="M212" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="N212" t="n">
-        <v>0</v>
+        <v>7.19</v>
       </c>
       <c r="O212" t="n">
         <v>0</v>
@@ -25732,22 +25732,22 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -25768,13 +25768,13 @@
         </is>
       </c>
       <c r="L213" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="M213" t="n">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="N213" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="O213" t="n">
         <v>0</v>
@@ -26208,7 +26208,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -26218,12 +26218,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -26327,7 +26327,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -26337,12 +26337,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -26363,13 +26363,13 @@
         </is>
       </c>
       <c r="L218" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="M218" t="n">
-        <v>5.28</v>
+        <v>0</v>
       </c>
       <c r="N218" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="O218" t="n">
         <v>0</v>
@@ -26414,10 +26414,10 @@
         <v>0</v>
       </c>
       <c r="AC218" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD218" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE218" t="n">
         <v>0</v>
@@ -26446,7 +26446,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -26456,12 +26456,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -26482,13 +26482,13 @@
         </is>
       </c>
       <c r="L219" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="M219" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="N219" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="O219" t="n">
         <v>0</v>
@@ -26527,10 +26527,10 @@
         <v>0</v>
       </c>
       <c r="AA219" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB219" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AC219" t="n">
         <v>0</v>
@@ -26565,7 +26565,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -26575,12 +26575,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -26684,7 +26684,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -26694,12 +26694,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -26803,7 +26803,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -26813,12 +26813,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -26922,7 +26922,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -26932,12 +26932,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -26958,13 +26958,13 @@
         </is>
       </c>
       <c r="L223" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="M223" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="N223" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="O223" t="n">
         <v>0</v>
@@ -27003,10 +27003,10 @@
         <v>0</v>
       </c>
       <c r="AA223" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB223" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC223" t="n">
         <v>0</v>
@@ -27041,7 +27041,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -27051,12 +27051,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -27160,7 +27160,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -27170,12 +27170,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -27279,7 +27279,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -27289,12 +27289,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -27315,13 +27315,13 @@
         </is>
       </c>
       <c r="L226" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="M226" t="n">
-        <v>0</v>
+        <v>5.28</v>
       </c>
       <c r="N226" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="O226" t="n">
         <v>0</v>
@@ -27366,10 +27366,10 @@
         <v>0</v>
       </c>
       <c r="AC226" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD226" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE226" t="n">
         <v>0</v>
@@ -27398,7 +27398,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -27408,12 +27408,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -27636,22 +27636,22 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -27755,22 +27755,22 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -27874,22 +27874,22 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -27993,7 +27993,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -28003,12 +28003,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -28112,7 +28112,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -28122,12 +28122,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -28148,13 +28148,13 @@
         </is>
       </c>
       <c r="L233" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="M233" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="N233" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O233" t="n">
         <v>0</v>
@@ -28193,10 +28193,10 @@
         <v>0</v>
       </c>
       <c r="AA233" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB233" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC233" t="n">
         <v>0</v>
@@ -28231,7 +28231,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -28241,12 +28241,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -28350,22 +28350,22 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -28469,7 +28469,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -28479,12 +28479,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -28505,13 +28505,13 @@
         </is>
       </c>
       <c r="L236" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="M236" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="N236" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O236" t="n">
         <v>0</v>
@@ -28550,10 +28550,10 @@
         <v>0</v>
       </c>
       <c r="AA236" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB236" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC236" t="n">
         <v>0</v>
@@ -28826,7 +28826,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -28836,12 +28836,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -28945,7 +28945,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -28955,12 +28955,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -29064,7 +29064,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -29074,12 +29074,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -29183,7 +29183,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -29193,12 +29193,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -29302,7 +29302,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -29312,12 +29312,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -29421,22 +29421,22 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -29659,22 +29659,22 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -29778,22 +29778,22 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -29814,13 +29814,13 @@
         </is>
       </c>
       <c r="L247" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="M247" t="n">
-        <v>4.01</v>
+        <v>0</v>
       </c>
       <c r="N247" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O247" t="n">
         <v>0</v>
@@ -29897,22 +29897,22 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -29933,13 +29933,13 @@
         </is>
       </c>
       <c r="L248" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="M248" t="n">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="N248" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O248" t="n">
         <v>0</v>
@@ -30016,7 +30016,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -30026,12 +30026,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -30135,22 +30135,22 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -30264,12 +30264,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -30373,7 +30373,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -30383,12 +30383,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -30492,7 +30492,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -30502,12 +30502,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -30528,13 +30528,13 @@
         </is>
       </c>
       <c r="L253" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="M253" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="N253" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="O253" t="n">
         <v>0</v>
@@ -30579,10 +30579,10 @@
         <v>0</v>
       </c>
       <c r="AC253" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD253" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AE253" t="n">
         <v>0</v>
@@ -30611,7 +30611,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -30621,12 +30621,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -30730,22 +30730,22 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -30766,13 +30766,13 @@
         </is>
       </c>
       <c r="L255" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="M255" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="N255" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="O255" t="n">
         <v>0</v>
@@ -30817,10 +30817,10 @@
         <v>0</v>
       </c>
       <c r="AC255" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD255" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AE255" t="n">
         <v>0</v>
@@ -30849,7 +30849,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -30859,12 +30859,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -30885,13 +30885,13 @@
         </is>
       </c>
       <c r="L256" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="M256" t="n">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="N256" t="n">
-        <v>3.4</v>
+        <v>3.24</v>
       </c>
       <c r="O256" t="n">
         <v>0</v>
@@ -30930,10 +30930,10 @@
         <v>0</v>
       </c>
       <c r="AA256" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB256" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC256" t="n">
         <v>0</v>
@@ -30968,22 +30968,22 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -31004,13 +31004,13 @@
         </is>
       </c>
       <c r="L257" t="n">
-        <v>1.29</v>
+        <v>1.75</v>
       </c>
       <c r="M257" t="n">
-        <v>5.1</v>
+        <v>3.74</v>
       </c>
       <c r="N257" t="n">
-        <v>10.5</v>
+        <v>4.94</v>
       </c>
       <c r="O257" t="n">
         <v>0</v>
@@ -31049,10 +31049,10 @@
         <v>0</v>
       </c>
       <c r="AA257" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AB257" t="n">
-        <v>1.98</v>
+        <v>1.8</v>
       </c>
       <c r="AC257" t="n">
         <v>0</v>
@@ -31087,7 +31087,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -31097,12 +31097,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Connecticut United</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -31123,13 +31123,13 @@
         </is>
       </c>
       <c r="L258" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M258" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="N258" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O258" t="n">
         <v>0</v>
@@ -31168,10 +31168,10 @@
         <v>0</v>
       </c>
       <c r="AA258" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB258" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC258" t="n">
         <v>0</v>
@@ -31206,22 +31206,22 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -31242,13 +31242,13 @@
         </is>
       </c>
       <c r="L259" t="n">
-        <v>2</v>
+        <v>1.29</v>
       </c>
       <c r="M259" t="n">
-        <v>2.88</v>
+        <v>5.1</v>
       </c>
       <c r="N259" t="n">
-        <v>4.2</v>
+        <v>10.5</v>
       </c>
       <c r="O259" t="n">
         <v>0</v>
@@ -31287,10 +31287,10 @@
         <v>0</v>
       </c>
       <c r="AA259" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB259" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC259" t="n">
         <v>0</v>
@@ -31325,7 +31325,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -31335,12 +31335,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -31361,13 +31361,13 @@
         </is>
       </c>
       <c r="L260" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M260" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="N260" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O260" t="n">
         <v>0</v>
@@ -31444,7 +31444,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -31454,12 +31454,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -31480,13 +31480,13 @@
         </is>
       </c>
       <c r="L261" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="M261" t="n">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="N261" t="n">
-        <v>3.24</v>
+        <v>3.4</v>
       </c>
       <c r="O261" t="n">
         <v>0</v>
@@ -31525,10 +31525,10 @@
         <v>0</v>
       </c>
       <c r="AA261" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB261" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC261" t="n">
         <v>0</v>
@@ -31563,7 +31563,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -31573,12 +31573,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Connecticut United</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -31599,13 +31599,13 @@
         </is>
       </c>
       <c r="L262" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M262" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="N262" t="n">
-        <v>4.94</v>
+        <v>0</v>
       </c>
       <c r="O262" t="n">
         <v>0</v>
@@ -31644,10 +31644,10 @@
         <v>0</v>
       </c>
       <c r="AA262" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB262" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC262" t="n">
         <v>0</v>
@@ -31682,7 +31682,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -31692,12 +31692,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -31718,13 +31718,13 @@
         </is>
       </c>
       <c r="L263" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M263" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="N263" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O263" t="n">
         <v>0</v>
@@ -31763,10 +31763,10 @@
         <v>0</v>
       </c>
       <c r="AA263" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB263" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC263" t="n">
         <v>0</v>
@@ -32277,22 +32277,22 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G268" t="n">
@@ -32515,22 +32515,22 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="G270" t="n">
@@ -32991,22 +32991,22 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G274" t="n">
@@ -33027,13 +33027,13 @@
         </is>
       </c>
       <c r="L274" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M274" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N274" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O274" t="n">
         <v>0</v>
@@ -33110,7 +33110,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -33120,12 +33120,12 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="G275" t="n">
@@ -33358,12 +33358,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G277" t="n">
@@ -33467,7 +33467,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -33477,12 +33477,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G278" t="n">
@@ -33503,13 +33503,13 @@
         </is>
       </c>
       <c r="L278" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M278" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N278" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O278" t="n">
         <v>0</v>
@@ -33586,22 +33586,22 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G279" t="n">
@@ -33705,7 +33705,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -33715,12 +33715,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G280" t="n">
@@ -33824,7 +33824,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -33834,12 +33834,12 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G281" t="n">
@@ -33860,13 +33860,13 @@
         </is>
       </c>
       <c r="L281" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M281" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="N281" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O281" t="n">
         <v>0</v>
@@ -33943,7 +33943,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -33953,12 +33953,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="G282" t="n">
@@ -33979,13 +33979,13 @@
         </is>
       </c>
       <c r="L282" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M282" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="N282" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O282" t="n">
         <v>0</v>
@@ -34062,7 +34062,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -34072,12 +34072,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G283" t="n">
@@ -34310,12 +34310,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G285" t="n">
@@ -34336,13 +34336,13 @@
         </is>
       </c>
       <c r="L285" t="n">
-        <v>1.51</v>
+        <v>1.83</v>
       </c>
       <c r="M285" t="n">
-        <v>4.32</v>
+        <v>3.46</v>
       </c>
       <c r="N285" t="n">
-        <v>6.69</v>
+        <v>4.84</v>
       </c>
       <c r="O285" t="n">
         <v>0</v>
@@ -34381,10 +34381,10 @@
         <v>0</v>
       </c>
       <c r="AA285" t="n">
-        <v>1.65</v>
+        <v>2.25</v>
       </c>
       <c r="AB285" t="n">
-        <v>2.1</v>
+        <v>1.57</v>
       </c>
       <c r="AC285" t="n">
         <v>0</v>
@@ -34429,12 +34429,12 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G286" t="n">
@@ -34455,13 +34455,13 @@
         </is>
       </c>
       <c r="L286" t="n">
-        <v>1.83</v>
+        <v>1.51</v>
       </c>
       <c r="M286" t="n">
-        <v>3.46</v>
+        <v>4.32</v>
       </c>
       <c r="N286" t="n">
-        <v>4.84</v>
+        <v>6.69</v>
       </c>
       <c r="O286" t="n">
         <v>0</v>
@@ -34500,10 +34500,10 @@
         <v>0</v>
       </c>
       <c r="AA286" t="n">
-        <v>2.25</v>
+        <v>1.65</v>
       </c>
       <c r="AB286" t="n">
-        <v>1.57</v>
+        <v>2.1</v>
       </c>
       <c r="AC286" t="n">
         <v>0</v>
@@ -34538,7 +34538,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -34548,12 +34548,12 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G287" t="n">
@@ -34657,7 +34657,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -34667,12 +34667,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G288" t="n">
@@ -34786,12 +34786,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Atlanta United II</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="G289" t="n">
@@ -34905,12 +34905,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="G290" t="n">
@@ -35014,7 +35014,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -35024,12 +35024,12 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Atlanta United II</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="G291" t="n">
@@ -35133,7 +35133,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -35143,12 +35143,12 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G292" t="n">
@@ -35371,7 +35371,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -35381,12 +35381,12 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G294" t="n">
@@ -35609,7 +35609,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -35619,12 +35619,12 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G296" t="n">
@@ -35645,13 +35645,13 @@
         </is>
       </c>
       <c r="L296" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="M296" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N296" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="O296" t="n">
         <v>0</v>
@@ -35690,10 +35690,10 @@
         <v>0</v>
       </c>
       <c r="AA296" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB296" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC296" t="n">
         <v>0</v>
@@ -35728,7 +35728,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -35738,12 +35738,12 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G297" t="n">
@@ -35764,13 +35764,13 @@
         </is>
       </c>
       <c r="L297" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="M297" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N297" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="O297" t="n">
         <v>0</v>
@@ -35809,10 +35809,10 @@
         <v>0</v>
       </c>
       <c r="AA297" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB297" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC297" t="n">
         <v>0</v>

--- a/jogos_2026-03-15.xlsx
+++ b/jogos_2026-03-15.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Marconi Stallions</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Marconi Stallions</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2646,22 +2646,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,22 +2884,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,22 +3836,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Port FC</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4550,22 +4550,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Port FC</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,22 +4669,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4788,22 +4788,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5264,22 +5264,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5502,22 +5502,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6529,10 +6529,10 @@
         <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z51" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6692,22 +6692,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>NorthEast United</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Jamshedpur</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7124,10 +7124,10 @@
         <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z56" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA56" t="n">
         <v>0</v>
@@ -7168,22 +7168,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>NorthEast United</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Jamshedpur</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ayutthaya United</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Ayutthaya United</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9191,22 +9191,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9310,22 +9310,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9548,22 +9548,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9905,22 +9905,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Balestier Khalsa</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Home United</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10262,22 +10262,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Balestier Khalsa</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Home United</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10381,22 +10381,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="M100" t="n">
-        <v>0</v>
+        <v>5.97</v>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>10.3</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="M101" t="n">
-        <v>0</v>
+        <v>5.58</v>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Johor Darul Ta'zim</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="M103" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N103" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="M104" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Johor Darul Ta'zim</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13154,13 +13154,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="M107" t="n">
-        <v>5.58</v>
+        <v>0</v>
       </c>
       <c r="N107" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13630,13 +13630,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="M111" t="n">
-        <v>5.97</v>
+        <v>0</v>
       </c>
       <c r="N111" t="n">
-        <v>10.3</v>
+        <v>0</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14070,7 +14070,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14106,13 +14106,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M115" t="n">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="N115" t="n">
-        <v>4.77</v>
+        <v>0</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -14151,10 +14151,10 @@
         <v>0</v>
       </c>
       <c r="AA115" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB115" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AC115" t="n">
         <v>0</v>
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="M116" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="N116" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -14270,10 +14270,10 @@
         <v>0</v>
       </c>
       <c r="AA116" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB116" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC116" t="n">
         <v>0</v>
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14582,13 +14582,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M119" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="N119" t="n">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -14627,10 +14627,10 @@
         <v>0</v>
       </c>
       <c r="AA119" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB119" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC119" t="n">
         <v>0</v>
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14701,13 +14701,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M120" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="N120" t="n">
-        <v>0</v>
+        <v>4.77</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -14746,10 +14746,10 @@
         <v>0</v>
       </c>
       <c r="AA120" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB120" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC120" t="n">
         <v>0</v>
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Inter Kashi</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Mumbai City</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15177,13 +15177,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>2.64</v>
+        <v>2.96</v>
       </c>
       <c r="M124" t="n">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="N124" t="n">
-        <v>2.52</v>
+        <v>2.61</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -15222,10 +15222,10 @@
         <v>0</v>
       </c>
       <c r="AA124" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AB124" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AC124" t="n">
         <v>0</v>
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15379,22 +15379,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15772,13 +15772,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="M129" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="N129" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -15817,10 +15817,10 @@
         <v>0</v>
       </c>
       <c r="AA129" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB129" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC129" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="M130" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="N130" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -15936,10 +15936,10 @@
         <v>0</v>
       </c>
       <c r="AA130" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB130" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC130" t="n">
         <v>0</v>
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Inter Kashi</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Mumbai City</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16129,13 +16129,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>2.96</v>
+        <v>2.64</v>
       </c>
       <c r="M132" t="n">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="N132" t="n">
-        <v>2.61</v>
+        <v>2.52</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -16174,10 +16174,10 @@
         <v>0</v>
       </c>
       <c r="AA132" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AB132" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AC132" t="n">
         <v>0</v>
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16248,13 +16248,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M133" t="n">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="N133" t="n">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -16293,10 +16293,10 @@
         <v>0</v>
       </c>
       <c r="AA133" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB133" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC133" t="n">
         <v>0</v>
@@ -16331,22 +16331,22 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16450,7 +16450,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16486,13 +16486,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="M135" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="N135" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -16531,10 +16531,10 @@
         <v>0</v>
       </c>
       <c r="AA135" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB135" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC135" t="n">
         <v>0</v>
@@ -16569,7 +16569,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16605,13 +16605,13 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="M136" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N136" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="O136" t="n">
         <v>0</v>
@@ -16650,10 +16650,10 @@
         <v>0</v>
       </c>
       <c r="AA136" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB136" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC136" t="n">
         <v>0</v>
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16843,13 +16843,13 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="M138" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N138" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -16888,10 +16888,10 @@
         <v>0</v>
       </c>
       <c r="AA138" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB138" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC138" t="n">
         <v>0</v>
@@ -17045,22 +17045,22 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -17174,12 +17174,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Eléctrico</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -17283,22 +17283,22 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17521,7 +17521,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Chaves II</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Mirandela</t>
+          <t>Lajense</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17640,7 +17640,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17759,7 +17759,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -18007,12 +18007,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Clube Oriental de Lisboa</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -18116,7 +18116,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18235,7 +18235,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -18245,12 +18245,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -18354,7 +18354,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -18364,12 +18364,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>AR São Martinho</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -18473,7 +18473,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -18483,12 +18483,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -18592,7 +18592,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -18602,12 +18602,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -18711,7 +18711,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -18721,12 +18721,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -18830,22 +18830,22 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -18949,7 +18949,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -18959,12 +18959,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -19068,22 +19068,22 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Monção</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -19187,7 +19187,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Chaves II</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Mirandela</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -19306,22 +19306,22 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Machico</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -19425,7 +19425,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -19435,12 +19435,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19544,22 +19544,22 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -19663,22 +19663,22 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -19782,7 +19782,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -19792,12 +19792,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -19901,22 +19901,22 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Clube Oriental de Lisboa</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -20030,12 +20030,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Machico</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -20139,7 +20139,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -20149,12 +20149,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -20258,7 +20258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -20268,12 +20268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Gouveia</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -20377,7 +20377,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -20387,12 +20387,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -20496,7 +20496,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -20506,12 +20506,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -20615,7 +20615,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -20625,12 +20625,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -20734,7 +20734,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -20744,12 +20744,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -20853,7 +20853,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -20863,12 +20863,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -20972,22 +20972,22 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -21091,22 +21091,22 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Monção</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -21210,7 +21210,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -21220,12 +21220,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -21329,7 +21329,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -21339,12 +21339,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -21448,7 +21448,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -21458,12 +21458,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>AR São Martinho</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -21567,7 +21567,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -21577,12 +21577,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -21686,7 +21686,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -21696,12 +21696,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Eléctrico</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -21805,7 +21805,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -21815,12 +21815,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -21924,7 +21924,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -21934,12 +21934,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -22053,12 +22053,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -22162,7 +22162,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -22172,12 +22172,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -22281,7 +22281,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -22291,12 +22291,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -22400,7 +22400,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -22410,12 +22410,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -22436,13 +22436,13 @@
         </is>
       </c>
       <c r="L185" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="M185" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="N185" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="O185" t="n">
         <v>0</v>
@@ -22519,7 +22519,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -22529,12 +22529,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -22551,7 +22551,7 @@
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L186" t="n">
@@ -22638,7 +22638,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -22648,12 +22648,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -22670,7 +22670,7 @@
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L187" t="n">
@@ -22757,7 +22757,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -22767,12 +22767,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -22793,13 +22793,13 @@
         </is>
       </c>
       <c r="L188" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="M188" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="N188" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="O188" t="n">
         <v>0</v>
@@ -22876,7 +22876,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -22886,12 +22886,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -22908,7 +22908,7 @@
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L189" t="n">
@@ -22995,7 +22995,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -23005,12 +23005,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -23027,7 +23027,7 @@
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L190" t="n">
@@ -23471,7 +23471,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -23481,12 +23481,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -23503,7 +23503,7 @@
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L194" t="n">
@@ -23590,22 +23590,22 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -23626,13 +23626,13 @@
         </is>
       </c>
       <c r="L195" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="M195" t="n">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="N195" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="O195" t="n">
         <v>0</v>
@@ -23947,22 +23947,22 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -23983,13 +23983,13 @@
         </is>
       </c>
       <c r="L198" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M198" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N198" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O198" t="n">
         <v>0</v>
@@ -24066,22 +24066,22 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -24102,13 +24102,13 @@
         </is>
       </c>
       <c r="L199" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M199" t="n">
-        <v>4.19</v>
+        <v>0</v>
       </c>
       <c r="N199" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="O199" t="n">
         <v>0</v>
@@ -24153,10 +24153,10 @@
         <v>0</v>
       </c>
       <c r="AC199" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD199" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE199" t="n">
         <v>0</v>
@@ -24185,7 +24185,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -24195,12 +24195,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -24221,13 +24221,13 @@
         </is>
       </c>
       <c r="L200" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="M200" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="N200" t="n">
-        <v>0</v>
+        <v>7.19</v>
       </c>
       <c r="O200" t="n">
         <v>0</v>
@@ -24304,7 +24304,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -24314,12 +24314,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -24423,7 +24423,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -24433,12 +24433,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -24542,7 +24542,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -24552,12 +24552,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -24661,7 +24661,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -24671,12 +24671,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -24780,7 +24780,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -24790,12 +24790,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -24899,7 +24899,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -24909,12 +24909,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -24931,7 +24931,7 @@
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L206" t="n">
@@ -25028,12 +25028,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -25137,22 +25137,22 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -25173,13 +25173,13 @@
         </is>
       </c>
       <c r="L208" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="M208" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="N208" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O208" t="n">
         <v>0</v>
@@ -25256,22 +25256,22 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -25292,13 +25292,13 @@
         </is>
       </c>
       <c r="L209" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M209" t="n">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="N209" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="O209" t="n">
         <v>0</v>
@@ -25343,10 +25343,10 @@
         <v>0</v>
       </c>
       <c r="AC209" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD209" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE209" t="n">
         <v>0</v>
@@ -25375,7 +25375,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -25385,12 +25385,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -25494,7 +25494,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -25504,12 +25504,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -25613,22 +25613,22 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -25649,13 +25649,13 @@
         </is>
       </c>
       <c r="L212" t="n">
-        <v>1.42</v>
+        <v>1.95</v>
       </c>
       <c r="M212" t="n">
-        <v>4.45</v>
+        <v>3.65</v>
       </c>
       <c r="N212" t="n">
-        <v>7.19</v>
+        <v>3.85</v>
       </c>
       <c r="O212" t="n">
         <v>0</v>
@@ -25732,7 +25732,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -25742,12 +25742,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -25861,12 +25861,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -25887,13 +25887,13 @@
         </is>
       </c>
       <c r="L214" t="n">
-        <v>4.57</v>
+        <v>4.11</v>
       </c>
       <c r="M214" t="n">
-        <v>3.78</v>
+        <v>3.49</v>
       </c>
       <c r="N214" t="n">
-        <v>1.88</v>
+        <v>2.06</v>
       </c>
       <c r="O214" t="n">
         <v>0</v>
@@ -25932,10 +25932,10 @@
         <v>0</v>
       </c>
       <c r="AA214" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="AB214" t="n">
-        <v>1.79</v>
+        <v>1.66</v>
       </c>
       <c r="AC214" t="n">
         <v>0</v>
@@ -25980,12 +25980,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -26006,13 +26006,13 @@
         </is>
       </c>
       <c r="L215" t="n">
-        <v>4.11</v>
+        <v>4.57</v>
       </c>
       <c r="M215" t="n">
-        <v>3.49</v>
+        <v>3.78</v>
       </c>
       <c r="N215" t="n">
-        <v>2.06</v>
+        <v>1.88</v>
       </c>
       <c r="O215" t="n">
         <v>0</v>
@@ -26051,10 +26051,10 @@
         <v>0</v>
       </c>
       <c r="AA215" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AB215" t="n">
-        <v>1.66</v>
+        <v>1.79</v>
       </c>
       <c r="AC215" t="n">
         <v>0</v>
@@ -26208,7 +26208,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -26218,12 +26218,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -26327,7 +26327,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -26337,12 +26337,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -26446,7 +26446,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -26456,12 +26456,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -26565,7 +26565,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -26575,12 +26575,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -26684,7 +26684,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -26694,12 +26694,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -26803,7 +26803,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -26813,12 +26813,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -26922,7 +26922,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -26932,12 +26932,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -26958,13 +26958,13 @@
         </is>
       </c>
       <c r="L223" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="M223" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="N223" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="O223" t="n">
         <v>0</v>
@@ -27003,10 +27003,10 @@
         <v>0</v>
       </c>
       <c r="AA223" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB223" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AC223" t="n">
         <v>0</v>
@@ -27041,7 +27041,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -27051,12 +27051,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -27077,13 +27077,13 @@
         </is>
       </c>
       <c r="L224" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="M224" t="n">
-        <v>0</v>
+        <v>5.28</v>
       </c>
       <c r="N224" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="O224" t="n">
         <v>0</v>
@@ -27128,10 +27128,10 @@
         <v>0</v>
       </c>
       <c r="AC224" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD224" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE224" t="n">
         <v>0</v>
@@ -27160,7 +27160,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -27170,12 +27170,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -27196,13 +27196,13 @@
         </is>
       </c>
       <c r="L225" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="M225" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="N225" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="O225" t="n">
         <v>0</v>
@@ -27241,10 +27241,10 @@
         <v>0</v>
       </c>
       <c r="AA225" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB225" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC225" t="n">
         <v>0</v>
@@ -27279,7 +27279,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -27289,12 +27289,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -27315,13 +27315,13 @@
         </is>
       </c>
       <c r="L226" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="M226" t="n">
-        <v>5.28</v>
+        <v>0</v>
       </c>
       <c r="N226" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="O226" t="n">
         <v>0</v>
@@ -27366,10 +27366,10 @@
         <v>0</v>
       </c>
       <c r="AC226" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD226" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE226" t="n">
         <v>0</v>
@@ -27408,12 +27408,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -27636,22 +27636,22 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -27672,13 +27672,13 @@
         </is>
       </c>
       <c r="L229" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="M229" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="N229" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O229" t="n">
         <v>0</v>
@@ -27717,10 +27717,10 @@
         <v>0</v>
       </c>
       <c r="AA229" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB229" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC229" t="n">
         <v>0</v>
@@ -27755,22 +27755,22 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -27874,7 +27874,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -27884,12 +27884,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -27993,22 +27993,22 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -28112,7 +28112,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -28122,12 +28122,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -28241,12 +28241,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -28350,22 +28350,22 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -28469,7 +28469,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -28479,12 +28479,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -28505,13 +28505,13 @@
         </is>
       </c>
       <c r="L236" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="M236" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="N236" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O236" t="n">
         <v>0</v>
@@ -28550,10 +28550,10 @@
         <v>0</v>
       </c>
       <c r="AA236" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB236" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC236" t="n">
         <v>0</v>
@@ -28707,7 +28707,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -28717,12 +28717,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -28743,13 +28743,13 @@
         </is>
       </c>
       <c r="L238" t="n">
-        <v>6.71</v>
+        <v>0</v>
       </c>
       <c r="M238" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="N238" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="O238" t="n">
         <v>0</v>
@@ -28826,7 +28826,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -28836,12 +28836,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -28945,7 +28945,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -28955,12 +28955,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -29064,7 +29064,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -29074,12 +29074,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -29100,13 +29100,13 @@
         </is>
       </c>
       <c r="L241" t="n">
-        <v>0</v>
+        <v>6.71</v>
       </c>
       <c r="M241" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N241" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="O241" t="n">
         <v>0</v>
@@ -29183,7 +29183,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -29193,12 +29193,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -29421,22 +29421,22 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -29540,7 +29540,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -29550,12 +29550,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -29659,22 +29659,22 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -29778,22 +29778,22 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -29814,13 +29814,13 @@
         </is>
       </c>
       <c r="L247" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="M247" t="n">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="N247" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O247" t="n">
         <v>0</v>
@@ -29897,22 +29897,22 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -29933,13 +29933,13 @@
         </is>
       </c>
       <c r="L248" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="M248" t="n">
-        <v>4.01</v>
+        <v>0</v>
       </c>
       <c r="N248" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O248" t="n">
         <v>0</v>
@@ -30016,7 +30016,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -30026,12 +30026,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -30135,7 +30135,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -30145,12 +30145,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -30254,7 +30254,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -30264,12 +30264,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -30290,13 +30290,13 @@
         </is>
       </c>
       <c r="L251" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="M251" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="N251" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="O251" t="n">
         <v>0</v>
@@ -30341,10 +30341,10 @@
         <v>0</v>
       </c>
       <c r="AC251" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD251" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AE251" t="n">
         <v>0</v>
@@ -30373,22 +30373,22 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -30492,7 +30492,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -30502,12 +30502,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -30528,13 +30528,13 @@
         </is>
       </c>
       <c r="L253" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="M253" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="N253" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="O253" t="n">
         <v>0</v>
@@ -30579,10 +30579,10 @@
         <v>0</v>
       </c>
       <c r="AC253" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD253" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AE253" t="n">
         <v>0</v>
@@ -30611,7 +30611,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -30621,12 +30621,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -30730,22 +30730,22 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -30859,12 +30859,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -30885,13 +30885,13 @@
         </is>
       </c>
       <c r="L256" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="M256" t="n">
-        <v>3.25</v>
+        <v>3.42</v>
       </c>
       <c r="N256" t="n">
-        <v>3.24</v>
+        <v>3.4</v>
       </c>
       <c r="O256" t="n">
         <v>0</v>
@@ -30930,10 +30930,10 @@
         <v>0</v>
       </c>
       <c r="AA256" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AB256" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="AC256" t="n">
         <v>0</v>
@@ -30968,7 +30968,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -30978,12 +30978,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -31004,13 +31004,13 @@
         </is>
       </c>
       <c r="L257" t="n">
-        <v>1.75</v>
+        <v>2.3</v>
       </c>
       <c r="M257" t="n">
-        <v>3.74</v>
+        <v>2.88</v>
       </c>
       <c r="N257" t="n">
-        <v>4.94</v>
+        <v>3.4</v>
       </c>
       <c r="O257" t="n">
         <v>0</v>
@@ -31049,10 +31049,10 @@
         <v>0</v>
       </c>
       <c r="AA257" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB257" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC257" t="n">
         <v>0</v>
@@ -31097,12 +31097,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -31123,13 +31123,13 @@
         </is>
       </c>
       <c r="L258" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="M258" t="n">
-        <v>3.42</v>
+        <v>3.25</v>
       </c>
       <c r="N258" t="n">
-        <v>3.4</v>
+        <v>3.24</v>
       </c>
       <c r="O258" t="n">
         <v>0</v>
@@ -31168,10 +31168,10 @@
         <v>0</v>
       </c>
       <c r="AA258" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AB258" t="n">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="AC258" t="n">
         <v>0</v>
@@ -31206,22 +31206,22 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -31242,13 +31242,13 @@
         </is>
       </c>
       <c r="L259" t="n">
-        <v>1.29</v>
+        <v>2</v>
       </c>
       <c r="M259" t="n">
-        <v>5.1</v>
+        <v>2.88</v>
       </c>
       <c r="N259" t="n">
-        <v>10.5</v>
+        <v>4.2</v>
       </c>
       <c r="O259" t="n">
         <v>0</v>
@@ -31287,10 +31287,10 @@
         <v>0</v>
       </c>
       <c r="AA259" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB259" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC259" t="n">
         <v>0</v>
@@ -31325,22 +31325,22 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -31361,13 +31361,13 @@
         </is>
       </c>
       <c r="L260" t="n">
-        <v>2</v>
+        <v>1.29</v>
       </c>
       <c r="M260" t="n">
-        <v>2.88</v>
+        <v>5.1</v>
       </c>
       <c r="N260" t="n">
-        <v>4.2</v>
+        <v>10.5</v>
       </c>
       <c r="O260" t="n">
         <v>0</v>
@@ -31406,10 +31406,10 @@
         <v>0</v>
       </c>
       <c r="AA260" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB260" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC260" t="n">
         <v>0</v>
@@ -31444,7 +31444,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -31454,12 +31454,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Connecticut United</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -31480,13 +31480,13 @@
         </is>
       </c>
       <c r="L261" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M261" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="N261" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O261" t="n">
         <v>0</v>
@@ -31563,7 +31563,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -31573,12 +31573,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Connecticut United</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -31599,13 +31599,13 @@
         </is>
       </c>
       <c r="L262" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M262" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N262" t="n">
-        <v>0</v>
+        <v>4.94</v>
       </c>
       <c r="O262" t="n">
         <v>0</v>
@@ -31644,10 +31644,10 @@
         <v>0</v>
       </c>
       <c r="AA262" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB262" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC262" t="n">
         <v>0</v>
@@ -32039,7 +32039,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -32049,12 +32049,12 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G266" t="n">
@@ -32075,13 +32075,13 @@
         </is>
       </c>
       <c r="L266" t="n">
-        <v>2.67</v>
+        <v>3.79</v>
       </c>
       <c r="M266" t="n">
         <v>3.38</v>
       </c>
       <c r="N266" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="O266" t="n">
         <v>0</v>
@@ -32120,10 +32120,10 @@
         <v>0</v>
       </c>
       <c r="AA266" t="n">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="AB266" t="n">
-        <v>1.95</v>
+        <v>1.57</v>
       </c>
       <c r="AC266" t="n">
         <v>0</v>
@@ -32158,7 +32158,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -32168,12 +32168,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="G267" t="n">
@@ -32194,13 +32194,13 @@
         </is>
       </c>
       <c r="L267" t="n">
-        <v>3.79</v>
+        <v>2.67</v>
       </c>
       <c r="M267" t="n">
         <v>3.38</v>
       </c>
       <c r="N267" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="O267" t="n">
         <v>0</v>
@@ -32239,10 +32239,10 @@
         <v>0</v>
       </c>
       <c r="AA267" t="n">
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="AB267" t="n">
-        <v>1.57</v>
+        <v>1.95</v>
       </c>
       <c r="AC267" t="n">
         <v>0</v>
@@ -32991,7 +32991,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -33001,12 +33001,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G274" t="n">
@@ -33027,13 +33027,13 @@
         </is>
       </c>
       <c r="L274" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M274" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N274" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O274" t="n">
         <v>0</v>
@@ -33110,7 +33110,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -33120,12 +33120,12 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G275" t="n">
@@ -33239,12 +33239,12 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G276" t="n">
@@ -33358,12 +33358,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G277" t="n">
@@ -33467,22 +33467,22 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G278" t="n">
@@ -33586,22 +33586,22 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G279" t="n">
@@ -33622,13 +33622,13 @@
         </is>
       </c>
       <c r="L279" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M279" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N279" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O279" t="n">
         <v>0</v>
@@ -33705,7 +33705,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -33715,12 +33715,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="G280" t="n">
@@ -33824,7 +33824,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -33834,12 +33834,12 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="G281" t="n">
@@ -33860,13 +33860,13 @@
         </is>
       </c>
       <c r="L281" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M281" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="N281" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O281" t="n">
         <v>0</v>
@@ -33943,7 +33943,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -33953,12 +33953,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G282" t="n">
@@ -34062,7 +34062,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -34072,12 +34072,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G283" t="n">
@@ -34098,13 +34098,13 @@
         </is>
       </c>
       <c r="L283" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M283" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="N283" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O283" t="n">
         <v>0</v>
@@ -34181,7 +34181,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -34191,12 +34191,12 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Real Monarchs</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Los Angeles II</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G284" t="n">
@@ -34217,13 +34217,13 @@
         </is>
       </c>
       <c r="L284" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="M284" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="N284" t="n">
-        <v>0</v>
+        <v>6.69</v>
       </c>
       <c r="O284" t="n">
         <v>0</v>
@@ -34262,10 +34262,10 @@
         <v>0</v>
       </c>
       <c r="AA284" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB284" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC284" t="n">
         <v>0</v>
@@ -34300,7 +34300,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -34310,12 +34310,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Real Monarchs</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Los Angeles II</t>
         </is>
       </c>
       <c r="G285" t="n">
@@ -34336,13 +34336,13 @@
         </is>
       </c>
       <c r="L285" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M285" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="N285" t="n">
-        <v>4.84</v>
+        <v>0</v>
       </c>
       <c r="O285" t="n">
         <v>0</v>
@@ -34381,10 +34381,10 @@
         <v>0</v>
       </c>
       <c r="AA285" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB285" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC285" t="n">
         <v>0</v>
@@ -34429,12 +34429,12 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G286" t="n">
@@ -34455,13 +34455,13 @@
         </is>
       </c>
       <c r="L286" t="n">
-        <v>1.51</v>
+        <v>1.83</v>
       </c>
       <c r="M286" t="n">
-        <v>4.32</v>
+        <v>3.46</v>
       </c>
       <c r="N286" t="n">
-        <v>6.69</v>
+        <v>4.84</v>
       </c>
       <c r="O286" t="n">
         <v>0</v>
@@ -34500,10 +34500,10 @@
         <v>0</v>
       </c>
       <c r="AA286" t="n">
-        <v>1.65</v>
+        <v>2.25</v>
       </c>
       <c r="AB286" t="n">
-        <v>2.1</v>
+        <v>1.57</v>
       </c>
       <c r="AC286" t="n">
         <v>0</v>
@@ -34657,7 +34657,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -34667,12 +34667,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Atlanta United II</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="G288" t="n">
@@ -34786,12 +34786,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="G289" t="n">
@@ -34905,12 +34905,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G290" t="n">
@@ -35024,12 +35024,12 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Atlanta United II</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="G291" t="n">
@@ -35133,7 +35133,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -35143,12 +35143,12 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G292" t="n">
@@ -35371,7 +35371,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -35381,12 +35381,12 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G294" t="n">
@@ -35407,13 +35407,13 @@
         </is>
       </c>
       <c r="L294" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M294" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="N294" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="O294" t="n">
         <v>0</v>
@@ -35452,10 +35452,10 @@
         <v>0</v>
       </c>
       <c r="AA294" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB294" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC294" t="n">
         <v>0</v>
@@ -35490,7 +35490,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -35500,12 +35500,12 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G295" t="n">
@@ -35526,13 +35526,13 @@
         </is>
       </c>
       <c r="L295" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M295" t="n">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="N295" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="O295" t="n">
         <v>0</v>
@@ -35571,10 +35571,10 @@
         <v>0</v>
       </c>
       <c r="AA295" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB295" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC295" t="n">
         <v>0</v>
@@ -35609,7 +35609,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -35619,12 +35619,12 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G296" t="n">
@@ -35645,13 +35645,13 @@
         </is>
       </c>
       <c r="L296" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="M296" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N296" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="O296" t="n">
         <v>0</v>
@@ -35690,10 +35690,10 @@
         <v>0</v>
       </c>
       <c r="AA296" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB296" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC296" t="n">
         <v>0</v>
@@ -35728,7 +35728,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -35738,12 +35738,12 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G297" t="n">
@@ -35764,13 +35764,13 @@
         </is>
       </c>
       <c r="L297" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="M297" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N297" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="O297" t="n">
         <v>0</v>
@@ -35809,10 +35809,10 @@
         <v>0</v>
       </c>
       <c r="AA297" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB297" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC297" t="n">
         <v>0</v>

--- a/jogos_2026-03-15.xlsx
+++ b/jogos_2026-03-15.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Marconi Stallions</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Marconi Stallions</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,22 +1932,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Melbourne Victory FC</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Macarthur</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>4.08</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2051,22 +2051,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Melbourne Victory FC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Macarthur</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Port FC</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Port FC</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,22 +4431,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4550,22 +4550,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,22 +4669,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4788,22 +4788,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,22 +5502,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5978,22 +5978,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6692,22 +6692,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6930,22 +6930,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>NorthEast United</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Jamshedpur</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7124,10 +7124,10 @@
         <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z56" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA56" t="n">
         <v>0</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>NorthEast United</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Jamshedpur</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7243,10 +7243,10 @@
         <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z57" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA57" t="n">
         <v>0</v>
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Ayutthaya United</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ayutthaya United</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9191,22 +9191,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9310,22 +9310,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9667,22 +9667,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9905,22 +9905,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Balestier Khalsa</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Home United</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10262,22 +10262,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Balestier Khalsa</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Home United</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10500,22 +10500,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Johor Darul Ta'zim</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="M100" t="n">
-        <v>5.97</v>
+        <v>0</v>
       </c>
       <c r="N100" t="n">
-        <v>10.3</v>
+        <v>0</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="M101" t="n">
-        <v>5.58</v>
+        <v>5.97</v>
       </c>
       <c r="N101" t="n">
-        <v>8.1</v>
+        <v>10.3</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Johor Darul Ta'zim</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="M102" t="n">
-        <v>0</v>
+        <v>5.58</v>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="M104" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N104" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13749,13 +13749,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="M112" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N112" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -13951,7 +13951,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14070,7 +14070,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14463,13 +14463,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M118" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="N118" t="n">
-        <v>0</v>
+        <v>4.77</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -14508,10 +14508,10 @@
         <v>0</v>
       </c>
       <c r="AA118" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB118" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC118" t="n">
         <v>0</v>
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14582,13 +14582,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M119" t="n">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="N119" t="n">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -14627,10 +14627,10 @@
         <v>0</v>
       </c>
       <c r="AA119" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB119" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC119" t="n">
         <v>0</v>
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14701,13 +14701,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M120" t="n">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="N120" t="n">
-        <v>4.77</v>
+        <v>0</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -14746,10 +14746,10 @@
         <v>0</v>
       </c>
       <c r="AA120" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB120" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AC120" t="n">
         <v>0</v>
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14820,13 +14820,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="M121" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="N121" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -14865,10 +14865,10 @@
         <v>0</v>
       </c>
       <c r="AA121" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB121" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC121" t="n">
         <v>0</v>
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Inter Kashi</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Mumbai City</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15058,13 +15058,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M123" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="N123" t="n">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -15103,10 +15103,10 @@
         <v>0</v>
       </c>
       <c r="AA123" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB123" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC123" t="n">
         <v>0</v>
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15177,13 +15177,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>2.96</v>
+        <v>2.19</v>
       </c>
       <c r="M124" t="n">
-        <v>3.4</v>
+        <v>3.58</v>
       </c>
       <c r="N124" t="n">
-        <v>2.61</v>
+        <v>3.58</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -15222,10 +15222,10 @@
         <v>0</v>
       </c>
       <c r="AA124" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AB124" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AC124" t="n">
         <v>0</v>
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15296,13 +15296,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="M125" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="N125" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -15341,10 +15341,10 @@
         <v>0</v>
       </c>
       <c r="AA125" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB125" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC125" t="n">
         <v>0</v>
@@ -15379,22 +15379,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Inter Kashi</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Mumbai City</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15534,13 +15534,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="M127" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="N127" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -15579,10 +15579,10 @@
         <v>0</v>
       </c>
       <c r="AA127" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB127" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC127" t="n">
         <v>0</v>
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15736,22 +15736,22 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15772,13 +15772,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="M129" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="N129" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -15817,10 +15817,10 @@
         <v>0</v>
       </c>
       <c r="AA129" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB129" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC129" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="M130" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N130" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -15936,10 +15936,10 @@
         <v>0</v>
       </c>
       <c r="AA130" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB130" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC130" t="n">
         <v>0</v>
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16129,13 +16129,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="M132" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="N132" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -16174,10 +16174,10 @@
         <v>0</v>
       </c>
       <c r="AA132" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB132" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC132" t="n">
         <v>0</v>
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16450,7 +16450,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16486,13 +16486,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>2.29</v>
+        <v>2.64</v>
       </c>
       <c r="M135" t="n">
-        <v>3.62</v>
+        <v>3.38</v>
       </c>
       <c r="N135" t="n">
-        <v>3.31</v>
+        <v>2.52</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -16531,10 +16531,10 @@
         <v>0</v>
       </c>
       <c r="AA135" t="n">
-        <v>1.79</v>
+        <v>2.03</v>
       </c>
       <c r="AB135" t="n">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="AC135" t="n">
         <v>0</v>
@@ -16926,22 +16926,22 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Lajense</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -17045,7 +17045,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -17174,12 +17174,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Eléctrico</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -17283,22 +17283,22 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17402,7 +17402,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17640,7 +17640,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17759,7 +17759,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17878,7 +17878,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -17997,7 +17997,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -18007,12 +18007,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Eléctrico</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -18116,7 +18116,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18235,7 +18235,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -18245,12 +18245,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>Machico</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -18354,7 +18354,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -18364,12 +18364,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>AR São Martinho</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -18483,12 +18483,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -18592,7 +18592,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -18602,12 +18602,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -18711,7 +18711,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -18721,12 +18721,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Gouveia</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -18840,12 +18840,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Monção</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -18959,12 +18959,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>AR São Martinho</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -19078,12 +19078,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Chaves II</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Monção</t>
+          <t>Mirandela</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -19187,7 +19187,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Chaves II</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Mirandela</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -19306,22 +19306,22 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -19425,22 +19425,22 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19554,12 +19554,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -19673,12 +19673,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -19792,12 +19792,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -19911,12 +19911,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Clube Oriental de Lisboa</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -20020,7 +20020,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -20030,12 +20030,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Machico</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -20258,7 +20258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -20268,12 +20268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -20377,7 +20377,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -20387,12 +20387,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -20496,7 +20496,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -20506,12 +20506,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -20625,12 +20625,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -20734,7 +20734,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -20744,12 +20744,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -20853,7 +20853,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -20863,12 +20863,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -20972,22 +20972,22 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Clube Oriental de Lisboa</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -21091,22 +21091,22 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -21210,7 +21210,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -21220,12 +21220,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -21329,22 +21329,22 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -21448,7 +21448,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -21458,12 +21458,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -21567,7 +21567,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -21577,12 +21577,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -21686,22 +21686,22 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -21805,7 +21805,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -21815,12 +21815,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -21924,7 +21924,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -21934,12 +21934,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -22053,12 +22053,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -22162,7 +22162,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -22172,12 +22172,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -22281,7 +22281,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -22291,12 +22291,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -22317,13 +22317,13 @@
         </is>
       </c>
       <c r="L184" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="M184" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="N184" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="O184" t="n">
         <v>0</v>
@@ -22400,7 +22400,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -22410,12 +22410,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -22436,13 +22436,13 @@
         </is>
       </c>
       <c r="L185" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="M185" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="N185" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="O185" t="n">
         <v>0</v>
@@ -22529,12 +22529,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -22757,7 +22757,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -22767,12 +22767,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -22995,7 +22995,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -23005,12 +23005,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -23027,7 +23027,7 @@
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L190" t="n">
@@ -23124,12 +23124,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -23233,7 +23233,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -23243,12 +23243,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -23265,7 +23265,7 @@
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L192" t="n">
@@ -23471,7 +23471,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -23481,12 +23481,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -23503,7 +23503,7 @@
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L194" t="n">
@@ -23590,7 +23590,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -23600,12 +23600,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -23622,7 +23622,7 @@
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L195" t="n">
@@ -23828,7 +23828,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -23838,12 +23838,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -23947,7 +23947,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -23957,12 +23957,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -24066,7 +24066,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -24076,12 +24076,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -24185,7 +24185,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -24195,12 +24195,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -24221,13 +24221,13 @@
         </is>
       </c>
       <c r="L200" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="M200" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="N200" t="n">
-        <v>7.19</v>
+        <v>0</v>
       </c>
       <c r="O200" t="n">
         <v>0</v>
@@ -24304,7 +24304,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -24314,12 +24314,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -24423,7 +24423,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -24433,12 +24433,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -24459,13 +24459,13 @@
         </is>
       </c>
       <c r="L202" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="M202" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="N202" t="n">
-        <v>0</v>
+        <v>7.19</v>
       </c>
       <c r="O202" t="n">
         <v>0</v>
@@ -24542,7 +24542,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -24552,12 +24552,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -24661,7 +24661,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -24671,12 +24671,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -24790,12 +24790,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -24899,22 +24899,22 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -24935,13 +24935,13 @@
         </is>
       </c>
       <c r="L206" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="M206" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="N206" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O206" t="n">
         <v>0</v>
@@ -25137,22 +25137,22 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -25173,13 +25173,13 @@
         </is>
       </c>
       <c r="L208" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="M208" t="n">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="N208" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="O208" t="n">
         <v>0</v>
@@ -25256,22 +25256,22 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -25292,13 +25292,13 @@
         </is>
       </c>
       <c r="L209" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M209" t="n">
-        <v>4.19</v>
+        <v>0</v>
       </c>
       <c r="N209" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="O209" t="n">
         <v>0</v>
@@ -25343,10 +25343,10 @@
         <v>0</v>
       </c>
       <c r="AC209" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD209" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE209" t="n">
         <v>0</v>
@@ -25375,22 +25375,22 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -25411,13 +25411,13 @@
         </is>
       </c>
       <c r="L210" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M210" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N210" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O210" t="n">
         <v>0</v>
@@ -25494,22 +25494,22 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -25530,13 +25530,13 @@
         </is>
       </c>
       <c r="L211" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M211" t="n">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="N211" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="O211" t="n">
         <v>0</v>
@@ -25581,10 +25581,10 @@
         <v>0</v>
       </c>
       <c r="AC211" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD211" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE211" t="n">
         <v>0</v>
@@ -25613,22 +25613,22 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -25649,13 +25649,13 @@
         </is>
       </c>
       <c r="L212" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M212" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N212" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O212" t="n">
         <v>0</v>
@@ -25732,7 +25732,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -25742,12 +25742,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -26208,7 +26208,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -26218,12 +26218,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -26327,7 +26327,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -26337,12 +26337,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -26446,7 +26446,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -26456,12 +26456,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -26565,7 +26565,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -26575,12 +26575,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -26684,7 +26684,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -26694,12 +26694,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -26720,13 +26720,13 @@
         </is>
       </c>
       <c r="L221" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="M221" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="N221" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="O221" t="n">
         <v>0</v>
@@ -26765,10 +26765,10 @@
         <v>0</v>
       </c>
       <c r="AA221" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB221" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC221" t="n">
         <v>0</v>
@@ -26803,7 +26803,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -26813,12 +26813,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -26922,7 +26922,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -26932,12 +26932,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -27041,7 +27041,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -27051,12 +27051,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -27077,13 +27077,13 @@
         </is>
       </c>
       <c r="L224" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="M224" t="n">
-        <v>5.28</v>
+        <v>0</v>
       </c>
       <c r="N224" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="O224" t="n">
         <v>0</v>
@@ -27128,10 +27128,10 @@
         <v>0</v>
       </c>
       <c r="AC224" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD224" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE224" t="n">
         <v>0</v>
@@ -27160,7 +27160,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -27170,12 +27170,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -27196,13 +27196,13 @@
         </is>
       </c>
       <c r="L225" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="M225" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="N225" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="O225" t="n">
         <v>0</v>
@@ -27241,10 +27241,10 @@
         <v>0</v>
       </c>
       <c r="AA225" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB225" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AC225" t="n">
         <v>0</v>
@@ -27279,7 +27279,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -27289,12 +27289,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -27315,13 +27315,13 @@
         </is>
       </c>
       <c r="L226" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="M226" t="n">
-        <v>0</v>
+        <v>5.28</v>
       </c>
       <c r="N226" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="O226" t="n">
         <v>0</v>
@@ -27366,10 +27366,10 @@
         <v>0</v>
       </c>
       <c r="AC226" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD226" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE226" t="n">
         <v>0</v>
@@ -27398,7 +27398,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -27408,12 +27408,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -27636,7 +27636,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -27646,12 +27646,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -27672,13 +27672,13 @@
         </is>
       </c>
       <c r="L229" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="M229" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="N229" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O229" t="n">
         <v>0</v>
@@ -27717,10 +27717,10 @@
         <v>0</v>
       </c>
       <c r="AA229" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB229" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC229" t="n">
         <v>0</v>
@@ -28112,7 +28112,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -28122,12 +28122,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -28231,7 +28231,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -28241,12 +28241,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -28350,7 +28350,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -28360,12 +28360,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -28469,7 +28469,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -28479,12 +28479,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -28505,13 +28505,13 @@
         </is>
       </c>
       <c r="L236" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="M236" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="N236" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O236" t="n">
         <v>0</v>
@@ -28550,10 +28550,10 @@
         <v>0</v>
       </c>
       <c r="AA236" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB236" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC236" t="n">
         <v>0</v>
@@ -28707,7 +28707,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -28717,12 +28717,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -28743,13 +28743,13 @@
         </is>
       </c>
       <c r="L238" t="n">
-        <v>0</v>
+        <v>6.71</v>
       </c>
       <c r="M238" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N238" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="O238" t="n">
         <v>0</v>
@@ -28826,7 +28826,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -28836,12 +28836,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -28945,7 +28945,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -28955,12 +28955,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -29064,7 +29064,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -29074,12 +29074,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -29100,13 +29100,13 @@
         </is>
       </c>
       <c r="L241" t="n">
-        <v>6.71</v>
+        <v>0</v>
       </c>
       <c r="M241" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="N241" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="O241" t="n">
         <v>0</v>
@@ -29302,7 +29302,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -29312,12 +29312,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -29778,22 +29778,22 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -29814,13 +29814,13 @@
         </is>
       </c>
       <c r="L247" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="M247" t="n">
-        <v>4.01</v>
+        <v>0</v>
       </c>
       <c r="N247" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O247" t="n">
         <v>0</v>
@@ -29897,22 +29897,22 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -29933,13 +29933,13 @@
         </is>
       </c>
       <c r="L248" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="M248" t="n">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="N248" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O248" t="n">
         <v>0</v>
@@ -30016,7 +30016,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -30026,12 +30026,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -30135,22 +30135,22 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -30373,22 +30373,22 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -30492,7 +30492,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -30502,12 +30502,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -30611,7 +30611,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -30621,12 +30621,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -30730,7 +30730,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -30740,12 +30740,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -30859,12 +30859,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -30885,13 +30885,13 @@
         </is>
       </c>
       <c r="L256" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="M256" t="n">
-        <v>3.42</v>
+        <v>3.25</v>
       </c>
       <c r="N256" t="n">
-        <v>3.4</v>
+        <v>3.24</v>
       </c>
       <c r="O256" t="n">
         <v>0</v>
@@ -30930,10 +30930,10 @@
         <v>0</v>
       </c>
       <c r="AA256" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AB256" t="n">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="AC256" t="n">
         <v>0</v>
@@ -30968,7 +30968,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -30978,12 +30978,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Connecticut United</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -31004,13 +31004,13 @@
         </is>
       </c>
       <c r="L257" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M257" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="N257" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O257" t="n">
         <v>0</v>
@@ -31087,22 +31087,22 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -31123,13 +31123,13 @@
         </is>
       </c>
       <c r="L258" t="n">
-        <v>2.35</v>
+        <v>1.29</v>
       </c>
       <c r="M258" t="n">
-        <v>3.25</v>
+        <v>5.1</v>
       </c>
       <c r="N258" t="n">
-        <v>3.24</v>
+        <v>10.5</v>
       </c>
       <c r="O258" t="n">
         <v>0</v>
@@ -31168,10 +31168,10 @@
         <v>0</v>
       </c>
       <c r="AA258" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AB258" t="n">
-        <v>1.63</v>
+        <v>1.98</v>
       </c>
       <c r="AC258" t="n">
         <v>0</v>
@@ -31206,7 +31206,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -31216,12 +31216,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -31242,13 +31242,13 @@
         </is>
       </c>
       <c r="L259" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M259" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="N259" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O259" t="n">
         <v>0</v>
@@ -31325,22 +31325,22 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -31361,13 +31361,13 @@
         </is>
       </c>
       <c r="L260" t="n">
-        <v>1.29</v>
+        <v>2</v>
       </c>
       <c r="M260" t="n">
-        <v>5.1</v>
+        <v>2.88</v>
       </c>
       <c r="N260" t="n">
-        <v>10.5</v>
+        <v>4.2</v>
       </c>
       <c r="O260" t="n">
         <v>0</v>
@@ -31406,10 +31406,10 @@
         <v>0</v>
       </c>
       <c r="AA260" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB260" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC260" t="n">
         <v>0</v>
@@ -31444,7 +31444,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -31454,12 +31454,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Connecticut United</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -31480,13 +31480,13 @@
         </is>
       </c>
       <c r="L261" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M261" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="N261" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O261" t="n">
         <v>0</v>
@@ -31573,12 +31573,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -31599,13 +31599,13 @@
         </is>
       </c>
       <c r="L262" t="n">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="M262" t="n">
-        <v>3.74</v>
+        <v>3.42</v>
       </c>
       <c r="N262" t="n">
-        <v>4.94</v>
+        <v>3.4</v>
       </c>
       <c r="O262" t="n">
         <v>0</v>
@@ -31644,10 +31644,10 @@
         <v>0</v>
       </c>
       <c r="AA262" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AB262" t="n">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="AC262" t="n">
         <v>0</v>
@@ -31682,7 +31682,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -31692,12 +31692,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -31718,13 +31718,13 @@
         </is>
       </c>
       <c r="L263" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M263" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N263" t="n">
-        <v>0</v>
+        <v>4.94</v>
       </c>
       <c r="O263" t="n">
         <v>0</v>
@@ -31763,10 +31763,10 @@
         <v>0</v>
       </c>
       <c r="AA263" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB263" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC263" t="n">
         <v>0</v>
@@ -32039,7 +32039,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -32049,12 +32049,12 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="G266" t="n">
@@ -32075,13 +32075,13 @@
         </is>
       </c>
       <c r="L266" t="n">
-        <v>3.79</v>
+        <v>2.67</v>
       </c>
       <c r="M266" t="n">
         <v>3.38</v>
       </c>
       <c r="N266" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="O266" t="n">
         <v>0</v>
@@ -32120,10 +32120,10 @@
         <v>0</v>
       </c>
       <c r="AA266" t="n">
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="AB266" t="n">
-        <v>1.57</v>
+        <v>1.95</v>
       </c>
       <c r="AC266" t="n">
         <v>0</v>
@@ -32158,7 +32158,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -32168,12 +32168,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G267" t="n">
@@ -32194,13 +32194,13 @@
         </is>
       </c>
       <c r="L267" t="n">
-        <v>2.67</v>
+        <v>3.79</v>
       </c>
       <c r="M267" t="n">
         <v>3.38</v>
       </c>
       <c r="N267" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="O267" t="n">
         <v>0</v>
@@ -32239,10 +32239,10 @@
         <v>0</v>
       </c>
       <c r="AA267" t="n">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="AB267" t="n">
-        <v>1.95</v>
+        <v>1.57</v>
       </c>
       <c r="AC267" t="n">
         <v>0</v>
@@ -32277,22 +32277,22 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G268" t="n">
@@ -32313,13 +32313,13 @@
         </is>
       </c>
       <c r="L268" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M268" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N268" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="O268" t="n">
         <v>0</v>
@@ -32396,22 +32396,22 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G269" t="n">
@@ -32515,7 +32515,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -32525,12 +32525,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G270" t="n">
@@ -32634,22 +32634,22 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="G271" t="n">
@@ -32753,22 +32753,22 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G272" t="n">
@@ -32789,13 +32789,13 @@
         </is>
       </c>
       <c r="L272" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M272" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N272" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="O272" t="n">
         <v>0</v>
@@ -33110,22 +33110,22 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G275" t="n">
@@ -33146,13 +33146,13 @@
         </is>
       </c>
       <c r="L275" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M275" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N275" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O275" t="n">
         <v>0</v>
@@ -33239,12 +33239,12 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G276" t="n">
@@ -33477,12 +33477,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G278" t="n">
@@ -33586,22 +33586,22 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="G279" t="n">
@@ -33622,13 +33622,13 @@
         </is>
       </c>
       <c r="L279" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M279" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N279" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O279" t="n">
         <v>0</v>
@@ -33705,7 +33705,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -33715,12 +33715,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G280" t="n">
@@ -34538,7 +34538,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -34548,12 +34548,12 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G287" t="n">
@@ -34776,7 +34776,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -34786,12 +34786,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G289" t="n">
@@ -34905,12 +34905,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="G290" t="n">
@@ -35381,12 +35381,12 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G294" t="n">
@@ -35407,13 +35407,13 @@
         </is>
       </c>
       <c r="L294" t="n">
-        <v>1.7</v>
+        <v>2.61</v>
       </c>
       <c r="M294" t="n">
-        <v>3.79</v>
+        <v>3.23</v>
       </c>
       <c r="N294" t="n">
-        <v>5.3</v>
+        <v>2.86</v>
       </c>
       <c r="O294" t="n">
         <v>0</v>
@@ -35452,10 +35452,10 @@
         <v>0</v>
       </c>
       <c r="AA294" t="n">
-        <v>1.93</v>
+        <v>2.3</v>
       </c>
       <c r="AB294" t="n">
-        <v>1.75</v>
+        <v>1.55</v>
       </c>
       <c r="AC294" t="n">
         <v>0</v>
@@ -35490,7 +35490,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -35500,12 +35500,12 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G295" t="n">
@@ -35526,13 +35526,13 @@
         </is>
       </c>
       <c r="L295" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M295" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="N295" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="O295" t="n">
         <v>0</v>
@@ -35571,10 +35571,10 @@
         <v>0</v>
       </c>
       <c r="AA295" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB295" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC295" t="n">
         <v>0</v>
@@ -35728,7 +35728,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -35738,12 +35738,12 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G297" t="n">
@@ -35764,13 +35764,13 @@
         </is>
       </c>
       <c r="L297" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="M297" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N297" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="O297" t="n">
         <v>0</v>
@@ -35809,10 +35809,10 @@
         <v>0</v>
       </c>
       <c r="AA297" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB297" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC297" t="n">
         <v>0</v>

--- a/jogos_2026-03-15.xlsx
+++ b/jogos_2026-03-15.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Marconi Stallions</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Marconi Stallions</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,22 +1932,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Melbourne Victory FC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Macarthur</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2051,22 +2051,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Melbourne Victory FC</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Macarthur</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>4.08</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Port FC</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,22 +4193,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,22 +4431,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Port FC</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,22 +5502,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5740,22 +5740,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5978,22 +5978,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>4.48</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>6.17</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>4.48</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>6.17</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6692,22 +6692,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6930,22 +6930,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ayutthaya United</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Ayutthaya United</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9548,22 +9548,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10262,22 +10262,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10381,22 +10381,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10500,22 +10500,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M97" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>4.59</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Johor Darul Ta'zim</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Johor Darul Ta'zim</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="M101" t="n">
-        <v>5.97</v>
+        <v>0</v>
       </c>
       <c r="N101" t="n">
-        <v>10.3</v>
+        <v>0</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12523,22 +12523,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>1.35</v>
+        <v>4.3</v>
       </c>
       <c r="M102" t="n">
-        <v>5.58</v>
+        <v>3.94</v>
       </c>
       <c r="N102" t="n">
-        <v>8.1</v>
+        <v>1.78</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="M104" t="n">
-        <v>0</v>
+        <v>5.58</v>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13356,22 +13356,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13392,13 +13392,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="M109" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="N109" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13630,13 +13630,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="M111" t="n">
-        <v>0</v>
+        <v>5.97</v>
       </c>
       <c r="N111" t="n">
-        <v>0</v>
+        <v>10.3</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -13951,7 +13951,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14070,7 +14070,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14106,13 +14106,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M115" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="N115" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -14151,10 +14151,10 @@
         <v>0</v>
       </c>
       <c r="AA115" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB115" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC115" t="n">
         <v>0</v>
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M116" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="N116" t="n">
-        <v>0</v>
+        <v>4.77</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -14270,10 +14270,10 @@
         <v>0</v>
       </c>
       <c r="AA116" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB116" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC116" t="n">
         <v>0</v>
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14463,13 +14463,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="M118" t="n">
-        <v>4.06</v>
+        <v>4.17</v>
       </c>
       <c r="N118" t="n">
-        <v>4.77</v>
+        <v>4.27</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -14508,10 +14508,10 @@
         <v>0</v>
       </c>
       <c r="AA118" t="n">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AB118" t="n">
-        <v>1.97</v>
+        <v>2.15</v>
       </c>
       <c r="AC118" t="n">
         <v>0</v>
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14582,13 +14582,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="M119" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="N119" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -14627,10 +14627,10 @@
         <v>0</v>
       </c>
       <c r="AA119" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB119" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC119" t="n">
         <v>0</v>
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15058,13 +15058,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M123" t="n">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="N123" t="n">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -15103,10 +15103,10 @@
         <v>0</v>
       </c>
       <c r="AA123" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB123" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC123" t="n">
         <v>0</v>
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15177,13 +15177,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="M124" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="N124" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -15222,10 +15222,10 @@
         <v>0</v>
       </c>
       <c r="AA124" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB124" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC124" t="n">
         <v>0</v>
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15296,13 +15296,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="M125" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="N125" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -15341,10 +15341,10 @@
         <v>0</v>
       </c>
       <c r="AA125" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB125" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC125" t="n">
         <v>0</v>
@@ -15379,22 +15379,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Inter Kashi</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Mumbai City</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15534,13 +15534,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>2.48</v>
+        <v>2.64</v>
       </c>
       <c r="M127" t="n">
-        <v>3.29</v>
+        <v>3.38</v>
       </c>
       <c r="N127" t="n">
-        <v>3.25</v>
+        <v>2.52</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -15579,10 +15579,10 @@
         <v>0</v>
       </c>
       <c r="AA127" t="n">
-        <v>2.3</v>
+        <v>2.03</v>
       </c>
       <c r="AB127" t="n">
-        <v>1.55</v>
+        <v>1.83</v>
       </c>
       <c r="AC127" t="n">
         <v>0</v>
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15653,13 +15653,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="M128" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="N128" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -15698,10 +15698,10 @@
         <v>0</v>
       </c>
       <c r="AA128" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB128" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC128" t="n">
         <v>0</v>
@@ -15736,22 +15736,22 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15772,13 +15772,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M129" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="N129" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -15817,10 +15817,10 @@
         <v>0</v>
       </c>
       <c r="AA129" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB129" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC129" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>2.96</v>
+        <v>3.51</v>
       </c>
       <c r="M130" t="n">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="N130" t="n">
-        <v>2.61</v>
+        <v>2.03</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -15936,10 +15936,10 @@
         <v>0</v>
       </c>
       <c r="AA130" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB130" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC130" t="n">
         <v>0</v>
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Inter Kashi</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Mumbai City</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16367,13 +16367,13 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="M134" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N134" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -16412,10 +16412,10 @@
         <v>0</v>
       </c>
       <c r="AA134" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB134" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC134" t="n">
         <v>0</v>
@@ -16450,7 +16450,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16486,13 +16486,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="M135" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="N135" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -16531,10 +16531,10 @@
         <v>0</v>
       </c>
       <c r="AA135" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB135" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC135" t="n">
         <v>0</v>
@@ -16569,7 +16569,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16605,13 +16605,13 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="M136" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N136" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="O136" t="n">
         <v>0</v>
@@ -16650,10 +16650,10 @@
         <v>0</v>
       </c>
       <c r="AA136" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB136" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC136" t="n">
         <v>0</v>
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16843,13 +16843,13 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="M138" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N138" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -16888,10 +16888,10 @@
         <v>0</v>
       </c>
       <c r="AA138" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB138" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC138" t="n">
         <v>0</v>
@@ -16926,7 +16926,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -17045,22 +17045,22 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -17174,12 +17174,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -17283,22 +17283,22 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17319,13 +17319,13 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="M142" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N142" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O142" t="n">
         <v>0</v>
@@ -17402,22 +17402,22 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17521,7 +17521,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17759,22 +17759,22 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17878,7 +17878,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -17997,7 +17997,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -18007,12 +18007,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Eléctrico</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -18116,7 +18116,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18235,7 +18235,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -18245,12 +18245,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Machico</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -18354,7 +18354,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -18364,12 +18364,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -18473,7 +18473,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -18483,12 +18483,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Gouveia</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -18592,7 +18592,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -18602,12 +18602,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Clube Oriental de Lisboa</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -18711,7 +18711,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -18721,12 +18721,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -18830,7 +18830,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -18840,12 +18840,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Monção</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -18949,7 +18949,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -18959,12 +18959,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>AR São Martinho</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -19068,7 +19068,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -19078,12 +19078,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Chaves II</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Mirandela</t>
+          <t>Lajense</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -19187,7 +19187,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -19306,7 +19306,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -19316,12 +19316,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -19425,22 +19425,22 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Eléctrico</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19544,22 +19544,22 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -19663,22 +19663,22 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -19792,12 +19792,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -19901,7 +19901,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -19911,12 +19911,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -20020,7 +20020,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -20030,12 +20030,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -20139,7 +20139,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -20149,12 +20149,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -20258,7 +20258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -20268,12 +20268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -20377,7 +20377,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -20387,12 +20387,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -20496,7 +20496,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -20506,12 +20506,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -20615,7 +20615,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -20625,12 +20625,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Monção</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -20734,7 +20734,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -20744,12 +20744,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>AR São Martinho</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -20853,7 +20853,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -20863,12 +20863,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Machico</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -20972,7 +20972,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -20982,12 +20982,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>Chaves II</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Clube Oriental de Lisboa</t>
+          <t>Mirandela</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -21091,22 +21091,22 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -21210,22 +21210,22 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -21329,22 +21329,22 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -21448,22 +21448,22 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -21567,7 +21567,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -21577,12 +21577,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -21686,22 +21686,22 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -21805,7 +21805,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -21815,12 +21815,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -21924,7 +21924,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -21934,12 +21934,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -22162,7 +22162,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -22172,12 +22172,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -22281,7 +22281,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -22291,12 +22291,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -22317,13 +22317,13 @@
         </is>
       </c>
       <c r="L184" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="M184" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="N184" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="O184" t="n">
         <v>0</v>
@@ -22400,7 +22400,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -22410,12 +22410,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -22519,7 +22519,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -22529,12 +22529,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -22555,13 +22555,13 @@
         </is>
       </c>
       <c r="L186" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="M186" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="N186" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="O186" t="n">
         <v>0</v>
@@ -22638,7 +22638,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -22648,12 +22648,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -22670,7 +22670,7 @@
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L187" t="n">
@@ -22757,7 +22757,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -22767,12 +22767,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -22789,7 +22789,7 @@
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L188" t="n">
@@ -22876,7 +22876,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -22886,12 +22886,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -22912,13 +22912,13 @@
         </is>
       </c>
       <c r="L189" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="M189" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N189" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O189" t="n">
         <v>0</v>
@@ -22957,10 +22957,10 @@
         <v>0</v>
       </c>
       <c r="AA189" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB189" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC189" t="n">
         <v>0</v>
@@ -23005,12 +23005,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -23124,12 +23124,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -23233,7 +23233,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -23243,12 +23243,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -23265,7 +23265,7 @@
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L192" t="n">
@@ -23352,7 +23352,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -23362,12 +23362,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -23384,17 +23384,17 @@
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L193" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="M193" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N193" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O193" t="n">
         <v>0</v>
@@ -23433,10 +23433,10 @@
         <v>0</v>
       </c>
       <c r="AA193" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB193" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC193" t="n">
         <v>0</v>
@@ -23471,7 +23471,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -23481,12 +23481,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -23590,7 +23590,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -23600,12 +23600,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -23622,7 +23622,7 @@
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L195" t="n">
@@ -23709,7 +23709,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -23719,12 +23719,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -23745,13 +23745,13 @@
         </is>
       </c>
       <c r="L196" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="M196" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="N196" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O196" t="n">
         <v>0</v>
@@ -23828,7 +23828,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -23838,12 +23838,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -23947,7 +23947,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -23957,12 +23957,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -23979,7 +23979,7 @@
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L198" t="n">
@@ -24066,7 +24066,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -24076,12 +24076,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -24185,7 +24185,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -24195,12 +24195,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -24221,13 +24221,13 @@
         </is>
       </c>
       <c r="L200" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="M200" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="N200" t="n">
-        <v>0</v>
+        <v>7.19</v>
       </c>
       <c r="O200" t="n">
         <v>0</v>
@@ -24314,12 +24314,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -24423,7 +24423,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -24433,12 +24433,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -24459,13 +24459,13 @@
         </is>
       </c>
       <c r="L202" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="M202" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="N202" t="n">
-        <v>7.19</v>
+        <v>0</v>
       </c>
       <c r="O202" t="n">
         <v>0</v>
@@ -24542,7 +24542,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -24552,12 +24552,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -24671,12 +24671,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -24780,22 +24780,22 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -24816,13 +24816,13 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M205" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N205" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O205" t="n">
         <v>0</v>
@@ -24899,22 +24899,22 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -24935,13 +24935,13 @@
         </is>
       </c>
       <c r="L206" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="M206" t="n">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="N206" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="O206" t="n">
         <v>0</v>
@@ -25018,7 +25018,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -25028,12 +25028,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -25137,22 +25137,22 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -25173,13 +25173,13 @@
         </is>
       </c>
       <c r="L208" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M208" t="n">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="N208" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="O208" t="n">
         <v>0</v>
@@ -25224,10 +25224,10 @@
         <v>0</v>
       </c>
       <c r="AC208" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD208" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE208" t="n">
         <v>0</v>
@@ -25256,7 +25256,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -25266,12 +25266,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -25375,22 +25375,22 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -25411,13 +25411,13 @@
         </is>
       </c>
       <c r="L210" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M210" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N210" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O210" t="n">
         <v>0</v>
@@ -25494,22 +25494,22 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -25530,13 +25530,13 @@
         </is>
       </c>
       <c r="L211" t="n">
-        <v>1.86</v>
+        <v>3.16</v>
       </c>
       <c r="M211" t="n">
-        <v>4.19</v>
+        <v>3.44</v>
       </c>
       <c r="N211" t="n">
-        <v>3.68</v>
+        <v>2.45</v>
       </c>
       <c r="O211" t="n">
         <v>0</v>
@@ -25581,10 +25581,10 @@
         <v>0</v>
       </c>
       <c r="AC211" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD211" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE211" t="n">
         <v>0</v>
@@ -25613,7 +25613,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -25623,12 +25623,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -25732,22 +25732,22 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -25768,13 +25768,13 @@
         </is>
       </c>
       <c r="L213" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="M213" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="N213" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O213" t="n">
         <v>0</v>
@@ -26208,7 +26208,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -26218,12 +26218,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -26327,7 +26327,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -26337,12 +26337,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -26456,12 +26456,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -26684,7 +26684,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -26694,12 +26694,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -26720,13 +26720,13 @@
         </is>
       </c>
       <c r="L221" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="M221" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="N221" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="O221" t="n">
         <v>0</v>
@@ -26765,10 +26765,10 @@
         <v>0</v>
       </c>
       <c r="AA221" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB221" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AC221" t="n">
         <v>0</v>
@@ -26803,7 +26803,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -26813,12 +26813,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -26922,7 +26922,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -26932,12 +26932,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -27041,7 +27041,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -27051,12 +27051,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -27160,7 +27160,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -27170,12 +27170,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -27196,13 +27196,13 @@
         </is>
       </c>
       <c r="L225" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="M225" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="N225" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="O225" t="n">
         <v>0</v>
@@ -27241,10 +27241,10 @@
         <v>0</v>
       </c>
       <c r="AA225" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB225" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC225" t="n">
         <v>0</v>
@@ -27398,7 +27398,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -27408,12 +27408,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -27636,22 +27636,22 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -27755,22 +27755,22 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -27874,7 +27874,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -27884,12 +27884,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -27993,22 +27993,22 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -28029,13 +28029,13 @@
         </is>
       </c>
       <c r="L232" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="M232" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="N232" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O232" t="n">
         <v>0</v>
@@ -28074,10 +28074,10 @@
         <v>0</v>
       </c>
       <c r="AA232" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB232" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC232" t="n">
         <v>0</v>
@@ -28112,7 +28112,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -28122,12 +28122,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -28231,7 +28231,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -28241,12 +28241,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -28350,22 +28350,22 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -28469,7 +28469,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -28479,12 +28479,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -28505,13 +28505,13 @@
         </is>
       </c>
       <c r="L236" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="M236" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="N236" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O236" t="n">
         <v>0</v>
@@ -28550,10 +28550,10 @@
         <v>0</v>
       </c>
       <c r="AA236" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB236" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC236" t="n">
         <v>0</v>
@@ -28707,7 +28707,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -28717,12 +28717,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -28743,13 +28743,13 @@
         </is>
       </c>
       <c r="L238" t="n">
-        <v>6.71</v>
+        <v>0</v>
       </c>
       <c r="M238" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="N238" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="O238" t="n">
         <v>0</v>
@@ -28826,7 +28826,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -28836,12 +28836,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -28945,7 +28945,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -28955,12 +28955,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -29183,7 +29183,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -29193,12 +29193,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -29219,13 +29219,13 @@
         </is>
       </c>
       <c r="L242" t="n">
-        <v>0</v>
+        <v>6.71</v>
       </c>
       <c r="M242" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N242" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="O242" t="n">
         <v>0</v>
@@ -29421,22 +29421,22 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -29659,22 +29659,22 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -30016,7 +30016,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -30026,12 +30026,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -30135,22 +30135,22 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -30171,13 +30171,13 @@
         </is>
       </c>
       <c r="L250" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="M250" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="N250" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="O250" t="n">
         <v>0</v>
@@ -30222,10 +30222,10 @@
         <v>0</v>
       </c>
       <c r="AC250" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD250" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AE250" t="n">
         <v>0</v>
@@ -30254,7 +30254,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -30264,12 +30264,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -30290,13 +30290,13 @@
         </is>
       </c>
       <c r="L251" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="M251" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="N251" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="O251" t="n">
         <v>0</v>
@@ -30341,10 +30341,10 @@
         <v>0</v>
       </c>
       <c r="AC251" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD251" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AE251" t="n">
         <v>0</v>
@@ -30373,22 +30373,22 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -30492,7 +30492,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -30502,12 +30502,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -30730,7 +30730,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -30740,12 +30740,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -30968,7 +30968,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -30978,12 +30978,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Connecticut United</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -31004,13 +31004,13 @@
         </is>
       </c>
       <c r="L257" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M257" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="N257" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O257" t="n">
         <v>0</v>
@@ -31049,10 +31049,10 @@
         <v>0</v>
       </c>
       <c r="AA257" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB257" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC257" t="n">
         <v>0</v>
@@ -31087,22 +31087,22 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Connecticut United</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -31123,13 +31123,13 @@
         </is>
       </c>
       <c r="L258" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="M258" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="N258" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="O258" t="n">
         <v>0</v>
@@ -31168,10 +31168,10 @@
         <v>0</v>
       </c>
       <c r="AA258" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB258" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC258" t="n">
         <v>0</v>
@@ -31206,7 +31206,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -31216,12 +31216,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -31242,13 +31242,13 @@
         </is>
       </c>
       <c r="L259" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M259" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="N259" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O259" t="n">
         <v>0</v>
@@ -31325,7 +31325,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -31335,12 +31335,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -31361,13 +31361,13 @@
         </is>
       </c>
       <c r="L260" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="M260" t="n">
-        <v>2.88</v>
+        <v>3.74</v>
       </c>
       <c r="N260" t="n">
-        <v>4.2</v>
+        <v>4.94</v>
       </c>
       <c r="O260" t="n">
         <v>0</v>
@@ -31406,10 +31406,10 @@
         <v>0</v>
       </c>
       <c r="AA260" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB260" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC260" t="n">
         <v>0</v>
@@ -31444,22 +31444,22 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -31480,13 +31480,13 @@
         </is>
       </c>
       <c r="L261" t="n">
-        <v>2.3</v>
+        <v>1.29</v>
       </c>
       <c r="M261" t="n">
-        <v>2.88</v>
+        <v>5.1</v>
       </c>
       <c r="N261" t="n">
-        <v>3.4</v>
+        <v>10.5</v>
       </c>
       <c r="O261" t="n">
         <v>0</v>
@@ -31525,10 +31525,10 @@
         <v>0</v>
       </c>
       <c r="AA261" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB261" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC261" t="n">
         <v>0</v>
@@ -31563,7 +31563,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -31573,12 +31573,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -31599,13 +31599,13 @@
         </is>
       </c>
       <c r="L262" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="M262" t="n">
-        <v>3.42</v>
+        <v>2.88</v>
       </c>
       <c r="N262" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="O262" t="n">
         <v>0</v>
@@ -31644,10 +31644,10 @@
         <v>0</v>
       </c>
       <c r="AA262" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB262" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC262" t="n">
         <v>0</v>
@@ -31682,7 +31682,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -31692,12 +31692,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -31718,13 +31718,13 @@
         </is>
       </c>
       <c r="L263" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M263" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="N263" t="n">
-        <v>4.94</v>
+        <v>0</v>
       </c>
       <c r="O263" t="n">
         <v>0</v>
@@ -31763,10 +31763,10 @@
         <v>0</v>
       </c>
       <c r="AA263" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB263" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC263" t="n">
         <v>0</v>
@@ -32277,7 +32277,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -32287,12 +32287,12 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="G268" t="n">
@@ -32313,13 +32313,13 @@
         </is>
       </c>
       <c r="L268" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M268" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N268" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="O268" t="n">
         <v>0</v>
@@ -32396,22 +32396,22 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G269" t="n">
@@ -32432,13 +32432,13 @@
         </is>
       </c>
       <c r="L269" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M269" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N269" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="O269" t="n">
         <v>0</v>
@@ -32634,22 +32634,22 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G271" t="n">
@@ -32753,7 +32753,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -32763,12 +32763,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G272" t="n">
@@ -32991,22 +32991,22 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G274" t="n">
@@ -33110,22 +33110,22 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="G275" t="n">
@@ -33146,13 +33146,13 @@
         </is>
       </c>
       <c r="L275" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M275" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N275" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O275" t="n">
         <v>0</v>
@@ -33348,22 +33348,22 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G277" t="n">
@@ -33467,22 +33467,22 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G278" t="n">
@@ -33503,13 +33503,13 @@
         </is>
       </c>
       <c r="L278" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M278" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N278" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O278" t="n">
         <v>0</v>
@@ -33586,7 +33586,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -33596,12 +33596,12 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G279" t="n">
@@ -33715,12 +33715,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G280" t="n">
@@ -33824,7 +33824,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -33834,12 +33834,12 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G281" t="n">
@@ -33943,7 +33943,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -33953,12 +33953,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G282" t="n">
@@ -33979,13 +33979,13 @@
         </is>
       </c>
       <c r="L282" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M282" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="N282" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O282" t="n">
         <v>0</v>
@@ -34062,7 +34062,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -34072,12 +34072,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="G283" t="n">
@@ -34098,13 +34098,13 @@
         </is>
       </c>
       <c r="L283" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M283" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="N283" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O283" t="n">
         <v>0</v>
@@ -34300,7 +34300,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -34310,12 +34310,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Real Monarchs</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Los Angeles II</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G285" t="n">
@@ -34336,13 +34336,13 @@
         </is>
       </c>
       <c r="L285" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M285" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="N285" t="n">
-        <v>0</v>
+        <v>4.84</v>
       </c>
       <c r="O285" t="n">
         <v>0</v>
@@ -34381,10 +34381,10 @@
         <v>0</v>
       </c>
       <c r="AA285" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB285" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC285" t="n">
         <v>0</v>
@@ -34419,7 +34419,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -34429,12 +34429,12 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Real Monarchs</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Los Angeles II</t>
         </is>
       </c>
       <c r="G286" t="n">
@@ -34455,13 +34455,13 @@
         </is>
       </c>
       <c r="L286" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M286" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="N286" t="n">
-        <v>4.84</v>
+        <v>0</v>
       </c>
       <c r="O286" t="n">
         <v>0</v>
@@ -34500,10 +34500,10 @@
         <v>0</v>
       </c>
       <c r="AA286" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB286" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC286" t="n">
         <v>0</v>
@@ -34538,7 +34538,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -34548,12 +34548,12 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G287" t="n">
@@ -34776,7 +34776,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -34786,12 +34786,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="G289" t="n">
@@ -34905,12 +34905,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G290" t="n">
@@ -35024,12 +35024,12 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="G291" t="n">
@@ -35857,12 +35857,12 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="G298" t="n">
@@ -35976,12 +35976,12 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="G299" t="n">

--- a/jogos_2026-03-15.xlsx
+++ b/jogos_2026-03-15.xlsx
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1932,22 +1932,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Melbourne Victory FC</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Macarthur</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>4.08</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2051,22 +2051,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Melbourne Victory FC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Macarthur</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2646,22 +2646,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,22 +2884,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,22 +3003,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Port FC</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,22 +3598,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,22 +3717,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,22 +4193,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Port FC</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,22 +5383,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5740,22 +5740,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>NorthEast United</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Jamshedpur</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6692,22 +6692,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6886,10 +6886,10 @@
         <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z54" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA54" t="n">
         <v>0</v>
@@ -6930,22 +6930,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>NorthEast United</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Jamshedpur</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7243,10 +7243,10 @@
         <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z57" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA57" t="n">
         <v>0</v>
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ayutthaya United</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Ayutthaya United</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>4.97</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9191,22 +9191,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9310,22 +9310,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9548,22 +9548,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9748,10 +9748,10 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB78" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9905,22 +9905,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Balestier Khalsa</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Home United</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB81" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10262,22 +10262,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10381,22 +10381,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Balestier Khalsa</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Home United</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10581,10 +10581,10 @@
         <v>0</v>
       </c>
       <c r="AA85" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB85" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC85" t="n">
         <v>0</v>
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11250,13 +11250,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M91" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Johor Darul Ta'zim</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N97" t="n">
-        <v>4.59</v>
+        <v>0</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Johor Darul Ta'zim</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12523,22 +12523,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="M102" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="N102" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="M104" t="n">
-        <v>5.58</v>
+        <v>0</v>
       </c>
       <c r="N104" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="M105" t="n">
-        <v>0</v>
+        <v>5.58</v>
       </c>
       <c r="N105" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13035,13 +13035,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="M106" t="n">
-        <v>0</v>
+        <v>5.97</v>
       </c>
       <c r="N106" t="n">
-        <v>0</v>
+        <v>10.3</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13154,13 +13154,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="M107" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N107" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13392,13 +13392,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M109" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N109" t="n">
-        <v>0</v>
+        <v>4.59</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13594,22 +13594,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13630,13 +13630,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>1.29</v>
+        <v>4.3</v>
       </c>
       <c r="M111" t="n">
-        <v>5.97</v>
+        <v>3.94</v>
       </c>
       <c r="N111" t="n">
-        <v>10.3</v>
+        <v>1.78</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13749,13 +13749,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="M112" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N112" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -13868,13 +13868,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="M113" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="N113" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -14070,7 +14070,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14106,13 +14106,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="M115" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="N115" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -14151,10 +14151,10 @@
         <v>0</v>
       </c>
       <c r="AA115" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB115" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC115" t="n">
         <v>0</v>
@@ -14427,22 +14427,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14463,13 +14463,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M118" t="n">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="N118" t="n">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -14508,10 +14508,10 @@
         <v>0</v>
       </c>
       <c r="AA118" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB118" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC118" t="n">
         <v>0</v>
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14582,13 +14582,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="M119" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="N119" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -14627,10 +14627,10 @@
         <v>0</v>
       </c>
       <c r="AA119" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB119" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC119" t="n">
         <v>0</v>
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14701,13 +14701,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="M120" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="N120" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -14746,10 +14746,10 @@
         <v>0</v>
       </c>
       <c r="AA120" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB120" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC120" t="n">
         <v>0</v>
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Inter Kashi</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Mumbai City</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15296,13 +15296,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M125" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="N125" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -15341,10 +15341,10 @@
         <v>0</v>
       </c>
       <c r="AA125" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB125" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC125" t="n">
         <v>0</v>
@@ -15379,22 +15379,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15415,13 +15415,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="M126" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="N126" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15534,13 +15534,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>2.64</v>
+        <v>1.85</v>
       </c>
       <c r="M127" t="n">
-        <v>3.38</v>
+        <v>4.17</v>
       </c>
       <c r="N127" t="n">
-        <v>2.52</v>
+        <v>4.27</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -15579,10 +15579,10 @@
         <v>0</v>
       </c>
       <c r="AA127" t="n">
-        <v>2.03</v>
+        <v>1.62</v>
       </c>
       <c r="AB127" t="n">
-        <v>1.83</v>
+        <v>2.15</v>
       </c>
       <c r="AC127" t="n">
         <v>0</v>
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15653,13 +15653,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="M128" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="N128" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -15698,10 +15698,10 @@
         <v>0</v>
       </c>
       <c r="AA128" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB128" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC128" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="M130" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="N130" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16129,13 +16129,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="M132" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="N132" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -16174,10 +16174,10 @@
         <v>0</v>
       </c>
       <c r="AA132" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB132" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC132" t="n">
         <v>0</v>
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Inter Kashi</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Mumbai City</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16248,13 +16248,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="M133" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N133" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -16293,10 +16293,10 @@
         <v>0</v>
       </c>
       <c r="AA133" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB133" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC133" t="n">
         <v>0</v>
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16367,13 +16367,13 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>2.96</v>
+        <v>2.29</v>
       </c>
       <c r="M134" t="n">
-        <v>3.4</v>
+        <v>3.62</v>
       </c>
       <c r="N134" t="n">
-        <v>2.61</v>
+        <v>3.31</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -16412,10 +16412,10 @@
         <v>0</v>
       </c>
       <c r="AA134" t="n">
-        <v>2</v>
+        <v>1.79</v>
       </c>
       <c r="AB134" t="n">
-        <v>1.77</v>
+        <v>1.92</v>
       </c>
       <c r="AC134" t="n">
         <v>0</v>
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16724,13 +16724,13 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="M137" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N137" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="O137" t="n">
         <v>0</v>
@@ -16769,10 +16769,10 @@
         <v>0</v>
       </c>
       <c r="AA137" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB137" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC137" t="n">
         <v>0</v>
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16843,13 +16843,13 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="M138" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N138" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -16888,10 +16888,10 @@
         <v>0</v>
       </c>
       <c r="AA138" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB138" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC138" t="n">
         <v>0</v>
@@ -16926,7 +16926,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -17045,22 +17045,22 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17081,13 +17081,13 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="M140" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N140" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O140" t="n">
         <v>0</v>
@@ -17164,22 +17164,22 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17319,13 +17319,13 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="M142" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N142" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O142" t="n">
         <v>0</v>
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -21603,13 +21603,13 @@
         </is>
       </c>
       <c r="L178" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="M178" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="N178" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O178" t="n">
         <v>0</v>
@@ -22043,7 +22043,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -22053,12 +22053,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -22075,7 +22075,7 @@
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L182" t="n">
@@ -22198,13 +22198,13 @@
         </is>
       </c>
       <c r="L183" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="M183" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="N183" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="O183" t="n">
         <v>0</v>
@@ -22281,7 +22281,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -22291,12 +22291,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -22400,7 +22400,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -22410,12 +22410,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -22436,13 +22436,13 @@
         </is>
       </c>
       <c r="L185" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="M185" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="N185" t="n">
-        <v>0</v>
+        <v>6.57</v>
       </c>
       <c r="O185" t="n">
         <v>0</v>
@@ -22487,10 +22487,10 @@
         <v>0</v>
       </c>
       <c r="AC185" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD185" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AE185" t="n">
         <v>0</v>
@@ -22638,7 +22638,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -22648,12 +22648,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -22757,7 +22757,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -22767,12 +22767,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -22789,7 +22789,7 @@
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L188" t="n">
@@ -22876,7 +22876,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -22886,12 +22886,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -22912,13 +22912,13 @@
         </is>
       </c>
       <c r="L189" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="M189" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N189" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O189" t="n">
         <v>0</v>
@@ -22957,10 +22957,10 @@
         <v>0</v>
       </c>
       <c r="AA189" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB189" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC189" t="n">
         <v>0</v>
@@ -22995,7 +22995,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -23005,12 +23005,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -23027,7 +23027,7 @@
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L190" t="n">
@@ -23243,12 +23243,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -23352,7 +23352,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -23362,12 +23362,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -23384,17 +23384,17 @@
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L193" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="M193" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N193" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O193" t="n">
         <v>0</v>
@@ -23433,10 +23433,10 @@
         <v>0</v>
       </c>
       <c r="AA193" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB193" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC193" t="n">
         <v>0</v>
@@ -23471,7 +23471,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -23481,12 +23481,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -23590,7 +23590,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -23600,12 +23600,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -23709,7 +23709,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -23719,12 +23719,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -23828,7 +23828,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -23838,12 +23838,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -23947,7 +23947,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -23957,12 +23957,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -23979,7 +23979,7 @@
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L198" t="n">
@@ -24066,7 +24066,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -24076,12 +24076,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -24185,7 +24185,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -24195,12 +24195,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -24221,13 +24221,13 @@
         </is>
       </c>
       <c r="L200" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="M200" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="N200" t="n">
-        <v>7.19</v>
+        <v>0</v>
       </c>
       <c r="O200" t="n">
         <v>0</v>
@@ -24304,7 +24304,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -24314,12 +24314,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -24336,7 +24336,7 @@
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L201" t="n">
@@ -24423,7 +24423,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -24433,12 +24433,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -24542,7 +24542,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -24552,12 +24552,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -24661,7 +24661,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -24671,12 +24671,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -24780,22 +24780,22 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -24816,13 +24816,13 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M205" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N205" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O205" t="n">
         <v>0</v>
@@ -24899,7 +24899,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -24909,12 +24909,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -25018,7 +25018,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -25028,12 +25028,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -25054,13 +25054,13 @@
         </is>
       </c>
       <c r="L207" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="M207" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="N207" t="n">
-        <v>0</v>
+        <v>7.19</v>
       </c>
       <c r="O207" t="n">
         <v>0</v>
@@ -25137,22 +25137,22 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -25173,13 +25173,13 @@
         </is>
       </c>
       <c r="L208" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M208" t="n">
-        <v>4.19</v>
+        <v>0</v>
       </c>
       <c r="N208" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="O208" t="n">
         <v>0</v>
@@ -25224,10 +25224,10 @@
         <v>0</v>
       </c>
       <c r="AC208" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD208" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE208" t="n">
         <v>0</v>
@@ -25256,22 +25256,22 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -25292,13 +25292,13 @@
         </is>
       </c>
       <c r="L209" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="M209" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="N209" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O209" t="n">
         <v>0</v>
@@ -25375,22 +25375,22 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -25411,13 +25411,13 @@
         </is>
       </c>
       <c r="L210" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M210" t="n">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="N210" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="O210" t="n">
         <v>0</v>
@@ -25462,10 +25462,10 @@
         <v>0</v>
       </c>
       <c r="AC210" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD210" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE210" t="n">
         <v>0</v>
@@ -25613,7 +25613,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -25623,12 +25623,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -25742,12 +25742,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -25768,13 +25768,13 @@
         </is>
       </c>
       <c r="L213" t="n">
-        <v>3.35</v>
+        <v>1.95</v>
       </c>
       <c r="M213" t="n">
-        <v>4.14</v>
+        <v>3.65</v>
       </c>
       <c r="N213" t="n">
-        <v>1.97</v>
+        <v>3.85</v>
       </c>
       <c r="O213" t="n">
         <v>0</v>
@@ -25851,7 +25851,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -25861,12 +25861,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -25887,13 +25887,13 @@
         </is>
       </c>
       <c r="L214" t="n">
-        <v>4.11</v>
+        <v>0</v>
       </c>
       <c r="M214" t="n">
-        <v>3.49</v>
+        <v>0</v>
       </c>
       <c r="N214" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="O214" t="n">
         <v>0</v>
@@ -25932,10 +25932,10 @@
         <v>0</v>
       </c>
       <c r="AA214" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB214" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AC214" t="n">
         <v>0</v>
@@ -26089,7 +26089,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -26099,12 +26099,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -26125,13 +26125,13 @@
         </is>
       </c>
       <c r="L216" t="n">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="M216" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="N216" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="O216" t="n">
         <v>0</v>
@@ -26170,10 +26170,10 @@
         <v>0</v>
       </c>
       <c r="AA216" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB216" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC216" t="n">
         <v>0</v>
@@ -26208,7 +26208,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -26218,12 +26218,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -26244,13 +26244,13 @@
         </is>
       </c>
       <c r="L217" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M217" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N217" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="O217" t="n">
         <v>0</v>
@@ -26565,7 +26565,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -26575,12 +26575,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -26684,7 +26684,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -26694,12 +26694,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -26720,13 +26720,13 @@
         </is>
       </c>
       <c r="L221" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="M221" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="N221" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="O221" t="n">
         <v>0</v>
@@ -26765,10 +26765,10 @@
         <v>0</v>
       </c>
       <c r="AA221" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB221" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC221" t="n">
         <v>0</v>
@@ -26803,7 +26803,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -26813,12 +26813,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -26922,7 +26922,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -26932,12 +26932,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -26958,13 +26958,13 @@
         </is>
       </c>
       <c r="L223" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="M223" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N223" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O223" t="n">
         <v>0</v>
@@ -27041,7 +27041,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -27051,12 +27051,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -27160,7 +27160,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -27170,12 +27170,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -27196,13 +27196,13 @@
         </is>
       </c>
       <c r="L225" t="n">
-        <v>2.22</v>
+        <v>1.42</v>
       </c>
       <c r="M225" t="n">
-        <v>3.44</v>
+        <v>5.28</v>
       </c>
       <c r="N225" t="n">
-        <v>3.66</v>
+        <v>8.1</v>
       </c>
       <c r="O225" t="n">
         <v>0</v>
@@ -27241,16 +27241,16 @@
         <v>0</v>
       </c>
       <c r="AA225" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB225" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AC225" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD225" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE225" t="n">
         <v>0</v>
@@ -27279,7 +27279,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -27289,12 +27289,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -27315,13 +27315,13 @@
         </is>
       </c>
       <c r="L226" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="M226" t="n">
-        <v>5.28</v>
+        <v>0</v>
       </c>
       <c r="N226" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="O226" t="n">
         <v>0</v>
@@ -27366,10 +27366,10 @@
         <v>0</v>
       </c>
       <c r="AC226" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD226" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE226" t="n">
         <v>0</v>
@@ -27398,7 +27398,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -27408,12 +27408,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -27636,22 +27636,22 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -27755,7 +27755,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -27765,12 +27765,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -27874,22 +27874,22 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -28112,7 +28112,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -28122,12 +28122,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -28241,12 +28241,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -28707,7 +28707,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -28717,12 +28717,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -28826,7 +28826,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -28836,12 +28836,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -28862,13 +28862,13 @@
         </is>
       </c>
       <c r="L239" t="n">
-        <v>0</v>
+        <v>6.71</v>
       </c>
       <c r="M239" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N239" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="O239" t="n">
         <v>0</v>
@@ -28945,7 +28945,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -28955,12 +28955,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -29074,12 +29074,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -29183,7 +29183,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -29193,12 +29193,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -29219,13 +29219,13 @@
         </is>
       </c>
       <c r="L242" t="n">
-        <v>6.71</v>
+        <v>0</v>
       </c>
       <c r="M242" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="N242" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="O242" t="n">
         <v>0</v>
@@ -29302,7 +29302,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -29312,12 +29312,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -29338,13 +29338,13 @@
         </is>
       </c>
       <c r="L243" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="M243" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="N243" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="O243" t="n">
         <v>0</v>
@@ -29421,22 +29421,22 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -29540,7 +29540,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -29550,12 +29550,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -29659,22 +29659,22 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -29814,13 +29814,13 @@
         </is>
       </c>
       <c r="L247" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M247" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="N247" t="n">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="O247" t="n">
         <v>0</v>
@@ -29859,10 +29859,10 @@
         <v>0</v>
       </c>
       <c r="AA247" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB247" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC247" t="n">
         <v>0</v>
@@ -30502,12 +30502,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -30611,7 +30611,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -30621,12 +30621,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -30730,7 +30730,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -30740,12 +30740,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -30849,22 +30849,22 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -30885,13 +30885,13 @@
         </is>
       </c>
       <c r="L256" t="n">
-        <v>2.35</v>
+        <v>1.29</v>
       </c>
       <c r="M256" t="n">
-        <v>3.25</v>
+        <v>5.1</v>
       </c>
       <c r="N256" t="n">
-        <v>3.24</v>
+        <v>10.5</v>
       </c>
       <c r="O256" t="n">
         <v>0</v>
@@ -30930,10 +30930,10 @@
         <v>0</v>
       </c>
       <c r="AA256" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AB256" t="n">
-        <v>1.63</v>
+        <v>1.98</v>
       </c>
       <c r="AC256" t="n">
         <v>0</v>
@@ -31097,12 +31097,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Connecticut United</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -31444,22 +31444,22 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -31480,13 +31480,13 @@
         </is>
       </c>
       <c r="L261" t="n">
-        <v>1.29</v>
+        <v>2.35</v>
       </c>
       <c r="M261" t="n">
-        <v>5.1</v>
+        <v>3.25</v>
       </c>
       <c r="N261" t="n">
-        <v>10.5</v>
+        <v>3.24</v>
       </c>
       <c r="O261" t="n">
         <v>0</v>
@@ -31525,10 +31525,10 @@
         <v>0</v>
       </c>
       <c r="AA261" t="n">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="AB261" t="n">
-        <v>1.98</v>
+        <v>1.63</v>
       </c>
       <c r="AC261" t="n">
         <v>0</v>
@@ -31692,12 +31692,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Connecticut United</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -32396,22 +32396,22 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G269" t="n">
@@ -32432,13 +32432,13 @@
         </is>
       </c>
       <c r="L269" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M269" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N269" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="O269" t="n">
         <v>0</v>
@@ -32515,22 +32515,22 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G270" t="n">
@@ -32634,22 +32634,22 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G271" t="n">
@@ -32670,13 +32670,13 @@
         </is>
       </c>
       <c r="L271" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M271" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N271" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="O271" t="n">
         <v>0</v>
@@ -32753,22 +32753,22 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G272" t="n">
@@ -33001,12 +33001,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G274" t="n">
@@ -33110,7 +33110,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -33120,12 +33120,12 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G275" t="n">
@@ -33348,22 +33348,22 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="G277" t="n">
@@ -33467,22 +33467,22 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G278" t="n">
@@ -33503,13 +33503,13 @@
         </is>
       </c>
       <c r="L278" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M278" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N278" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O278" t="n">
         <v>0</v>
@@ -33586,22 +33586,22 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G279" t="n">
@@ -33705,22 +33705,22 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G280" t="n">
@@ -33741,13 +33741,13 @@
         </is>
       </c>
       <c r="L280" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M280" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N280" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O280" t="n">
         <v>0</v>
@@ -33824,7 +33824,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -33834,12 +33834,12 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G281" t="n">
@@ -33860,13 +33860,13 @@
         </is>
       </c>
       <c r="L281" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M281" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="N281" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O281" t="n">
         <v>0</v>
@@ -33943,7 +33943,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -33953,12 +33953,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="G282" t="n">
@@ -33979,13 +33979,13 @@
         </is>
       </c>
       <c r="L282" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M282" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="N282" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O282" t="n">
         <v>0</v>
@@ -34062,7 +34062,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -34072,12 +34072,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G283" t="n">
@@ -34181,7 +34181,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -34191,12 +34191,12 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Real Monarchs</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Los Angeles II</t>
         </is>
       </c>
       <c r="G284" t="n">
@@ -34217,13 +34217,13 @@
         </is>
       </c>
       <c r="L284" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="M284" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="N284" t="n">
-        <v>6.69</v>
+        <v>0</v>
       </c>
       <c r="O284" t="n">
         <v>0</v>
@@ -34262,10 +34262,10 @@
         <v>0</v>
       </c>
       <c r="AA284" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB284" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC284" t="n">
         <v>0</v>
@@ -34419,7 +34419,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -34429,12 +34429,12 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Real Monarchs</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Los Angeles II</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G286" t="n">
@@ -34455,13 +34455,13 @@
         </is>
       </c>
       <c r="L286" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="M286" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="N286" t="n">
-        <v>0</v>
+        <v>6.69</v>
       </c>
       <c r="O286" t="n">
         <v>0</v>
@@ -34500,10 +34500,10 @@
         <v>0</v>
       </c>
       <c r="AA286" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB286" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC286" t="n">
         <v>0</v>
@@ -34538,7 +34538,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -34548,12 +34548,12 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Atlanta United II</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="G287" t="n">
@@ -34657,7 +34657,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -34667,12 +34667,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Atlanta United II</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G288" t="n">
@@ -34786,12 +34786,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="G289" t="n">
@@ -34905,12 +34905,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="G290" t="n">
@@ -35014,7 +35014,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -35024,12 +35024,12 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G291" t="n">
@@ -35133,7 +35133,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -35143,12 +35143,12 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G292" t="n">
@@ -35371,7 +35371,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -35381,12 +35381,12 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G294" t="n">
@@ -35407,13 +35407,13 @@
         </is>
       </c>
       <c r="L294" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="M294" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N294" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="O294" t="n">
         <v>0</v>
@@ -35452,10 +35452,10 @@
         <v>0</v>
       </c>
       <c r="AA294" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB294" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC294" t="n">
         <v>0</v>
@@ -35500,12 +35500,12 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G295" t="n">
@@ -35526,13 +35526,13 @@
         </is>
       </c>
       <c r="L295" t="n">
-        <v>1.7</v>
+        <v>2.61</v>
       </c>
       <c r="M295" t="n">
-        <v>3.79</v>
+        <v>3.23</v>
       </c>
       <c r="N295" t="n">
-        <v>5.3</v>
+        <v>2.86</v>
       </c>
       <c r="O295" t="n">
         <v>0</v>
@@ -35571,10 +35571,10 @@
         <v>0</v>
       </c>
       <c r="AA295" t="n">
-        <v>1.93</v>
+        <v>2.3</v>
       </c>
       <c r="AB295" t="n">
-        <v>1.75</v>
+        <v>1.55</v>
       </c>
       <c r="AC295" t="n">
         <v>0</v>
@@ -35609,7 +35609,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -35619,12 +35619,12 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G296" t="n">
@@ -35645,13 +35645,13 @@
         </is>
       </c>
       <c r="L296" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M296" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="N296" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="O296" t="n">
         <v>0</v>
@@ -35690,10 +35690,10 @@
         <v>0</v>
       </c>
       <c r="AA296" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB296" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC296" t="n">
         <v>0</v>

--- a/jogos_2026-03-15.xlsx
+++ b/jogos_2026-03-15.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -2646,22 +2646,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,22 +2765,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3003,22 +3003,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Port FC</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Port FC</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3280,10 +3280,10 @@
         <v>2.09</v>
       </c>
       <c r="M24" t="n">
-        <v>3.42</v>
+        <v>3.25</v>
       </c>
       <c r="N24" t="n">
-        <v>3.02</v>
+        <v>3.19</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3836,22 +3836,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>NorthEast United</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Jamshedpur</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>NorthEast United</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Jamshedpur</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6886,10 +6886,10 @@
         <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z54" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA54" t="n">
         <v>0</v>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7124,10 +7124,10 @@
         <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z56" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA56" t="n">
         <v>0</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Kanchanaburi</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Kanchanaburi</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>4.53</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Ayutthaya United</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>4.97</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ayutthaya United</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>4.97</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9548,22 +9548,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9629,10 +9629,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB77" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9748,10 +9748,10 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -9786,22 +9786,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Balestier Khalsa</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Home United</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10381,22 +10381,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Balestier Khalsa</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Home United</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13392,13 +13392,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M109" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N109" t="n">
-        <v>4.59</v>
+        <v>0</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -13475,22 +13475,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13511,13 +13511,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="M110" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="N110" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -13594,22 +13594,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13630,13 +13630,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="M111" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="N111" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13749,13 +13749,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M112" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N112" t="n">
-        <v>0</v>
+        <v>4.59</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Inter Kashi</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Mumbai City</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M116" t="n">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="N116" t="n">
-        <v>4.77</v>
+        <v>0</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -14270,10 +14270,10 @@
         <v>0</v>
       </c>
       <c r="AA116" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB116" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AC116" t="n">
         <v>0</v>
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14344,13 +14344,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M117" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="N117" t="n">
-        <v>0</v>
+        <v>4.77</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -14389,10 +14389,10 @@
         <v>0</v>
       </c>
       <c r="AA117" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB117" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC117" t="n">
         <v>0</v>
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Inter Kashi</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Mumbai City</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -21567,7 +21567,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -21577,12 +21577,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -21603,13 +21603,13 @@
         </is>
       </c>
       <c r="L178" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="M178" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="N178" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O178" t="n">
         <v>0</v>
@@ -21686,7 +21686,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -21696,12 +21696,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -21722,13 +21722,13 @@
         </is>
       </c>
       <c r="L179" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="M179" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="N179" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O179" t="n">
         <v>0</v>
@@ -22043,7 +22043,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -22053,12 +22053,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -22075,17 +22075,17 @@
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L182" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="M182" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="N182" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="O182" t="n">
         <v>0</v>
@@ -22162,7 +22162,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -22172,12 +22172,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -22198,13 +22198,13 @@
         </is>
       </c>
       <c r="L183" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="M183" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="N183" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="O183" t="n">
         <v>0</v>
@@ -22281,7 +22281,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -22291,12 +22291,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -22317,13 +22317,13 @@
         </is>
       </c>
       <c r="L184" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="M184" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="N184" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="O184" t="n">
         <v>0</v>
@@ -22400,7 +22400,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -22410,12 +22410,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -22436,13 +22436,13 @@
         </is>
       </c>
       <c r="L185" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="M185" t="n">
-        <v>5.35</v>
+        <v>0</v>
       </c>
       <c r="N185" t="n">
-        <v>6.57</v>
+        <v>0</v>
       </c>
       <c r="O185" t="n">
         <v>0</v>
@@ -22487,10 +22487,10 @@
         <v>0</v>
       </c>
       <c r="AC185" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AD185" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AE185" t="n">
         <v>0</v>
@@ -22519,7 +22519,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -22529,12 +22529,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -22551,17 +22551,17 @@
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L186" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="M186" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="N186" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="O186" t="n">
         <v>0</v>
@@ -22638,7 +22638,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -22648,12 +22648,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -22757,7 +22757,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -22767,12 +22767,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -22793,13 +22793,13 @@
         </is>
       </c>
       <c r="L188" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="M188" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="N188" t="n">
-        <v>0</v>
+        <v>6.57</v>
       </c>
       <c r="O188" t="n">
         <v>0</v>
@@ -22844,10 +22844,10 @@
         <v>0</v>
       </c>
       <c r="AC188" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD188" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AE188" t="n">
         <v>0</v>
@@ -22876,7 +22876,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -22886,12 +22886,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -22908,7 +22908,7 @@
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L189" t="n">
@@ -22995,7 +22995,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -23005,12 +23005,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -23027,7 +23027,7 @@
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L190" t="n">
@@ -23471,7 +23471,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -23481,12 +23481,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -23590,7 +23590,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -23600,12 +23600,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -23709,7 +23709,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -23719,12 +23719,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -23828,7 +23828,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -23838,12 +23838,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -23947,7 +23947,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -23957,12 +23957,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -24066,7 +24066,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -24076,12 +24076,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -24185,22 +24185,22 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -24221,13 +24221,13 @@
         </is>
       </c>
       <c r="L200" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="M200" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="N200" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O200" t="n">
         <v>0</v>
@@ -24304,22 +24304,22 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -24336,17 +24336,17 @@
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L201" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M201" t="n">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="N201" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="O201" t="n">
         <v>0</v>
@@ -24391,10 +24391,10 @@
         <v>0</v>
       </c>
       <c r="AC201" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD201" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE201" t="n">
         <v>0</v>
@@ -24423,22 +24423,22 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -24459,13 +24459,13 @@
         </is>
       </c>
       <c r="L202" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M202" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N202" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O202" t="n">
         <v>0</v>
@@ -24542,7 +24542,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -24552,12 +24552,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -24578,13 +24578,13 @@
         </is>
       </c>
       <c r="L203" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="M203" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="N203" t="n">
-        <v>0</v>
+        <v>7.19</v>
       </c>
       <c r="O203" t="n">
         <v>0</v>
@@ -24661,7 +24661,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -24671,12 +24671,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -24780,7 +24780,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -24790,12 +24790,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -24899,7 +24899,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -24909,12 +24909,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -24931,7 +24931,7 @@
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L206" t="n">
@@ -25018,7 +25018,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -25028,12 +25028,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -25054,13 +25054,13 @@
         </is>
       </c>
       <c r="L207" t="n">
-        <v>1.42</v>
+        <v>3.16</v>
       </c>
       <c r="M207" t="n">
-        <v>4.45</v>
+        <v>3.44</v>
       </c>
       <c r="N207" t="n">
-        <v>7.19</v>
+        <v>2.45</v>
       </c>
       <c r="O207" t="n">
         <v>0</v>
@@ -25147,12 +25147,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -25256,22 +25256,22 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -25292,13 +25292,13 @@
         </is>
       </c>
       <c r="L209" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="M209" t="n">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="N209" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="O209" t="n">
         <v>0</v>
@@ -25375,22 +25375,22 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -25411,13 +25411,13 @@
         </is>
       </c>
       <c r="L210" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M210" t="n">
-        <v>4.19</v>
+        <v>0</v>
       </c>
       <c r="N210" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="O210" t="n">
         <v>0</v>
@@ -25462,10 +25462,10 @@
         <v>0</v>
       </c>
       <c r="AC210" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD210" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE210" t="n">
         <v>0</v>
@@ -25494,7 +25494,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -25504,12 +25504,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -25530,13 +25530,13 @@
         </is>
       </c>
       <c r="L211" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="M211" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="N211" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O211" t="n">
         <v>0</v>
@@ -25613,7 +25613,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -25623,12 +25623,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -25732,22 +25732,22 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -25768,13 +25768,13 @@
         </is>
       </c>
       <c r="L213" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M213" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N213" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O213" t="n">
         <v>0</v>
@@ -25851,7 +25851,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -25861,12 +25861,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -25887,13 +25887,13 @@
         </is>
       </c>
       <c r="L214" t="n">
-        <v>0</v>
+        <v>4.57</v>
       </c>
       <c r="M214" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="N214" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="O214" t="n">
         <v>0</v>
@@ -25932,10 +25932,10 @@
         <v>0</v>
       </c>
       <c r="AA214" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB214" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC214" t="n">
         <v>0</v>
@@ -25970,7 +25970,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -25980,12 +25980,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -26006,13 +26006,13 @@
         </is>
       </c>
       <c r="L215" t="n">
-        <v>4.57</v>
+        <v>0</v>
       </c>
       <c r="M215" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="N215" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="O215" t="n">
         <v>0</v>
@@ -26051,10 +26051,10 @@
         <v>0</v>
       </c>
       <c r="AA215" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AB215" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC215" t="n">
         <v>0</v>
@@ -26208,7 +26208,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -26218,12 +26218,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -26244,13 +26244,13 @@
         </is>
       </c>
       <c r="L217" t="n">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="M217" t="n">
-        <v>3.2</v>
+        <v>3.44</v>
       </c>
       <c r="N217" t="n">
-        <v>2.93</v>
+        <v>3.66</v>
       </c>
       <c r="O217" t="n">
         <v>0</v>
@@ -26289,10 +26289,10 @@
         <v>0</v>
       </c>
       <c r="AA217" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB217" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC217" t="n">
         <v>0</v>
@@ -26327,7 +26327,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -26337,12 +26337,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -26363,13 +26363,13 @@
         </is>
       </c>
       <c r="L218" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M218" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N218" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="O218" t="n">
         <v>0</v>
@@ -26565,7 +26565,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -26575,12 +26575,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -26601,13 +26601,13 @@
         </is>
       </c>
       <c r="L220" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="M220" t="n">
-        <v>0</v>
+        <v>5.28</v>
       </c>
       <c r="N220" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="O220" t="n">
         <v>0</v>
@@ -26652,10 +26652,10 @@
         <v>0</v>
       </c>
       <c r="AC220" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD220" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE220" t="n">
         <v>0</v>
@@ -26684,7 +26684,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -26694,12 +26694,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -26720,13 +26720,13 @@
         </is>
       </c>
       <c r="L221" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="M221" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="N221" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="O221" t="n">
         <v>0</v>
@@ -26765,10 +26765,10 @@
         <v>0</v>
       </c>
       <c r="AA221" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB221" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AC221" t="n">
         <v>0</v>
@@ -26922,7 +26922,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -26932,12 +26932,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -26958,13 +26958,13 @@
         </is>
       </c>
       <c r="L223" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="M223" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N223" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="O223" t="n">
         <v>0</v>
@@ -27041,7 +27041,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -27051,12 +27051,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -27160,7 +27160,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -27170,12 +27170,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -27196,13 +27196,13 @@
         </is>
       </c>
       <c r="L225" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="M225" t="n">
-        <v>5.28</v>
+        <v>0</v>
       </c>
       <c r="N225" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="O225" t="n">
         <v>0</v>
@@ -27247,10 +27247,10 @@
         <v>0</v>
       </c>
       <c r="AC225" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD225" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE225" t="n">
         <v>0</v>
@@ -27279,7 +27279,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -27289,12 +27289,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -27315,13 +27315,13 @@
         </is>
       </c>
       <c r="L226" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="M226" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N226" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O226" t="n">
         <v>0</v>
@@ -27636,7 +27636,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -27646,12 +27646,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -27755,7 +27755,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -27765,12 +27765,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -27874,7 +27874,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -27884,12 +27884,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -27993,22 +27993,22 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -28029,13 +28029,13 @@
         </is>
       </c>
       <c r="L232" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="M232" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="N232" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O232" t="n">
         <v>0</v>
@@ -28074,10 +28074,10 @@
         <v>0</v>
       </c>
       <c r="AA232" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB232" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC232" t="n">
         <v>0</v>
@@ -28112,7 +28112,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -28122,12 +28122,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -28231,7 +28231,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -28241,12 +28241,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -28267,13 +28267,13 @@
         </is>
       </c>
       <c r="L234" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="M234" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="N234" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O234" t="n">
         <v>0</v>
@@ -28312,10 +28312,10 @@
         <v>0</v>
       </c>
       <c r="AA234" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB234" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC234" t="n">
         <v>0</v>
@@ -28350,22 +28350,22 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -28469,7 +28469,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -28479,12 +28479,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -28945,7 +28945,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -28955,12 +28955,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -28981,13 +28981,13 @@
         </is>
       </c>
       <c r="L240" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="M240" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="N240" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="O240" t="n">
         <v>0</v>
@@ -29074,12 +29074,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -29183,7 +29183,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -29193,12 +29193,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -29302,7 +29302,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -29312,12 +29312,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -29338,13 +29338,13 @@
         </is>
       </c>
       <c r="L243" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="M243" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="N243" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="O243" t="n">
         <v>0</v>
@@ -30016,7 +30016,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -30026,12 +30026,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -30254,22 +30254,22 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -30290,13 +30290,13 @@
         </is>
       </c>
       <c r="L251" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M251" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N251" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="O251" t="n">
         <v>0</v>
@@ -30335,10 +30335,10 @@
         <v>0</v>
       </c>
       <c r="AA251" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB251" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC251" t="n">
         <v>0</v>
@@ -30373,22 +30373,22 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -30492,7 +30492,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -30502,12 +30502,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -30849,22 +30849,22 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Connecticut United</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -30885,13 +30885,13 @@
         </is>
       </c>
       <c r="L256" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="M256" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="N256" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="O256" t="n">
         <v>0</v>
@@ -30930,10 +30930,10 @@
         <v>0</v>
       </c>
       <c r="AA256" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB256" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC256" t="n">
         <v>0</v>
@@ -31087,7 +31087,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -31097,12 +31097,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -31123,13 +31123,13 @@
         </is>
       </c>
       <c r="L258" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M258" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N258" t="n">
-        <v>0</v>
+        <v>4.94</v>
       </c>
       <c r="O258" t="n">
         <v>0</v>
@@ -31168,10 +31168,10 @@
         <v>0</v>
       </c>
       <c r="AA258" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB258" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC258" t="n">
         <v>0</v>
@@ -31206,7 +31206,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -31216,12 +31216,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -31242,13 +31242,13 @@
         </is>
       </c>
       <c r="L259" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="M259" t="n">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="N259" t="n">
-        <v>3.4</v>
+        <v>3.24</v>
       </c>
       <c r="O259" t="n">
         <v>0</v>
@@ -31287,10 +31287,10 @@
         <v>0</v>
       </c>
       <c r="AA259" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB259" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC259" t="n">
         <v>0</v>
@@ -31325,7 +31325,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -31335,12 +31335,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -31361,13 +31361,13 @@
         </is>
       </c>
       <c r="L260" t="n">
-        <v>1.75</v>
+        <v>2.3</v>
       </c>
       <c r="M260" t="n">
-        <v>3.74</v>
+        <v>2.88</v>
       </c>
       <c r="N260" t="n">
-        <v>4.94</v>
+        <v>3.4</v>
       </c>
       <c r="O260" t="n">
         <v>0</v>
@@ -31406,10 +31406,10 @@
         <v>0</v>
       </c>
       <c r="AA260" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB260" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC260" t="n">
         <v>0</v>
@@ -31444,22 +31444,22 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -31480,13 +31480,13 @@
         </is>
       </c>
       <c r="L261" t="n">
-        <v>2.35</v>
+        <v>1.29</v>
       </c>
       <c r="M261" t="n">
-        <v>3.25</v>
+        <v>5.1</v>
       </c>
       <c r="N261" t="n">
-        <v>3.24</v>
+        <v>10.5</v>
       </c>
       <c r="O261" t="n">
         <v>0</v>
@@ -31525,10 +31525,10 @@
         <v>0</v>
       </c>
       <c r="AA261" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AB261" t="n">
-        <v>1.63</v>
+        <v>1.98</v>
       </c>
       <c r="AC261" t="n">
         <v>0</v>
@@ -31563,7 +31563,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -31573,12 +31573,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -31599,13 +31599,13 @@
         </is>
       </c>
       <c r="L262" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M262" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="N262" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O262" t="n">
         <v>0</v>
@@ -31682,7 +31682,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -31692,12 +31692,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Connecticut United</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -31718,13 +31718,13 @@
         </is>
       </c>
       <c r="L263" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M263" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="N263" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O263" t="n">
         <v>0</v>
@@ -32277,7 +32277,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -32287,12 +32287,12 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G268" t="n">
@@ -32396,22 +32396,22 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G269" t="n">
@@ -32432,13 +32432,13 @@
         </is>
       </c>
       <c r="L269" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M269" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N269" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="O269" t="n">
         <v>0</v>
@@ -32515,22 +32515,22 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="G270" t="n">
@@ -32634,22 +32634,22 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G271" t="n">
@@ -32670,13 +32670,13 @@
         </is>
       </c>
       <c r="L271" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M271" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N271" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="O271" t="n">
         <v>0</v>
@@ -32753,22 +32753,22 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G272" t="n">
@@ -32991,22 +32991,22 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G274" t="n">
@@ -33027,13 +33027,13 @@
         </is>
       </c>
       <c r="L274" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M274" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N274" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O274" t="n">
         <v>0</v>
@@ -33110,7 +33110,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -33120,12 +33120,12 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="G275" t="n">
@@ -33229,22 +33229,22 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G276" t="n">
@@ -33265,13 +33265,13 @@
         </is>
       </c>
       <c r="L276" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="M276" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="N276" t="n">
-        <v>0</v>
+        <v>6.39</v>
       </c>
       <c r="O276" t="n">
         <v>0</v>
@@ -33316,10 +33316,10 @@
         <v>0</v>
       </c>
       <c r="AC276" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD276" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE276" t="n">
         <v>0</v>
@@ -33348,7 +33348,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -33358,12 +33358,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G277" t="n">
@@ -33586,22 +33586,22 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G279" t="n">
@@ -33705,22 +33705,22 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G280" t="n">
@@ -33741,13 +33741,13 @@
         </is>
       </c>
       <c r="L280" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M280" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N280" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O280" t="n">
         <v>0</v>
@@ -33824,7 +33824,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -33834,12 +33834,12 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="G281" t="n">
@@ -33860,13 +33860,13 @@
         </is>
       </c>
       <c r="L281" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M281" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="N281" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O281" t="n">
         <v>0</v>
@@ -33943,7 +33943,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -33953,12 +33953,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G282" t="n">
@@ -33979,13 +33979,13 @@
         </is>
       </c>
       <c r="L282" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M282" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="N282" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O282" t="n">
         <v>0</v>
@@ -34181,7 +34181,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -34191,12 +34191,12 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Real Monarchs</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Los Angeles II</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G284" t="n">
@@ -34217,13 +34217,13 @@
         </is>
       </c>
       <c r="L284" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="M284" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="N284" t="n">
-        <v>0</v>
+        <v>6.69</v>
       </c>
       <c r="O284" t="n">
         <v>0</v>
@@ -34262,10 +34262,10 @@
         <v>0</v>
       </c>
       <c r="AA284" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB284" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC284" t="n">
         <v>0</v>
@@ -34419,7 +34419,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -34429,12 +34429,12 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Real Monarchs</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Los Angeles II</t>
         </is>
       </c>
       <c r="G286" t="n">
@@ -34455,13 +34455,13 @@
         </is>
       </c>
       <c r="L286" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="M286" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="N286" t="n">
-        <v>6.69</v>
+        <v>0</v>
       </c>
       <c r="O286" t="n">
         <v>0</v>
@@ -34500,10 +34500,10 @@
         <v>0</v>
       </c>
       <c r="AA286" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB286" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC286" t="n">
         <v>0</v>
@@ -34548,12 +34548,12 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Atlanta United II</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="G287" t="n">
@@ -34657,7 +34657,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -34667,12 +34667,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Atlanta United II</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="G288" t="n">
@@ -34786,12 +34786,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G289" t="n">
@@ -35014,7 +35014,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -35024,12 +35024,12 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G291" t="n">
@@ -35050,13 +35050,13 @@
         </is>
       </c>
       <c r="L291" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="M291" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="N291" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="O291" t="n">
         <v>0</v>
@@ -35095,10 +35095,10 @@
         <v>0</v>
       </c>
       <c r="AA291" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB291" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AC291" t="n">
         <v>0</v>
@@ -35133,7 +35133,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -35143,12 +35143,12 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G292" t="n">
@@ -35490,7 +35490,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -35500,12 +35500,12 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G295" t="n">
@@ -35526,13 +35526,13 @@
         </is>
       </c>
       <c r="L295" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="M295" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N295" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="O295" t="n">
         <v>0</v>
@@ -35571,10 +35571,10 @@
         <v>0</v>
       </c>
       <c r="AA295" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB295" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC295" t="n">
         <v>0</v>
@@ -35619,12 +35619,12 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G296" t="n">
@@ -35645,13 +35645,13 @@
         </is>
       </c>
       <c r="L296" t="n">
-        <v>1.7</v>
+        <v>2.61</v>
       </c>
       <c r="M296" t="n">
-        <v>3.79</v>
+        <v>3.23</v>
       </c>
       <c r="N296" t="n">
-        <v>5.3</v>
+        <v>2.86</v>
       </c>
       <c r="O296" t="n">
         <v>0</v>
@@ -35690,10 +35690,10 @@
         <v>0</v>
       </c>
       <c r="AA296" t="n">
-        <v>1.93</v>
+        <v>2.3</v>
       </c>
       <c r="AB296" t="n">
-        <v>1.75</v>
+        <v>1.55</v>
       </c>
       <c r="AC296" t="n">
         <v>0</v>
@@ -35728,7 +35728,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -35738,12 +35738,12 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G297" t="n">
@@ -35764,13 +35764,13 @@
         </is>
       </c>
       <c r="L297" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M297" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="N297" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="O297" t="n">
         <v>0</v>
@@ -35809,10 +35809,10 @@
         <v>0</v>
       </c>
       <c r="AA297" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB297" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC297" t="n">
         <v>0</v>

--- a/jogos_2026-03-15.xlsx
+++ b/jogos_2026-03-15.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="M9" t="n">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="N9" t="n">
-        <v>3.72</v>
+        <v>3.37</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2646,22 +2646,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,22 +2765,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,22 +3360,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,22 +3598,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,22 +3717,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,22 +3836,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5621,22 +5621,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5740,22 +5740,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>4.48</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>6.17</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>4.48</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>6.17</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>NorthEast United</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Jamshedpur</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6886,10 +6886,10 @@
         <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z54" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA54" t="n">
         <v>0</v>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Kanchanaburi</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>3.25</v>
+        <v>1.63</v>
       </c>
       <c r="M56" t="n">
-        <v>3.15</v>
+        <v>3.74</v>
       </c>
       <c r="N56" t="n">
-        <v>2.57</v>
+        <v>4.53</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7124,10 +7124,10 @@
         <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z56" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA56" t="n">
         <v>0</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Kanchanaburi</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>4.53</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>NorthEast United</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Jamshedpur</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Ayutthaya United</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>4.97</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ayutthaya United</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>4.97</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9548,22 +9548,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9629,10 +9629,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -9667,22 +9667,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9786,22 +9786,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Balestier Khalsa</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Home United</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="M79" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB79" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -9905,22 +9905,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="M80" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB80" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>2.06</v>
+        <v>1.9</v>
       </c>
       <c r="M81" t="n">
-        <v>3.56</v>
+        <v>3.84</v>
       </c>
       <c r="N81" t="n">
-        <v>3.32</v>
+        <v>3.57</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>1.87</v>
+        <v>1.55</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>1.4</v>
+        <v>2.17</v>
       </c>
       <c r="M82" t="n">
-        <v>4.3</v>
+        <v>3.75</v>
       </c>
       <c r="N82" t="n">
-        <v>7.9</v>
+        <v>3</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10381,22 +10381,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10417,13 +10417,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M84" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -10500,22 +10500,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Balestier Khalsa</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Home United</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10581,10 +10581,10 @@
         <v>0</v>
       </c>
       <c r="AA85" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB85" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC85" t="n">
         <v>0</v>
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="N88" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11250,13 +11250,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M91" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N91" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,13 +11607,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M94" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11726,13 +11726,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="M95" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Johor Darul Ta'zim</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="M97" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Johor Darul Ta'zim</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="M105" t="n">
-        <v>5.58</v>
+        <v>0</v>
       </c>
       <c r="N105" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13035,13 +13035,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>1.29</v>
+        <v>1.85</v>
       </c>
       <c r="M106" t="n">
-        <v>5.97</v>
+        <v>2.9</v>
       </c>
       <c r="N106" t="n">
-        <v>10.3</v>
+        <v>4.59</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13154,13 +13154,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="M107" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N107" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13273,13 +13273,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="M108" t="n">
-        <v>0</v>
+        <v>5.97</v>
       </c>
       <c r="N108" t="n">
-        <v>0</v>
+        <v>10.3</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13475,22 +13475,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13511,13 +13511,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>4.3</v>
+        <v>1.35</v>
       </c>
       <c r="M110" t="n">
-        <v>3.94</v>
+        <v>5.58</v>
       </c>
       <c r="N110" t="n">
-        <v>1.78</v>
+        <v>8.1</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -13594,22 +13594,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13630,13 +13630,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="M111" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="N111" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13749,13 +13749,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M112" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N112" t="n">
-        <v>4.59</v>
+        <v>0</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14070,7 +14070,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Inter Kashi</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Mumbai City</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M116" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="N116" t="n">
-        <v>0</v>
+        <v>4.77</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -14270,10 +14270,10 @@
         <v>0</v>
       </c>
       <c r="AA116" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB116" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC116" t="n">
         <v>0</v>
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14344,13 +14344,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M117" t="n">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="N117" t="n">
-        <v>4.77</v>
+        <v>0</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -14389,10 +14389,10 @@
         <v>0</v>
       </c>
       <c r="AA117" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB117" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AC117" t="n">
         <v>0</v>
@@ -14427,22 +14427,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14463,13 +14463,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="M118" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="N118" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -14508,10 +14508,10 @@
         <v>0</v>
       </c>
       <c r="AA118" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB118" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC118" t="n">
         <v>0</v>
@@ -14546,22 +14546,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14701,13 +14701,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>2.64</v>
+        <v>2.29</v>
       </c>
       <c r="M120" t="n">
-        <v>3.38</v>
+        <v>3.62</v>
       </c>
       <c r="N120" t="n">
-        <v>2.52</v>
+        <v>3.31</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -14746,10 +14746,10 @@
         <v>0</v>
       </c>
       <c r="AA120" t="n">
-        <v>2.03</v>
+        <v>1.79</v>
       </c>
       <c r="AB120" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AC120" t="n">
         <v>0</v>
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Inter Kashi</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Mumbai City</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -14939,13 +14939,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="M122" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N122" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -14984,10 +14984,10 @@
         <v>0</v>
       </c>
       <c r="AA122" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB122" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC122" t="n">
         <v>0</v>
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15296,13 +15296,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="M125" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="N125" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -15341,10 +15341,10 @@
         <v>0</v>
       </c>
       <c r="AA125" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB125" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC125" t="n">
         <v>0</v>
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15415,13 +15415,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="M126" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="N126" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15534,13 +15534,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="M127" t="n">
-        <v>4.17</v>
+        <v>2.92</v>
       </c>
       <c r="N127" t="n">
-        <v>4.27</v>
+        <v>3.69</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -15579,10 +15579,10 @@
         <v>0</v>
       </c>
       <c r="AA127" t="n">
-        <v>1.62</v>
+        <v>2.25</v>
       </c>
       <c r="AB127" t="n">
-        <v>2.15</v>
+        <v>1.57</v>
       </c>
       <c r="AC127" t="n">
         <v>0</v>
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15653,13 +15653,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M128" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="N128" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -15698,10 +15698,10 @@
         <v>0</v>
       </c>
       <c r="AA128" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB128" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC128" t="n">
         <v>0</v>
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15772,13 +15772,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>2.2</v>
+        <v>3.51</v>
       </c>
       <c r="M129" t="n">
-        <v>2.92</v>
+        <v>3.38</v>
       </c>
       <c r="N129" t="n">
-        <v>3.69</v>
+        <v>2.03</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -15817,10 +15817,10 @@
         <v>0</v>
       </c>
       <c r="AA129" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB129" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC129" t="n">
         <v>0</v>
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16010,13 +16010,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M131" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="N131" t="n">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -16055,10 +16055,10 @@
         <v>0</v>
       </c>
       <c r="AA131" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB131" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC131" t="n">
         <v>0</v>
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16129,13 +16129,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="M132" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="N132" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -16174,10 +16174,10 @@
         <v>0</v>
       </c>
       <c r="AA132" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB132" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC132" t="n">
         <v>0</v>
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16248,13 +16248,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="M133" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N133" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -16293,10 +16293,10 @@
         <v>0</v>
       </c>
       <c r="AA133" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB133" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC133" t="n">
         <v>0</v>
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16367,13 +16367,13 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="M134" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="N134" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -16412,10 +16412,10 @@
         <v>0</v>
       </c>
       <c r="AA134" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB134" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC134" t="n">
         <v>0</v>
@@ -16450,7 +16450,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16486,13 +16486,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="M135" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="N135" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -16531,10 +16531,10 @@
         <v>0</v>
       </c>
       <c r="AA135" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB135" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC135" t="n">
         <v>0</v>
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16724,13 +16724,13 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="M137" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N137" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="O137" t="n">
         <v>0</v>
@@ -16769,10 +16769,10 @@
         <v>0</v>
       </c>
       <c r="AA137" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB137" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC137" t="n">
         <v>0</v>
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16843,13 +16843,13 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="M138" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N138" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -16888,10 +16888,10 @@
         <v>0</v>
       </c>
       <c r="AA138" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB138" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC138" t="n">
         <v>0</v>
@@ -16926,22 +16926,22 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -17045,7 +17045,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17081,13 +17081,13 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="M140" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N140" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O140" t="n">
         <v>0</v>
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17319,13 +17319,13 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="M142" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N142" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O142" t="n">
         <v>0</v>
@@ -17402,22 +17402,22 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -22162,7 +22162,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -22172,12 +22172,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -22400,7 +22400,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -22410,12 +22410,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -28945,7 +28945,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -28955,12 +28955,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -28981,13 +28981,13 @@
         </is>
       </c>
       <c r="L240" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="M240" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="N240" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="O240" t="n">
         <v>0</v>
@@ -29064,7 +29064,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -29074,12 +29074,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -29100,13 +29100,13 @@
         </is>
       </c>
       <c r="L241" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="M241" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="N241" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="O241" t="n">
         <v>0</v>
@@ -30016,7 +30016,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -30026,12 +30026,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -30052,13 +30052,13 @@
         </is>
       </c>
       <c r="L249" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="M249" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="N249" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="O249" t="n">
         <v>0</v>
@@ -30103,10 +30103,10 @@
         <v>0</v>
       </c>
       <c r="AC249" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD249" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AE249" t="n">
         <v>0</v>
@@ -30135,7 +30135,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -30145,12 +30145,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -30171,13 +30171,13 @@
         </is>
       </c>
       <c r="L250" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="M250" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="N250" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="O250" t="n">
         <v>0</v>
@@ -30222,10 +30222,10 @@
         <v>0</v>
       </c>
       <c r="AC250" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD250" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AE250" t="n">
         <v>0</v>
@@ -30254,22 +30254,22 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -30290,13 +30290,13 @@
         </is>
       </c>
       <c r="L251" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M251" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N251" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="O251" t="n">
         <v>0</v>
@@ -30335,10 +30335,10 @@
         <v>0</v>
       </c>
       <c r="AA251" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB251" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC251" t="n">
         <v>0</v>
@@ -30373,7 +30373,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -30383,12 +30383,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -30492,7 +30492,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -30502,12 +30502,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -30611,22 +30611,22 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -30647,13 +30647,13 @@
         </is>
       </c>
       <c r="L254" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M254" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N254" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="O254" t="n">
         <v>0</v>
@@ -30692,10 +30692,10 @@
         <v>0</v>
       </c>
       <c r="AA254" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB254" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC254" t="n">
         <v>0</v>
@@ -30730,7 +30730,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -30740,12 +30740,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -30849,7 +30849,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -30859,12 +30859,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Connecticut United</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -30885,13 +30885,13 @@
         </is>
       </c>
       <c r="L256" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M256" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="N256" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O256" t="n">
         <v>0</v>
@@ -30968,22 +30968,22 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -31004,13 +31004,13 @@
         </is>
       </c>
       <c r="L257" t="n">
-        <v>2.2</v>
+        <v>1.29</v>
       </c>
       <c r="M257" t="n">
-        <v>3.42</v>
+        <v>5.1</v>
       </c>
       <c r="N257" t="n">
-        <v>3.4</v>
+        <v>10.5</v>
       </c>
       <c r="O257" t="n">
         <v>0</v>
@@ -31049,10 +31049,10 @@
         <v>0</v>
       </c>
       <c r="AA257" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AB257" t="n">
-        <v>1.68</v>
+        <v>1.98</v>
       </c>
       <c r="AC257" t="n">
         <v>0</v>
@@ -31087,7 +31087,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -31097,12 +31097,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -31123,13 +31123,13 @@
         </is>
       </c>
       <c r="L258" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="M258" t="n">
-        <v>3.74</v>
+        <v>2.88</v>
       </c>
       <c r="N258" t="n">
-        <v>4.94</v>
+        <v>4.2</v>
       </c>
       <c r="O258" t="n">
         <v>0</v>
@@ -31168,10 +31168,10 @@
         <v>0</v>
       </c>
       <c r="AA258" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB258" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC258" t="n">
         <v>0</v>
@@ -31216,12 +31216,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -31242,13 +31242,13 @@
         </is>
       </c>
       <c r="L259" t="n">
-        <v>2.35</v>
+        <v>1.75</v>
       </c>
       <c r="M259" t="n">
-        <v>3.25</v>
+        <v>3.74</v>
       </c>
       <c r="N259" t="n">
-        <v>3.24</v>
+        <v>4.94</v>
       </c>
       <c r="O259" t="n">
         <v>0</v>
@@ -31287,10 +31287,10 @@
         <v>0</v>
       </c>
       <c r="AA259" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AB259" t="n">
-        <v>1.63</v>
+        <v>1.8</v>
       </c>
       <c r="AC259" t="n">
         <v>0</v>
@@ -31325,7 +31325,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -31335,12 +31335,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -31361,10 +31361,10 @@
         </is>
       </c>
       <c r="L260" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="M260" t="n">
-        <v>2.88</v>
+        <v>3.42</v>
       </c>
       <c r="N260" t="n">
         <v>3.4</v>
@@ -31406,10 +31406,10 @@
         <v>0</v>
       </c>
       <c r="AA260" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB260" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC260" t="n">
         <v>0</v>
@@ -31444,22 +31444,22 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Connecticut United</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -31480,13 +31480,13 @@
         </is>
       </c>
       <c r="L261" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="M261" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="N261" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="O261" t="n">
         <v>0</v>
@@ -31525,10 +31525,10 @@
         <v>0</v>
       </c>
       <c r="AA261" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB261" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC261" t="n">
         <v>0</v>
@@ -31682,7 +31682,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -31692,12 +31692,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -31718,13 +31718,13 @@
         </is>
       </c>
       <c r="L263" t="n">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="M263" t="n">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="N263" t="n">
-        <v>4.2</v>
+        <v>3.24</v>
       </c>
       <c r="O263" t="n">
         <v>0</v>
@@ -31763,10 +31763,10 @@
         <v>0</v>
       </c>
       <c r="AA263" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB263" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC263" t="n">
         <v>0</v>
@@ -32039,7 +32039,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -32049,12 +32049,12 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G266" t="n">
@@ -32075,13 +32075,13 @@
         </is>
       </c>
       <c r="L266" t="n">
-        <v>2.67</v>
+        <v>3.79</v>
       </c>
       <c r="M266" t="n">
         <v>3.38</v>
       </c>
       <c r="N266" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="O266" t="n">
         <v>0</v>
@@ -32120,10 +32120,10 @@
         <v>0</v>
       </c>
       <c r="AA266" t="n">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="AB266" t="n">
-        <v>1.95</v>
+        <v>1.57</v>
       </c>
       <c r="AC266" t="n">
         <v>0</v>
@@ -32158,7 +32158,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -32168,12 +32168,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="G267" t="n">
@@ -32194,13 +32194,13 @@
         </is>
       </c>
       <c r="L267" t="n">
-        <v>3.79</v>
+        <v>2.67</v>
       </c>
       <c r="M267" t="n">
         <v>3.38</v>
       </c>
       <c r="N267" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="O267" t="n">
         <v>0</v>
@@ -32239,10 +32239,10 @@
         <v>0</v>
       </c>
       <c r="AA267" t="n">
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="AB267" t="n">
-        <v>1.57</v>
+        <v>1.95</v>
       </c>
       <c r="AC267" t="n">
         <v>0</v>
@@ -32277,22 +32277,22 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G268" t="n">
@@ -32515,22 +32515,22 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G270" t="n">
@@ -32634,22 +32634,22 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="G271" t="n">
@@ -32753,22 +32753,22 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G272" t="n">
@@ -32991,22 +32991,22 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="G274" t="n">
@@ -33027,13 +33027,13 @@
         </is>
       </c>
       <c r="L274" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M274" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N274" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O274" t="n">
         <v>0</v>
@@ -33110,22 +33110,22 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G275" t="n">
@@ -33146,13 +33146,13 @@
         </is>
       </c>
       <c r="L275" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="M275" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="N275" t="n">
-        <v>0</v>
+        <v>6.39</v>
       </c>
       <c r="O275" t="n">
         <v>0</v>
@@ -33197,10 +33197,10 @@
         <v>0</v>
       </c>
       <c r="AC275" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD275" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE275" t="n">
         <v>0</v>
@@ -33229,22 +33229,22 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G276" t="n">
@@ -33265,13 +33265,13 @@
         </is>
       </c>
       <c r="L276" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="M276" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="N276" t="n">
-        <v>6.39</v>
+        <v>0</v>
       </c>
       <c r="O276" t="n">
         <v>0</v>
@@ -33316,10 +33316,10 @@
         <v>0</v>
       </c>
       <c r="AC276" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD276" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE276" t="n">
         <v>0</v>
@@ -33358,12 +33358,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G277" t="n">
@@ -33477,12 +33477,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G278" t="n">
@@ -33586,22 +33586,22 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G279" t="n">
@@ -33622,13 +33622,13 @@
         </is>
       </c>
       <c r="L279" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M279" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N279" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O279" t="n">
         <v>0</v>
@@ -33715,12 +33715,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G280" t="n">
@@ -33824,7 +33824,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -33834,12 +33834,12 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G281" t="n">
@@ -33943,7 +33943,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -33953,12 +33953,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="G282" t="n">
@@ -33979,13 +33979,13 @@
         </is>
       </c>
       <c r="L282" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M282" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="N282" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O282" t="n">
         <v>0</v>
@@ -34062,7 +34062,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -34072,12 +34072,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G283" t="n">
@@ -34098,13 +34098,13 @@
         </is>
       </c>
       <c r="L283" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M283" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="N283" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O283" t="n">
         <v>0</v>
@@ -34548,12 +34548,12 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="G287" t="n">
@@ -34786,12 +34786,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="G289" t="n">
@@ -34905,12 +34905,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G290" t="n">

--- a/jogos_2026-03-15.xlsx
+++ b/jogos_2026-03-15.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Marconi Stallions</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Marconi Stallions</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.04</v>
+        <v>1.77</v>
       </c>
       <c r="M9" t="n">
-        <v>3.2</v>
+        <v>4.07</v>
       </c>
       <c r="N9" t="n">
-        <v>3.37</v>
+        <v>4.22</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1932,22 +1932,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Melbourne Victory FC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Macarthur</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2051,22 +2051,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Melbourne Victory FC</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Macarthur</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>4.08</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2646,22 +2646,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2884,22 +2884,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Port FC</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Port FC</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3241,22 +3241,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>5.21</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>6.82</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3360,22 +3360,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,22 +3598,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4907,22 +4907,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5621,22 +5621,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5740,22 +5740,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>4.48</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>6.17</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>4.48</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>6.17</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Kanchanaburi</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>NorthEast United</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Jamshedpur</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Kanchanaburi</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>4.53</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>NorthEast United</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Jamshedpur</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ayutthaya United</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>4.97</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Ayutthaya United</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>4.97</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9191,22 +9191,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9429,22 +9429,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9548,22 +9548,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9629,10 +9629,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB77" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>2.33</v>
+        <v>1.9</v>
       </c>
       <c r="M79" t="n">
-        <v>3.42</v>
+        <v>3.84</v>
       </c>
       <c r="N79" t="n">
-        <v>2.89</v>
+        <v>3.57</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>1.86</v>
+        <v>1.55</v>
       </c>
       <c r="AB79" t="n">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="N80" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB80" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>1.9</v>
+        <v>2.17</v>
       </c>
       <c r="M81" t="n">
-        <v>3.84</v>
+        <v>3.75</v>
       </c>
       <c r="N81" t="n">
-        <v>3.57</v>
+        <v>3</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB81" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10143,22 +10143,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10343,10 +10343,10 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB83" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11012,13 +11012,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,13 +11607,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N94" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11726,13 +11726,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="N95" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11928,22 +11928,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>2.57</v>
+        <v>4.3</v>
       </c>
       <c r="M97" t="n">
-        <v>3.3</v>
+        <v>3.94</v>
       </c>
       <c r="N97" t="n">
-        <v>3.1</v>
+        <v>1.78</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Johor Darul Ta'zim</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M99" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>4.59</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="M100" t="n">
-        <v>0</v>
+        <v>5.97</v>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>10.3</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="M105" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N105" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13035,13 +13035,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M106" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N106" t="n">
-        <v>4.59</v>
+        <v>0</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13273,13 +13273,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="M108" t="n">
-        <v>5.97</v>
+        <v>0</v>
       </c>
       <c r="N108" t="n">
-        <v>10.3</v>
+        <v>0</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13511,13 +13511,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="M110" t="n">
-        <v>5.58</v>
+        <v>0</v>
       </c>
       <c r="N110" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -13594,22 +13594,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13630,13 +13630,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>4.3</v>
+        <v>1.35</v>
       </c>
       <c r="M111" t="n">
-        <v>3.94</v>
+        <v>5.58</v>
       </c>
       <c r="N111" t="n">
-        <v>1.78</v>
+        <v>8.1</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Johor Darul Ta'zim</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13951,7 +13951,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -13987,13 +13987,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="M114" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="N114" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -14032,10 +14032,10 @@
         <v>0</v>
       </c>
       <c r="AA114" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB114" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC114" t="n">
         <v>0</v>
@@ -14070,7 +14070,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14106,13 +14106,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="M115" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N115" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -14151,10 +14151,10 @@
         <v>0</v>
       </c>
       <c r="AA115" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB115" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC115" t="n">
         <v>0</v>
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M116" t="n">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="N116" t="n">
-        <v>4.77</v>
+        <v>0</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -14270,10 +14270,10 @@
         <v>0</v>
       </c>
       <c r="AA116" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB116" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AC116" t="n">
         <v>0</v>
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14463,13 +14463,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>2.64</v>
+        <v>2.48</v>
       </c>
       <c r="M118" t="n">
-        <v>3.38</v>
+        <v>3.29</v>
       </c>
       <c r="N118" t="n">
-        <v>2.52</v>
+        <v>3.25</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -14508,10 +14508,10 @@
         <v>0</v>
       </c>
       <c r="AA118" t="n">
-        <v>2.03</v>
+        <v>2.3</v>
       </c>
       <c r="AB118" t="n">
-        <v>1.83</v>
+        <v>1.55</v>
       </c>
       <c r="AC118" t="n">
         <v>0</v>
@@ -14546,22 +14546,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14701,13 +14701,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>2.29</v>
+        <v>3.06</v>
       </c>
       <c r="M120" t="n">
-        <v>3.62</v>
+        <v>3.25</v>
       </c>
       <c r="N120" t="n">
-        <v>3.31</v>
+        <v>2.28</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -14746,10 +14746,10 @@
         <v>0</v>
       </c>
       <c r="AA120" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB120" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC120" t="n">
         <v>0</v>
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Inter Kashi</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Mumbai City</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -14939,13 +14939,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="M122" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N122" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -14984,10 +14984,10 @@
         <v>0</v>
       </c>
       <c r="AA122" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB122" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC122" t="n">
         <v>0</v>
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15177,13 +15177,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="M124" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="N124" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Inter Kashi</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Mumbai City</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15415,13 +15415,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M126" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="N126" t="n">
-        <v>0</v>
+        <v>4.77</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -15460,10 +15460,10 @@
         <v>0</v>
       </c>
       <c r="AA126" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB126" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC126" t="n">
         <v>0</v>
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15534,13 +15534,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M127" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="N127" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -15579,10 +15579,10 @@
         <v>0</v>
       </c>
       <c r="AA127" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB127" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC127" t="n">
         <v>0</v>
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15653,13 +15653,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="M128" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="N128" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -15698,10 +15698,10 @@
         <v>0</v>
       </c>
       <c r="AA128" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB128" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC128" t="n">
         <v>0</v>
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15772,13 +15772,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>3.51</v>
+        <v>2.29</v>
       </c>
       <c r="M129" t="n">
-        <v>3.38</v>
+        <v>3.62</v>
       </c>
       <c r="N129" t="n">
-        <v>2.03</v>
+        <v>3.31</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -15817,10 +15817,10 @@
         <v>0</v>
       </c>
       <c r="AA129" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB129" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC129" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M130" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="N130" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -15936,10 +15936,10 @@
         <v>0</v>
       </c>
       <c r="AA130" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB130" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC130" t="n">
         <v>0</v>
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16010,13 +16010,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M131" t="n">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="N131" t="n">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -16055,10 +16055,10 @@
         <v>0</v>
       </c>
       <c r="AA131" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB131" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC131" t="n">
         <v>0</v>
@@ -16093,22 +16093,22 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16248,13 +16248,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M133" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="N133" t="n">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -16293,10 +16293,10 @@
         <v>0</v>
       </c>
       <c r="AA133" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB133" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC133" t="n">
         <v>0</v>
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16367,13 +16367,13 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M134" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="N134" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -16412,10 +16412,10 @@
         <v>0</v>
       </c>
       <c r="AA134" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB134" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC134" t="n">
         <v>0</v>
@@ -16450,7 +16450,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16486,13 +16486,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="M135" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="N135" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -16531,10 +16531,10 @@
         <v>0</v>
       </c>
       <c r="AA135" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB135" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC135" t="n">
         <v>0</v>
@@ -16926,22 +16926,22 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -16962,13 +16962,13 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="M139" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N139" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O139" t="n">
         <v>0</v>
@@ -17045,7 +17045,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17164,22 +17164,22 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -17283,7 +17283,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17319,13 +17319,13 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="M142" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N142" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O142" t="n">
         <v>0</v>
@@ -17521,7 +17521,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17640,7 +17640,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17759,22 +17759,22 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17795,13 +17795,13 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="M146" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="N146" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O146" t="n">
         <v>0</v>
@@ -17878,7 +17878,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -17997,7 +17997,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -18007,12 +18007,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -18116,7 +18116,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18235,22 +18235,22 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -18354,7 +18354,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -18364,12 +18364,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>AR São Martinho</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -18473,7 +18473,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -18483,12 +18483,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -18592,7 +18592,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -18602,12 +18602,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Clube Oriental de Lisboa</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -18711,7 +18711,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -18721,12 +18721,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -18830,7 +18830,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -18840,12 +18840,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -18959,12 +18959,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Eléctrico</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -19078,12 +19078,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -19316,12 +19316,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Lajense</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -19425,7 +19425,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -19435,12 +19435,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Eléctrico</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19554,12 +19554,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -19663,22 +19663,22 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -19782,22 +19782,22 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -19901,22 +19901,22 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -20020,22 +20020,22 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -20139,22 +20139,22 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -20258,7 +20258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -20268,12 +20268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -20377,7 +20377,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -20387,12 +20387,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>Chaves II</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Gouveia</t>
+          <t>Mirandela</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -20506,12 +20506,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Machico</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -20615,7 +20615,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -20625,12 +20625,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Monção</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -20734,7 +20734,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -20744,12 +20744,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>AR São Martinho</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -20863,12 +20863,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Machico</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>Monção</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -20972,7 +20972,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -20982,12 +20982,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Chaves II</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Mirandela</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -21091,22 +21091,22 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -21210,22 +21210,22 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -21329,7 +21329,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -21339,12 +21339,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Clube Oriental de Lisboa</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -21448,22 +21448,22 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -21567,7 +21567,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -21577,12 +21577,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -21686,7 +21686,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -21696,12 +21696,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -21722,13 +21722,13 @@
         </is>
       </c>
       <c r="L179" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="M179" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="N179" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O179" t="n">
         <v>0</v>
@@ -21805,7 +21805,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -21815,12 +21815,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -21924,7 +21924,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -21934,12 +21934,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -22162,7 +22162,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -22172,12 +22172,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -22198,13 +22198,13 @@
         </is>
       </c>
       <c r="L183" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="M183" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="N183" t="n">
-        <v>0</v>
+        <v>6.57</v>
       </c>
       <c r="O183" t="n">
         <v>0</v>
@@ -22249,10 +22249,10 @@
         <v>0</v>
       </c>
       <c r="AC183" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD183" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AE183" t="n">
         <v>0</v>
@@ -22400,7 +22400,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -22410,12 +22410,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -22519,7 +22519,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -22529,12 +22529,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -22551,7 +22551,7 @@
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L186" t="n">
@@ -22638,7 +22638,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -22648,12 +22648,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -22670,7 +22670,7 @@
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L187" t="n">
@@ -22757,7 +22757,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -22767,12 +22767,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -22793,13 +22793,13 @@
         </is>
       </c>
       <c r="L188" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="M188" t="n">
-        <v>5.35</v>
+        <v>0</v>
       </c>
       <c r="N188" t="n">
-        <v>6.57</v>
+        <v>0</v>
       </c>
       <c r="O188" t="n">
         <v>0</v>
@@ -22844,10 +22844,10 @@
         <v>0</v>
       </c>
       <c r="AC188" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AD188" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AE188" t="n">
         <v>0</v>
@@ -22876,7 +22876,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -22886,12 +22886,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -22908,17 +22908,17 @@
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L189" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="M189" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N189" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O189" t="n">
         <v>0</v>
@@ -22957,10 +22957,10 @@
         <v>0</v>
       </c>
       <c r="AA189" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB189" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC189" t="n">
         <v>0</v>
@@ -23352,7 +23352,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -23362,12 +23362,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -23384,17 +23384,17 @@
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L193" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="M193" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N193" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O193" t="n">
         <v>0</v>
@@ -23433,10 +23433,10 @@
         <v>0</v>
       </c>
       <c r="AA193" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB193" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC193" t="n">
         <v>0</v>
@@ -23471,22 +23471,22 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -23507,13 +23507,13 @@
         </is>
       </c>
       <c r="L194" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M194" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N194" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O194" t="n">
         <v>0</v>
@@ -23590,7 +23590,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -23600,12 +23600,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -23709,7 +23709,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -23719,12 +23719,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -23828,7 +23828,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -23838,12 +23838,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -23947,7 +23947,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -23957,12 +23957,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -24066,7 +24066,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -24076,12 +24076,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -24185,22 +24185,22 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -24221,13 +24221,13 @@
         </is>
       </c>
       <c r="L200" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="M200" t="n">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="N200" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="O200" t="n">
         <v>0</v>
@@ -24304,22 +24304,22 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -24340,13 +24340,13 @@
         </is>
       </c>
       <c r="L201" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M201" t="n">
-        <v>4.19</v>
+        <v>0</v>
       </c>
       <c r="N201" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="O201" t="n">
         <v>0</v>
@@ -24391,10 +24391,10 @@
         <v>0</v>
       </c>
       <c r="AC201" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD201" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE201" t="n">
         <v>0</v>
@@ -24423,22 +24423,22 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -24455,17 +24455,17 @@
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L202" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M202" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N202" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O202" t="n">
         <v>0</v>
@@ -24542,7 +24542,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -24552,12 +24552,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -24578,13 +24578,13 @@
         </is>
       </c>
       <c r="L203" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="M203" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="N203" t="n">
-        <v>7.19</v>
+        <v>0</v>
       </c>
       <c r="O203" t="n">
         <v>0</v>
@@ -24661,7 +24661,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -24671,12 +24671,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -24697,13 +24697,13 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="M204" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="N204" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O204" t="n">
         <v>0</v>
@@ -24780,22 +24780,22 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -24816,13 +24816,13 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M205" t="n">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="N205" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="O205" t="n">
         <v>0</v>
@@ -24867,10 +24867,10 @@
         <v>0</v>
       </c>
       <c r="AC205" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD205" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE205" t="n">
         <v>0</v>
@@ -24899,7 +24899,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -24909,12 +24909,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -24931,17 +24931,17 @@
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L206" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="M206" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="N206" t="n">
-        <v>0</v>
+        <v>7.19</v>
       </c>
       <c r="O206" t="n">
         <v>0</v>
@@ -25018,7 +25018,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -25028,12 +25028,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -25054,13 +25054,13 @@
         </is>
       </c>
       <c r="L207" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="M207" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="N207" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O207" t="n">
         <v>0</v>
@@ -25137,7 +25137,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -25147,12 +25147,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -25256,7 +25256,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -25266,12 +25266,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -25375,22 +25375,22 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -25411,13 +25411,13 @@
         </is>
       </c>
       <c r="L210" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="M210" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="N210" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O210" t="n">
         <v>0</v>
@@ -25504,12 +25504,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -25623,12 +25623,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -25732,7 +25732,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -25742,12 +25742,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -25861,12 +25861,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -25887,13 +25887,13 @@
         </is>
       </c>
       <c r="L214" t="n">
-        <v>4.57</v>
+        <v>4.11</v>
       </c>
       <c r="M214" t="n">
-        <v>3.78</v>
+        <v>3.49</v>
       </c>
       <c r="N214" t="n">
-        <v>1.88</v>
+        <v>2.06</v>
       </c>
       <c r="O214" t="n">
         <v>0</v>
@@ -25932,10 +25932,10 @@
         <v>0</v>
       </c>
       <c r="AA214" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="AB214" t="n">
-        <v>1.79</v>
+        <v>1.66</v>
       </c>
       <c r="AC214" t="n">
         <v>0</v>
@@ -26099,12 +26099,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -26125,13 +26125,13 @@
         </is>
       </c>
       <c r="L216" t="n">
-        <v>4.11</v>
+        <v>4.57</v>
       </c>
       <c r="M216" t="n">
-        <v>3.49</v>
+        <v>3.78</v>
       </c>
       <c r="N216" t="n">
-        <v>2.06</v>
+        <v>1.88</v>
       </c>
       <c r="O216" t="n">
         <v>0</v>
@@ -26170,10 +26170,10 @@
         <v>0</v>
       </c>
       <c r="AA216" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AB216" t="n">
-        <v>1.66</v>
+        <v>1.79</v>
       </c>
       <c r="AC216" t="n">
         <v>0</v>
@@ -26208,7 +26208,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -26218,12 +26218,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -26244,13 +26244,13 @@
         </is>
       </c>
       <c r="L217" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="M217" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="N217" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="O217" t="n">
         <v>0</v>
@@ -26289,10 +26289,10 @@
         <v>0</v>
       </c>
       <c r="AA217" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB217" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AC217" t="n">
         <v>0</v>
@@ -26327,7 +26327,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -26337,12 +26337,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -26363,13 +26363,13 @@
         </is>
       </c>
       <c r="L218" t="n">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="M218" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="N218" t="n">
-        <v>2.93</v>
+        <v>2.32</v>
       </c>
       <c r="O218" t="n">
         <v>0</v>
@@ -26456,12 +26456,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -26565,7 +26565,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -26575,12 +26575,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -26601,13 +26601,13 @@
         </is>
       </c>
       <c r="L220" t="n">
-        <v>1.42</v>
+        <v>2.3</v>
       </c>
       <c r="M220" t="n">
-        <v>5.28</v>
+        <v>3.2</v>
       </c>
       <c r="N220" t="n">
-        <v>8.1</v>
+        <v>2.93</v>
       </c>
       <c r="O220" t="n">
         <v>0</v>
@@ -26652,10 +26652,10 @@
         <v>0</v>
       </c>
       <c r="AC220" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD220" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE220" t="n">
         <v>0</v>
@@ -26684,7 +26684,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -26694,12 +26694,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -26803,7 +26803,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -26813,12 +26813,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -26922,7 +26922,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -26932,12 +26932,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -27041,7 +27041,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -27051,12 +27051,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -27160,7 +27160,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -27170,12 +27170,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -27196,13 +27196,13 @@
         </is>
       </c>
       <c r="L225" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="M225" t="n">
-        <v>0</v>
+        <v>5.28</v>
       </c>
       <c r="N225" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="O225" t="n">
         <v>0</v>
@@ -27247,10 +27247,10 @@
         <v>0</v>
       </c>
       <c r="AC225" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD225" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE225" t="n">
         <v>0</v>
@@ -27279,7 +27279,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -27289,12 +27289,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -27315,13 +27315,13 @@
         </is>
       </c>
       <c r="L226" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="M226" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N226" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="O226" t="n">
         <v>0</v>
@@ -27398,7 +27398,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -27408,12 +27408,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -27434,13 +27434,13 @@
         </is>
       </c>
       <c r="L227" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="M227" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="N227" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="O227" t="n">
         <v>0</v>
@@ -27479,10 +27479,10 @@
         <v>0</v>
       </c>
       <c r="AA227" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB227" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC227" t="n">
         <v>0</v>
@@ -27636,7 +27636,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -27646,12 +27646,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -27672,13 +27672,13 @@
         </is>
       </c>
       <c r="L229" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="M229" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="N229" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O229" t="n">
         <v>0</v>
@@ -27717,10 +27717,10 @@
         <v>0</v>
       </c>
       <c r="AA229" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB229" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC229" t="n">
         <v>0</v>
@@ -27755,7 +27755,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -27765,12 +27765,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -27874,22 +27874,22 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -27993,22 +27993,22 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -28112,22 +28112,22 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -28231,22 +28231,22 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -28267,13 +28267,13 @@
         </is>
       </c>
       <c r="L234" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="M234" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="N234" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O234" t="n">
         <v>0</v>
@@ -28312,10 +28312,10 @@
         <v>0</v>
       </c>
       <c r="AA234" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB234" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC234" t="n">
         <v>0</v>
@@ -28350,7 +28350,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -28360,12 +28360,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -28707,7 +28707,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -28717,12 +28717,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -28743,13 +28743,13 @@
         </is>
       </c>
       <c r="L238" t="n">
-        <v>0</v>
+        <v>6.71</v>
       </c>
       <c r="M238" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N238" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="O238" t="n">
         <v>0</v>
@@ -28826,7 +28826,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -28836,12 +28836,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -28862,13 +28862,13 @@
         </is>
       </c>
       <c r="L239" t="n">
-        <v>6.71</v>
+        <v>0</v>
       </c>
       <c r="M239" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="N239" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="O239" t="n">
         <v>0</v>
@@ -28945,7 +28945,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -28955,12 +28955,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -28981,13 +28981,13 @@
         </is>
       </c>
       <c r="L240" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="M240" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="N240" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="O240" t="n">
         <v>0</v>
@@ -29064,7 +29064,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -29074,12 +29074,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -29100,13 +29100,13 @@
         </is>
       </c>
       <c r="L241" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="M241" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="N241" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="O241" t="n">
         <v>0</v>
@@ -29183,7 +29183,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -29193,12 +29193,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -29421,7 +29421,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -29431,12 +29431,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -29540,22 +29540,22 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -29659,22 +29659,22 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -29778,22 +29778,22 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -29814,13 +29814,13 @@
         </is>
       </c>
       <c r="L247" t="n">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="M247" t="n">
-        <v>3.58</v>
+        <v>4.01</v>
       </c>
       <c r="N247" t="n">
-        <v>4.09</v>
+        <v>4.3</v>
       </c>
       <c r="O247" t="n">
         <v>0</v>
@@ -29859,10 +29859,10 @@
         <v>0</v>
       </c>
       <c r="AA247" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AB247" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC247" t="n">
         <v>0</v>
@@ -29897,22 +29897,22 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -29933,13 +29933,13 @@
         </is>
       </c>
       <c r="L248" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="M248" t="n">
-        <v>4.01</v>
+        <v>3.58</v>
       </c>
       <c r="N248" t="n">
-        <v>4.3</v>
+        <v>4.09</v>
       </c>
       <c r="O248" t="n">
         <v>0</v>
@@ -29978,10 +29978,10 @@
         <v>0</v>
       </c>
       <c r="AA248" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB248" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC248" t="n">
         <v>0</v>
@@ -30016,7 +30016,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -30026,12 +30026,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -30052,13 +30052,13 @@
         </is>
       </c>
       <c r="L249" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="M249" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="N249" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="O249" t="n">
         <v>0</v>
@@ -30103,10 +30103,10 @@
         <v>0</v>
       </c>
       <c r="AC249" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD249" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AE249" t="n">
         <v>0</v>
@@ -30135,7 +30135,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -30145,12 +30145,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -30254,7 +30254,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -30264,12 +30264,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -30373,7 +30373,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -30383,12 +30383,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -30492,7 +30492,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -30502,12 +30502,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -30730,7 +30730,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -30740,12 +30740,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -30766,13 +30766,13 @@
         </is>
       </c>
       <c r="L255" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="M255" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="N255" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="O255" t="n">
         <v>0</v>
@@ -30817,10 +30817,10 @@
         <v>0</v>
       </c>
       <c r="AC255" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD255" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AE255" t="n">
         <v>0</v>
@@ -30849,7 +30849,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -30859,12 +30859,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -30885,10 +30885,10 @@
         </is>
       </c>
       <c r="L256" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="M256" t="n">
-        <v>2.88</v>
+        <v>3.42</v>
       </c>
       <c r="N256" t="n">
         <v>3.4</v>
@@ -30930,10 +30930,10 @@
         <v>0</v>
       </c>
       <c r="AA256" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB256" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC256" t="n">
         <v>0</v>
@@ -31087,7 +31087,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -31097,12 +31097,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -31123,13 +31123,13 @@
         </is>
       </c>
       <c r="L258" t="n">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="M258" t="n">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="N258" t="n">
-        <v>4.2</v>
+        <v>3.24</v>
       </c>
       <c r="O258" t="n">
         <v>0</v>
@@ -31168,10 +31168,10 @@
         <v>0</v>
       </c>
       <c r="AA258" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB258" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC258" t="n">
         <v>0</v>
@@ -31325,7 +31325,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -31335,12 +31335,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -31361,13 +31361,13 @@
         </is>
       </c>
       <c r="L260" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M260" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="N260" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O260" t="n">
         <v>0</v>
@@ -31406,10 +31406,10 @@
         <v>0</v>
       </c>
       <c r="AA260" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB260" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC260" t="n">
         <v>0</v>
@@ -31444,7 +31444,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -31454,12 +31454,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Connecticut United</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -31480,13 +31480,13 @@
         </is>
       </c>
       <c r="L261" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M261" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="N261" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O261" t="n">
         <v>0</v>
@@ -31563,7 +31563,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -31573,12 +31573,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -31599,13 +31599,13 @@
         </is>
       </c>
       <c r="L262" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M262" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="N262" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O262" t="n">
         <v>0</v>
@@ -31682,7 +31682,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -31692,12 +31692,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Connecticut United</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -31718,13 +31718,13 @@
         </is>
       </c>
       <c r="L263" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M263" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N263" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="O263" t="n">
         <v>0</v>
@@ -31763,10 +31763,10 @@
         <v>0</v>
       </c>
       <c r="AA263" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB263" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC263" t="n">
         <v>0</v>
@@ -32396,7 +32396,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -32406,12 +32406,12 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G269" t="n">
@@ -32432,13 +32432,13 @@
         </is>
       </c>
       <c r="L269" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M269" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N269" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="O269" t="n">
         <v>0</v>
@@ -32515,22 +32515,22 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="G270" t="n">
@@ -32634,22 +32634,22 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G271" t="n">
@@ -32753,7 +32753,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -32763,12 +32763,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G272" t="n">
@@ -32789,13 +32789,13 @@
         </is>
       </c>
       <c r="L272" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M272" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N272" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="O272" t="n">
         <v>0</v>
@@ -32991,22 +32991,22 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G274" t="n">
@@ -33027,13 +33027,13 @@
         </is>
       </c>
       <c r="L274" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="M274" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="N274" t="n">
-        <v>0</v>
+        <v>6.39</v>
       </c>
       <c r="O274" t="n">
         <v>0</v>
@@ -33078,10 +33078,10 @@
         <v>0</v>
       </c>
       <c r="AC274" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD274" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE274" t="n">
         <v>0</v>
@@ -33110,22 +33110,22 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G275" t="n">
@@ -33146,13 +33146,13 @@
         </is>
       </c>
       <c r="L275" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="M275" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="N275" t="n">
-        <v>6.39</v>
+        <v>0</v>
       </c>
       <c r="O275" t="n">
         <v>0</v>
@@ -33197,10 +33197,10 @@
         <v>0</v>
       </c>
       <c r="AC275" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD275" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE275" t="n">
         <v>0</v>
@@ -33229,22 +33229,22 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G276" t="n">
@@ -33265,13 +33265,13 @@
         </is>
       </c>
       <c r="L276" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M276" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N276" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O276" t="n">
         <v>0</v>
@@ -33348,7 +33348,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -33358,12 +33358,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="G277" t="n">
@@ -33477,12 +33477,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G278" t="n">
@@ -33586,22 +33586,22 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G279" t="n">
@@ -33622,13 +33622,13 @@
         </is>
       </c>
       <c r="L279" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M279" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N279" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O279" t="n">
         <v>0</v>
@@ -33715,12 +33715,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G280" t="n">
@@ -33943,7 +33943,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -33953,12 +33953,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G282" t="n">
@@ -33979,13 +33979,13 @@
         </is>
       </c>
       <c r="L282" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M282" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="N282" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O282" t="n">
         <v>0</v>
@@ -34062,7 +34062,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -34072,12 +34072,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="G283" t="n">
@@ -34098,13 +34098,13 @@
         </is>
       </c>
       <c r="L283" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M283" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="N283" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O283" t="n">
         <v>0</v>
@@ -34181,7 +34181,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -34191,12 +34191,12 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Real Monarchs</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Los Angeles II</t>
         </is>
       </c>
       <c r="G284" t="n">
@@ -34217,13 +34217,13 @@
         </is>
       </c>
       <c r="L284" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="M284" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="N284" t="n">
-        <v>6.69</v>
+        <v>0</v>
       </c>
       <c r="O284" t="n">
         <v>0</v>
@@ -34262,10 +34262,10 @@
         <v>0</v>
       </c>
       <c r="AA284" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB284" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC284" t="n">
         <v>0</v>
@@ -34310,12 +34310,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G285" t="n">
@@ -34336,13 +34336,13 @@
         </is>
       </c>
       <c r="L285" t="n">
-        <v>1.83</v>
+        <v>1.51</v>
       </c>
       <c r="M285" t="n">
-        <v>3.46</v>
+        <v>4.32</v>
       </c>
       <c r="N285" t="n">
-        <v>4.84</v>
+        <v>6.69</v>
       </c>
       <c r="O285" t="n">
         <v>0</v>
@@ -34381,10 +34381,10 @@
         <v>0</v>
       </c>
       <c r="AA285" t="n">
-        <v>2.25</v>
+        <v>1.65</v>
       </c>
       <c r="AB285" t="n">
-        <v>1.57</v>
+        <v>2.1</v>
       </c>
       <c r="AC285" t="n">
         <v>0</v>
@@ -34419,7 +34419,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -34429,12 +34429,12 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Real Monarchs</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Los Angeles II</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G286" t="n">
@@ -34455,13 +34455,13 @@
         </is>
       </c>
       <c r="L286" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M286" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="N286" t="n">
-        <v>0</v>
+        <v>4.84</v>
       </c>
       <c r="O286" t="n">
         <v>0</v>
@@ -34500,10 +34500,10 @@
         <v>0</v>
       </c>
       <c r="AA286" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB286" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC286" t="n">
         <v>0</v>
@@ -34538,7 +34538,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -34548,12 +34548,12 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G287" t="n">
@@ -34574,13 +34574,13 @@
         </is>
       </c>
       <c r="L287" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="M287" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="N287" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="O287" t="n">
         <v>0</v>
@@ -34619,10 +34619,10 @@
         <v>0</v>
       </c>
       <c r="AA287" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB287" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AC287" t="n">
         <v>0</v>
@@ -34667,12 +34667,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Atlanta United II</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G288" t="n">
@@ -34786,12 +34786,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="G289" t="n">
@@ -34905,12 +34905,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>Atlanta United II</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="G290" t="n">
@@ -35014,7 +35014,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -35024,12 +35024,12 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="G291" t="n">
@@ -35050,13 +35050,13 @@
         </is>
       </c>
       <c r="L291" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="M291" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="N291" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="O291" t="n">
         <v>0</v>
@@ -35095,10 +35095,10 @@
         <v>0</v>
       </c>
       <c r="AA291" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB291" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AC291" t="n">
         <v>0</v>
@@ -35490,7 +35490,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -35500,12 +35500,12 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G295" t="n">
@@ -35526,13 +35526,13 @@
         </is>
       </c>
       <c r="L295" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="M295" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N295" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="O295" t="n">
         <v>0</v>
@@ -35571,10 +35571,10 @@
         <v>0</v>
       </c>
       <c r="AA295" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB295" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC295" t="n">
         <v>0</v>
@@ -35619,12 +35619,12 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G296" t="n">
@@ -35645,13 +35645,13 @@
         </is>
       </c>
       <c r="L296" t="n">
-        <v>2.61</v>
+        <v>1.7</v>
       </c>
       <c r="M296" t="n">
-        <v>3.23</v>
+        <v>3.79</v>
       </c>
       <c r="N296" t="n">
-        <v>2.86</v>
+        <v>5.3</v>
       </c>
       <c r="O296" t="n">
         <v>0</v>
@@ -35690,10 +35690,10 @@
         <v>0</v>
       </c>
       <c r="AA296" t="n">
-        <v>2.3</v>
+        <v>1.93</v>
       </c>
       <c r="AB296" t="n">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="AC296" t="n">
         <v>0</v>
@@ -35728,7 +35728,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -35738,12 +35738,12 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G297" t="n">
@@ -35764,13 +35764,13 @@
         </is>
       </c>
       <c r="L297" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M297" t="n">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="N297" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="O297" t="n">
         <v>0</v>
@@ -35809,10 +35809,10 @@
         <v>0</v>
       </c>
       <c r="AA297" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB297" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC297" t="n">
         <v>0</v>

--- a/jogos_2026-03-15.xlsx
+++ b/jogos_2026-03-15.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.77</v>
+        <v>2.04</v>
       </c>
       <c r="M9" t="n">
-        <v>4.07</v>
+        <v>3.2</v>
       </c>
       <c r="N9" t="n">
-        <v>4.22</v>
+        <v>3.37</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>4.07</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="M12" t="n">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="N12" t="n">
-        <v>3.37</v>
+        <v>3.72</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1932,22 +1932,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Melbourne Victory FC</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Macarthur</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>4.08</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2051,22 +2051,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Melbourne Victory FC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Macarthur</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Port FC</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,22 +3241,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.41</v>
+        <v>2.99</v>
       </c>
       <c r="M24" t="n">
-        <v>5.21</v>
+        <v>3.62</v>
       </c>
       <c r="N24" t="n">
-        <v>6.82</v>
+        <v>2.48</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3598,22 +3598,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.99</v>
+        <v>2.09</v>
       </c>
       <c r="M31" t="n">
-        <v>3.62</v>
+        <v>3.25</v>
       </c>
       <c r="N31" t="n">
-        <v>2.48</v>
+        <v>3.19</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,10 +4155,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4550,22 +4550,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Port FC</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4907,22 +4907,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,22 +5502,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5740,22 +5740,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.9</v>
+        <v>1.41</v>
       </c>
       <c r="M45" t="n">
-        <v>3.42</v>
+        <v>5.21</v>
       </c>
       <c r="N45" t="n">
-        <v>3.92</v>
+        <v>6.82</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>4.48</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>6.17</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>4.48</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>6.17</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Kanchanaburi</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>4.53</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6692,22 +6692,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>NorthEast United</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Jamshedpur</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6886,10 +6886,10 @@
         <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z54" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA54" t="n">
         <v>0</v>
@@ -6930,22 +6930,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7005,10 +7005,10 @@
         <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z55" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA55" t="n">
         <v>0</v>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>NorthEast United</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Jamshedpur</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Kanchanaburi</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>5.86</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7725,10 +7725,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB61" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>10.9</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>4.96</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8082,10 +8082,10 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB64" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ayutthaya United</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>4.97</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Ayutthaya United</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>4.97</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9191,22 +9191,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9429,22 +9429,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>2.06</v>
+        <v>1.4</v>
       </c>
       <c r="M77" t="n">
-        <v>3.56</v>
+        <v>4.3</v>
       </c>
       <c r="N77" t="n">
-        <v>3.32</v>
+        <v>7.9</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9629,10 +9629,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -9667,22 +9667,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9786,22 +9786,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="N79" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB79" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="M80" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB80" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -10143,22 +10143,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10224,10 +10224,10 @@
         <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB82" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC82" t="n">
         <v>0</v>
@@ -10262,22 +10262,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Balestier Khalsa</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Home United</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10343,10 +10343,10 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB83" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -10381,22 +10381,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10417,13 +10417,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -10500,22 +10500,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Balestier Khalsa</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Home United</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10581,10 +10581,10 @@
         <v>0</v>
       </c>
       <c r="AA85" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB85" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC85" t="n">
         <v>0</v>
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10655,13 +10655,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>5.01</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N88" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11012,13 +11012,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="N89" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11131,13 +11131,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11726,13 +11726,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M95" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11928,22 +11928,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>4.3</v>
+        <v>1.85</v>
       </c>
       <c r="M97" t="n">
-        <v>3.94</v>
+        <v>2.9</v>
       </c>
       <c r="N97" t="n">
-        <v>1.78</v>
+        <v>4.59</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M99" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N99" t="n">
-        <v>4.59</v>
+        <v>0</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>1.29</v>
+        <v>2.57</v>
       </c>
       <c r="M100" t="n">
-        <v>5.97</v>
+        <v>3.3</v>
       </c>
       <c r="N100" t="n">
-        <v>10.3</v>
+        <v>3.1</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="M104" t="n">
-        <v>0</v>
+        <v>5.97</v>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>10.3</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>2.57</v>
+        <v>1.35</v>
       </c>
       <c r="M105" t="n">
-        <v>3.3</v>
+        <v>5.58</v>
       </c>
       <c r="N105" t="n">
-        <v>3.1</v>
+        <v>8.1</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12999,22 +12999,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13035,13 +13035,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="M106" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="N106" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Johor Darul Ta'zim</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13630,13 +13630,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="M111" t="n">
-        <v>5.58</v>
+        <v>0</v>
       </c>
       <c r="N111" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Johor Darul Ta'zim</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13951,7 +13951,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -13987,13 +13987,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="M114" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="N114" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -14032,10 +14032,10 @@
         <v>0</v>
       </c>
       <c r="AA114" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB114" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC114" t="n">
         <v>0</v>
@@ -14070,7 +14070,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14106,13 +14106,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="M115" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N115" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -14151,10 +14151,10 @@
         <v>0</v>
       </c>
       <c r="AA115" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB115" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC115" t="n">
         <v>0</v>
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="M116" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N116" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -14270,10 +14270,10 @@
         <v>0</v>
       </c>
       <c r="AA116" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB116" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC116" t="n">
         <v>0</v>
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14344,13 +14344,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="M117" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="N117" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -14389,10 +14389,10 @@
         <v>0</v>
       </c>
       <c r="AA117" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB117" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC117" t="n">
         <v>0</v>
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14463,13 +14463,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>2.48</v>
+        <v>1.79</v>
       </c>
       <c r="M118" t="n">
-        <v>3.29</v>
+        <v>4.06</v>
       </c>
       <c r="N118" t="n">
-        <v>3.25</v>
+        <v>4.77</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -14508,10 +14508,10 @@
         <v>0</v>
       </c>
       <c r="AA118" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="AB118" t="n">
-        <v>1.55</v>
+        <v>1.97</v>
       </c>
       <c r="AC118" t="n">
         <v>0</v>
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Inter Kashi</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Mumbai City</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14701,13 +14701,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="M120" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N120" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -14939,13 +14939,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="M122" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="N122" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -14984,10 +14984,10 @@
         <v>0</v>
       </c>
       <c r="AA122" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB122" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC122" t="n">
         <v>0</v>
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15177,13 +15177,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="M124" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="N124" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Inter Kashi</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Mumbai City</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15415,13 +15415,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>1.79</v>
+        <v>2.19</v>
       </c>
       <c r="M126" t="n">
-        <v>4.06</v>
+        <v>3.58</v>
       </c>
       <c r="N126" t="n">
-        <v>4.77</v>
+        <v>3.58</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -15460,10 +15460,10 @@
         <v>0</v>
       </c>
       <c r="AA126" t="n">
-        <v>1.8</v>
+        <v>1.96</v>
       </c>
       <c r="AB126" t="n">
-        <v>1.97</v>
+        <v>1.75</v>
       </c>
       <c r="AC126" t="n">
         <v>0</v>
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15534,13 +15534,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M127" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="N127" t="n">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -15579,10 +15579,10 @@
         <v>0</v>
       </c>
       <c r="AA127" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB127" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC127" t="n">
         <v>0</v>
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15736,22 +15736,22 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15772,13 +15772,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="M129" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="N129" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -15817,10 +15817,10 @@
         <v>0</v>
       </c>
       <c r="AA129" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB129" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC129" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>2.2</v>
+        <v>3.51</v>
       </c>
       <c r="M130" t="n">
-        <v>2.92</v>
+        <v>3.38</v>
       </c>
       <c r="N130" t="n">
-        <v>3.69</v>
+        <v>2.03</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -15936,10 +15936,10 @@
         <v>0</v>
       </c>
       <c r="AA130" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB130" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC130" t="n">
         <v>0</v>
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16010,13 +16010,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M131" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="N131" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -16055,10 +16055,10 @@
         <v>0</v>
       </c>
       <c r="AA131" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB131" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC131" t="n">
         <v>0</v>
@@ -16093,22 +16093,22 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16129,13 +16129,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="M132" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N132" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16248,13 +16248,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M133" t="n">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="N133" t="n">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -16293,10 +16293,10 @@
         <v>0</v>
       </c>
       <c r="AA133" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB133" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC133" t="n">
         <v>0</v>
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16367,13 +16367,13 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="M134" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="N134" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -16412,10 +16412,10 @@
         <v>0</v>
       </c>
       <c r="AA134" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB134" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC134" t="n">
         <v>0</v>
@@ -16450,7 +16450,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16486,13 +16486,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="M135" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="N135" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -16531,10 +16531,10 @@
         <v>0</v>
       </c>
       <c r="AA135" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB135" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC135" t="n">
         <v>0</v>
@@ -16926,7 +16926,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Machico</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -16962,13 +16962,13 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="M139" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N139" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O139" t="n">
         <v>0</v>
@@ -17045,7 +17045,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>Lajense</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -17174,12 +17174,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Chaves II</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Mirandela</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -17283,7 +17283,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17402,7 +17402,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17438,13 +17438,13 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="M143" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="N143" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O143" t="n">
         <v>0</v>
@@ -17521,7 +17521,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17640,7 +17640,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>Clube Oriental de Lisboa</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17759,7 +17759,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17795,13 +17795,13 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>2.26</v>
+        <v>1.87</v>
       </c>
       <c r="M146" t="n">
-        <v>3.16</v>
+        <v>3.3</v>
       </c>
       <c r="N146" t="n">
-        <v>3.3</v>
+        <v>4.21</v>
       </c>
       <c r="O146" t="n">
         <v>0</v>
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -17997,7 +17997,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -18007,12 +18007,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -18116,22 +18116,22 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18235,7 +18235,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -18245,12 +18245,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -18354,22 +18354,22 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>AR São Martinho</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -18473,22 +18473,22 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -18592,7 +18592,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -18602,12 +18602,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -18711,7 +18711,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -18721,12 +18721,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>AR São Martinho</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -18830,7 +18830,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -18840,12 +18840,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>Eléctrico</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -18949,7 +18949,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -18959,12 +18959,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Eléctrico</t>
+          <t>Monção</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -19068,7 +19068,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -19078,12 +19078,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -19104,13 +19104,13 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="M157" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N157" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="O157" t="n">
         <v>0</v>
@@ -19187,7 +19187,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -19306,7 +19306,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -19316,12 +19316,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -19425,7 +19425,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -19435,12 +19435,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19544,7 +19544,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -19554,12 +19554,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -19663,22 +19663,22 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -19782,22 +19782,22 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -19818,13 +19818,13 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="M163" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N163" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O163" t="n">
         <v>0</v>
@@ -19901,22 +19901,22 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -20020,22 +20020,22 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -20139,7 +20139,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -20149,12 +20149,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -20258,7 +20258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -20268,12 +20268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -20377,7 +20377,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -20387,12 +20387,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Chaves II</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Mirandela</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -20496,7 +20496,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -20506,12 +20506,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Machico</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -20615,22 +20615,22 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -20734,7 +20734,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -20744,12 +20744,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Gouveia</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -20853,7 +20853,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -20863,12 +20863,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Monção</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -20972,7 +20972,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -20982,12 +20982,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -21210,7 +21210,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -21220,12 +21220,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -21246,13 +21246,13 @@
         </is>
       </c>
       <c r="L175" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M175" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N175" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O175" t="n">
         <v>0</v>
@@ -21329,7 +21329,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -21339,12 +21339,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Clube Oriental de Lisboa</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -21448,7 +21448,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -21458,12 +21458,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -21577,12 +21577,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -21686,7 +21686,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -21696,12 +21696,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -21841,13 +21841,13 @@
         </is>
       </c>
       <c r="L180" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M180" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="N180" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="O180" t="n">
         <v>0</v>
@@ -21886,10 +21886,10 @@
         <v>0</v>
       </c>
       <c r="AA180" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB180" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC180" t="n">
         <v>0</v>
@@ -22043,7 +22043,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -22053,12 +22053,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -22079,13 +22079,13 @@
         </is>
       </c>
       <c r="L182" t="n">
-        <v>2.07</v>
+        <v>5.04</v>
       </c>
       <c r="M182" t="n">
-        <v>3.24</v>
+        <v>3.62</v>
       </c>
       <c r="N182" t="n">
-        <v>3.62</v>
+        <v>1.8</v>
       </c>
       <c r="O182" t="n">
         <v>0</v>
@@ -22162,7 +22162,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -22172,12 +22172,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -22198,13 +22198,13 @@
         </is>
       </c>
       <c r="L183" t="n">
-        <v>1.37</v>
+        <v>2.07</v>
       </c>
       <c r="M183" t="n">
-        <v>5.35</v>
+        <v>3.24</v>
       </c>
       <c r="N183" t="n">
-        <v>6.57</v>
+        <v>3.62</v>
       </c>
       <c r="O183" t="n">
         <v>0</v>
@@ -22249,10 +22249,10 @@
         <v>0</v>
       </c>
       <c r="AC183" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AD183" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AE183" t="n">
         <v>0</v>
@@ -22281,7 +22281,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -22291,12 +22291,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -22317,13 +22317,13 @@
         </is>
       </c>
       <c r="L184" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="M184" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="N184" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="O184" t="n">
         <v>0</v>
@@ -22400,7 +22400,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -22410,12 +22410,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -22436,13 +22436,13 @@
         </is>
       </c>
       <c r="L185" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="M185" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="N185" t="n">
-        <v>0</v>
+        <v>6.57</v>
       </c>
       <c r="O185" t="n">
         <v>0</v>
@@ -22487,10 +22487,10 @@
         <v>0</v>
       </c>
       <c r="AC185" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD185" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AE185" t="n">
         <v>0</v>
@@ -22519,7 +22519,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -22529,12 +22529,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -22555,13 +22555,13 @@
         </is>
       </c>
       <c r="L186" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="M186" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="N186" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="O186" t="n">
         <v>0</v>
@@ -22638,7 +22638,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -22648,12 +22648,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -22670,17 +22670,17 @@
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L187" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="M187" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N187" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="O187" t="n">
         <v>0</v>
@@ -22757,7 +22757,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -22767,12 +22767,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -22789,7 +22789,7 @@
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L188" t="n">
@@ -22876,7 +22876,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -22886,12 +22886,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -22908,17 +22908,17 @@
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L189" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="M189" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N189" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O189" t="n">
         <v>0</v>
@@ -22957,10 +22957,10 @@
         <v>0</v>
       </c>
       <c r="AA189" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB189" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC189" t="n">
         <v>0</v>
@@ -22995,7 +22995,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -23005,12 +23005,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -23031,13 +23031,13 @@
         </is>
       </c>
       <c r="L190" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="M190" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N190" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O190" t="n">
         <v>0</v>
@@ -23076,10 +23076,10 @@
         <v>0</v>
       </c>
       <c r="AA190" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB190" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC190" t="n">
         <v>0</v>
@@ -23124,12 +23124,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -23243,12 +23243,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -23352,7 +23352,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -23362,12 +23362,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -23384,7 +23384,7 @@
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L193" t="n">
@@ -23471,22 +23471,22 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -23507,13 +23507,13 @@
         </is>
       </c>
       <c r="L194" t="n">
-        <v>1.95</v>
+        <v>3.16</v>
       </c>
       <c r="M194" t="n">
-        <v>3.65</v>
+        <v>3.44</v>
       </c>
       <c r="N194" t="n">
-        <v>3.85</v>
+        <v>2.45</v>
       </c>
       <c r="O194" t="n">
         <v>0</v>
@@ -23709,7 +23709,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -23719,12 +23719,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -23828,22 +23828,22 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -23864,13 +23864,13 @@
         </is>
       </c>
       <c r="L197" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="M197" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="N197" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O197" t="n">
         <v>0</v>
@@ -23947,7 +23947,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -23957,12 +23957,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -23983,13 +23983,13 @@
         </is>
       </c>
       <c r="L198" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="M198" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="N198" t="n">
-        <v>0</v>
+        <v>7.19</v>
       </c>
       <c r="O198" t="n">
         <v>0</v>
@@ -24076,12 +24076,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -24185,22 +24185,22 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -24221,13 +24221,13 @@
         </is>
       </c>
       <c r="L200" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M200" t="n">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="N200" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="O200" t="n">
         <v>0</v>
@@ -24272,10 +24272,10 @@
         <v>0</v>
       </c>
       <c r="AC200" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD200" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE200" t="n">
         <v>0</v>
@@ -24304,7 +24304,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -24314,12 +24314,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -24336,7 +24336,7 @@
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L201" t="n">
@@ -24423,22 +24423,22 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -24455,17 +24455,17 @@
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L202" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M202" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N202" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O202" t="n">
         <v>0</v>
@@ -24542,7 +24542,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -24552,12 +24552,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -24661,7 +24661,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -24671,12 +24671,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -24697,13 +24697,13 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="M204" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="N204" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O204" t="n">
         <v>0</v>
@@ -24780,22 +24780,22 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -24816,13 +24816,13 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M205" t="n">
-        <v>4.19</v>
+        <v>0</v>
       </c>
       <c r="N205" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="O205" t="n">
         <v>0</v>
@@ -24867,10 +24867,10 @@
         <v>0</v>
       </c>
       <c r="AC205" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD205" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE205" t="n">
         <v>0</v>
@@ -24899,7 +24899,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -24909,12 +24909,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -24935,13 +24935,13 @@
         </is>
       </c>
       <c r="L206" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="M206" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="N206" t="n">
-        <v>7.19</v>
+        <v>0</v>
       </c>
       <c r="O206" t="n">
         <v>0</v>
@@ -25018,7 +25018,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -25028,12 +25028,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -25147,12 +25147,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -25266,12 +25266,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -25375,22 +25375,22 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -25411,13 +25411,13 @@
         </is>
       </c>
       <c r="L210" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="M210" t="n">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="N210" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="O210" t="n">
         <v>0</v>
@@ -25504,12 +25504,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -25613,7 +25613,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -25623,12 +25623,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -25742,12 +25742,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -25861,12 +25861,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -25887,13 +25887,13 @@
         </is>
       </c>
       <c r="L214" t="n">
-        <v>4.11</v>
+        <v>4.57</v>
       </c>
       <c r="M214" t="n">
-        <v>3.49</v>
+        <v>3.78</v>
       </c>
       <c r="N214" t="n">
-        <v>2.06</v>
+        <v>1.88</v>
       </c>
       <c r="O214" t="n">
         <v>0</v>
@@ -25932,10 +25932,10 @@
         <v>0</v>
       </c>
       <c r="AA214" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AB214" t="n">
-        <v>1.66</v>
+        <v>1.79</v>
       </c>
       <c r="AC214" t="n">
         <v>0</v>
@@ -25970,7 +25970,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -25980,12 +25980,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -26006,13 +26006,13 @@
         </is>
       </c>
       <c r="L215" t="n">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="M215" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="N215" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="O215" t="n">
         <v>0</v>
@@ -26051,10 +26051,10 @@
         <v>0</v>
       </c>
       <c r="AA215" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB215" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC215" t="n">
         <v>0</v>
@@ -26089,7 +26089,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -26099,12 +26099,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -26125,55 +26125,55 @@
         </is>
       </c>
       <c r="L216" t="n">
-        <v>4.57</v>
+        <v>1.77</v>
       </c>
       <c r="M216" t="n">
-        <v>3.78</v>
+        <v>3.72</v>
       </c>
       <c r="N216" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="O216" t="n">
+        <v>0</v>
+      </c>
+      <c r="P216" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q216" t="n">
+        <v>0</v>
+      </c>
+      <c r="R216" t="n">
+        <v>0</v>
+      </c>
+      <c r="S216" t="n">
+        <v>0</v>
+      </c>
+      <c r="T216" t="n">
+        <v>0</v>
+      </c>
+      <c r="U216" t="n">
+        <v>0</v>
+      </c>
+      <c r="V216" t="n">
+        <v>0</v>
+      </c>
+      <c r="W216" t="n">
+        <v>0</v>
+      </c>
+      <c r="X216" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y216" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z216" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA216" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AB216" t="n">
         <v>1.88</v>
-      </c>
-      <c r="O216" t="n">
-        <v>0</v>
-      </c>
-      <c r="P216" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q216" t="n">
-        <v>0</v>
-      </c>
-      <c r="R216" t="n">
-        <v>0</v>
-      </c>
-      <c r="S216" t="n">
-        <v>0</v>
-      </c>
-      <c r="T216" t="n">
-        <v>0</v>
-      </c>
-      <c r="U216" t="n">
-        <v>0</v>
-      </c>
-      <c r="V216" t="n">
-        <v>0</v>
-      </c>
-      <c r="W216" t="n">
-        <v>0</v>
-      </c>
-      <c r="X216" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y216" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z216" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA216" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AB216" t="n">
-        <v>1.79</v>
       </c>
       <c r="AC216" t="n">
         <v>0</v>
@@ -26208,7 +26208,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -26218,12 +26218,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -26244,13 +26244,13 @@
         </is>
       </c>
       <c r="L217" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="M217" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N217" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O217" t="n">
         <v>0</v>
@@ -26327,7 +26327,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -26337,12 +26337,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -26363,13 +26363,13 @@
         </is>
       </c>
       <c r="L218" t="n">
-        <v>2.63</v>
+        <v>2.3</v>
       </c>
       <c r="M218" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="N218" t="n">
-        <v>2.32</v>
+        <v>2.93</v>
       </c>
       <c r="O218" t="n">
         <v>0</v>
@@ -26446,7 +26446,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -26456,12 +26456,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -26565,7 +26565,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -26575,12 +26575,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -26601,13 +26601,13 @@
         </is>
       </c>
       <c r="L220" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M220" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N220" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="O220" t="n">
         <v>0</v>
@@ -26684,7 +26684,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -26694,12 +26694,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -26803,7 +26803,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -26813,12 +26813,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -26932,12 +26932,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -27041,7 +27041,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -27051,12 +27051,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -27077,13 +27077,13 @@
         </is>
       </c>
       <c r="L224" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="M224" t="n">
-        <v>0</v>
+        <v>5.28</v>
       </c>
       <c r="N224" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="O224" t="n">
         <v>0</v>
@@ -27128,10 +27128,10 @@
         <v>0</v>
       </c>
       <c r="AC224" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD224" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE224" t="n">
         <v>0</v>
@@ -27160,7 +27160,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -27170,12 +27170,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -27196,13 +27196,13 @@
         </is>
       </c>
       <c r="L225" t="n">
-        <v>1.42</v>
+        <v>2.22</v>
       </c>
       <c r="M225" t="n">
-        <v>5.28</v>
+        <v>3.44</v>
       </c>
       <c r="N225" t="n">
-        <v>8.1</v>
+        <v>3.66</v>
       </c>
       <c r="O225" t="n">
         <v>0</v>
@@ -27241,16 +27241,16 @@
         <v>0</v>
       </c>
       <c r="AA225" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB225" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC225" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD225" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE225" t="n">
         <v>0</v>
@@ -27279,7 +27279,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -27289,12 +27289,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -27398,7 +27398,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -27408,12 +27408,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -27434,13 +27434,13 @@
         </is>
       </c>
       <c r="L227" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="M227" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="N227" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="O227" t="n">
         <v>0</v>
@@ -27479,10 +27479,10 @@
         <v>0</v>
       </c>
       <c r="AA227" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB227" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AC227" t="n">
         <v>0</v>
@@ -27636,7 +27636,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -27646,12 +27646,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -27672,13 +27672,13 @@
         </is>
       </c>
       <c r="L229" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="M229" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="N229" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O229" t="n">
         <v>0</v>
@@ -27717,10 +27717,10 @@
         <v>0</v>
       </c>
       <c r="AA229" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB229" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC229" t="n">
         <v>0</v>
@@ -27874,22 +27874,22 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -27993,22 +27993,22 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -28112,22 +28112,22 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -28148,13 +28148,13 @@
         </is>
       </c>
       <c r="L233" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="M233" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="N233" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="O233" t="n">
         <v>0</v>
@@ -28231,22 +28231,22 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -28350,7 +28350,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -28360,12 +28360,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -28469,7 +28469,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -28479,12 +28479,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -28505,13 +28505,13 @@
         </is>
       </c>
       <c r="L236" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="M236" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="N236" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O236" t="n">
         <v>0</v>
@@ -28550,10 +28550,10 @@
         <v>0</v>
       </c>
       <c r="AA236" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB236" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC236" t="n">
         <v>0</v>
@@ -28826,7 +28826,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -28836,12 +28836,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -28945,7 +28945,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -28955,12 +28955,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -28981,13 +28981,13 @@
         </is>
       </c>
       <c r="L240" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="M240" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="N240" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="O240" t="n">
         <v>0</v>
@@ -29064,7 +29064,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -29074,12 +29074,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -29100,13 +29100,13 @@
         </is>
       </c>
       <c r="L241" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="M241" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="N241" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="O241" t="n">
         <v>0</v>
@@ -29183,7 +29183,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -29193,12 +29193,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -29219,13 +29219,13 @@
         </is>
       </c>
       <c r="L242" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="M242" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="N242" t="n">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="O242" t="n">
         <v>0</v>
@@ -29302,7 +29302,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -29312,12 +29312,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -29338,13 +29338,13 @@
         </is>
       </c>
       <c r="L243" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="M243" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="N243" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="O243" t="n">
         <v>0</v>
@@ -29421,7 +29421,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -29431,12 +29431,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -29540,22 +29540,22 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -29659,22 +29659,22 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -29695,13 +29695,13 @@
         </is>
       </c>
       <c r="L246" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M246" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N246" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O246" t="n">
         <v>0</v>
@@ -30016,7 +30016,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -30026,12 +30026,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -30135,7 +30135,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -30145,12 +30145,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -30254,7 +30254,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -30264,12 +30264,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -30290,13 +30290,13 @@
         </is>
       </c>
       <c r="L251" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="M251" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="N251" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="O251" t="n">
         <v>0</v>
@@ -30341,10 +30341,10 @@
         <v>0</v>
       </c>
       <c r="AC251" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD251" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AE251" t="n">
         <v>0</v>
@@ -30373,22 +30373,22 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -30409,13 +30409,13 @@
         </is>
       </c>
       <c r="L252" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M252" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N252" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="O252" t="n">
         <v>0</v>
@@ -30454,10 +30454,10 @@
         <v>0</v>
       </c>
       <c r="AA252" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB252" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC252" t="n">
         <v>0</v>
@@ -30492,7 +30492,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -30502,12 +30502,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -30611,22 +30611,22 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -30647,13 +30647,13 @@
         </is>
       </c>
       <c r="L254" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M254" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N254" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="O254" t="n">
         <v>0</v>
@@ -30692,10 +30692,10 @@
         <v>0</v>
       </c>
       <c r="AA254" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB254" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC254" t="n">
         <v>0</v>
@@ -30730,7 +30730,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -30740,12 +30740,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -30766,13 +30766,13 @@
         </is>
       </c>
       <c r="L255" t="n">
-        <v>1.98</v>
+        <v>1.26</v>
       </c>
       <c r="M255" t="n">
-        <v>4.22</v>
+        <v>5.6</v>
       </c>
       <c r="N255" t="n">
-        <v>3.66</v>
+        <v>9.85</v>
       </c>
       <c r="O255" t="n">
         <v>0</v>
@@ -30817,10 +30817,10 @@
         <v>0</v>
       </c>
       <c r="AC255" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD255" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AE255" t="n">
         <v>0</v>
@@ -30859,12 +30859,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -30885,13 +30885,13 @@
         </is>
       </c>
       <c r="L256" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="M256" t="n">
-        <v>3.42</v>
+        <v>3.25</v>
       </c>
       <c r="N256" t="n">
-        <v>3.4</v>
+        <v>3.24</v>
       </c>
       <c r="O256" t="n">
         <v>0</v>
@@ -30930,10 +30930,10 @@
         <v>0</v>
       </c>
       <c r="AA256" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AB256" t="n">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="AC256" t="n">
         <v>0</v>
@@ -30968,22 +30968,22 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -31004,13 +31004,13 @@
         </is>
       </c>
       <c r="L257" t="n">
-        <v>1.29</v>
+        <v>2.3</v>
       </c>
       <c r="M257" t="n">
-        <v>5.1</v>
+        <v>2.88</v>
       </c>
       <c r="N257" t="n">
-        <v>10.5</v>
+        <v>3.4</v>
       </c>
       <c r="O257" t="n">
         <v>0</v>
@@ -31049,10 +31049,10 @@
         <v>0</v>
       </c>
       <c r="AA257" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB257" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC257" t="n">
         <v>0</v>
@@ -31087,7 +31087,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -31097,12 +31097,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -31123,13 +31123,13 @@
         </is>
       </c>
       <c r="L258" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M258" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N258" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="O258" t="n">
         <v>0</v>
@@ -31168,10 +31168,10 @@
         <v>0</v>
       </c>
       <c r="AA258" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB258" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC258" t="n">
         <v>0</v>
@@ -31216,12 +31216,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -31242,13 +31242,13 @@
         </is>
       </c>
       <c r="L259" t="n">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="M259" t="n">
-        <v>3.74</v>
+        <v>3.42</v>
       </c>
       <c r="N259" t="n">
-        <v>4.94</v>
+        <v>3.4</v>
       </c>
       <c r="O259" t="n">
         <v>0</v>
@@ -31287,10 +31287,10 @@
         <v>0</v>
       </c>
       <c r="AA259" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AB259" t="n">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="AC259" t="n">
         <v>0</v>
@@ -31325,7 +31325,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -31335,12 +31335,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -31361,13 +31361,13 @@
         </is>
       </c>
       <c r="L260" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M260" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="N260" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O260" t="n">
         <v>0</v>
@@ -31444,7 +31444,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -31454,12 +31454,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Connecticut United</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -31480,13 +31480,13 @@
         </is>
       </c>
       <c r="L261" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M261" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="N261" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O261" t="n">
         <v>0</v>
@@ -31563,7 +31563,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -31573,12 +31573,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -31599,13 +31599,13 @@
         </is>
       </c>
       <c r="L262" t="n">
-        <v>2.3</v>
+        <v>1.75</v>
       </c>
       <c r="M262" t="n">
-        <v>2.88</v>
+        <v>3.74</v>
       </c>
       <c r="N262" t="n">
-        <v>3.4</v>
+        <v>4.94</v>
       </c>
       <c r="O262" t="n">
         <v>0</v>
@@ -31644,10 +31644,10 @@
         <v>0</v>
       </c>
       <c r="AA262" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB262" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC262" t="n">
         <v>0</v>
@@ -31682,22 +31682,22 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Connecticut United</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -31718,13 +31718,13 @@
         </is>
       </c>
       <c r="L263" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="M263" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="N263" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="O263" t="n">
         <v>0</v>
@@ -31763,10 +31763,10 @@
         <v>0</v>
       </c>
       <c r="AA263" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB263" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC263" t="n">
         <v>0</v>
@@ -31837,13 +31837,13 @@
         </is>
       </c>
       <c r="L264" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="M264" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N264" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="O264" t="n">
         <v>0</v>
@@ -32039,7 +32039,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -32049,12 +32049,12 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="G266" t="n">
@@ -32075,13 +32075,13 @@
         </is>
       </c>
       <c r="L266" t="n">
-        <v>3.79</v>
+        <v>2.67</v>
       </c>
       <c r="M266" t="n">
         <v>3.38</v>
       </c>
       <c r="N266" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="O266" t="n">
         <v>0</v>
@@ -32120,10 +32120,10 @@
         <v>0</v>
       </c>
       <c r="AA266" t="n">
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="AB266" t="n">
-        <v>1.57</v>
+        <v>1.95</v>
       </c>
       <c r="AC266" t="n">
         <v>0</v>
@@ -32158,7 +32158,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -32168,12 +32168,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G267" t="n">
@@ -32194,13 +32194,13 @@
         </is>
       </c>
       <c r="L267" t="n">
-        <v>2.67</v>
+        <v>3.79</v>
       </c>
       <c r="M267" t="n">
         <v>3.38</v>
       </c>
       <c r="N267" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="O267" t="n">
         <v>0</v>
@@ -32239,10 +32239,10 @@
         <v>0</v>
       </c>
       <c r="AA267" t="n">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="AB267" t="n">
-        <v>1.95</v>
+        <v>1.57</v>
       </c>
       <c r="AC267" t="n">
         <v>0</v>
@@ -32277,7 +32277,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -32287,12 +32287,12 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G268" t="n">
@@ -32313,13 +32313,13 @@
         </is>
       </c>
       <c r="L268" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M268" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N268" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O268" t="n">
         <v>0</v>
@@ -32358,10 +32358,10 @@
         <v>0</v>
       </c>
       <c r="AA268" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB268" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC268" t="n">
         <v>0</v>
@@ -32432,13 +32432,13 @@
         </is>
       </c>
       <c r="L269" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M269" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N269" t="n">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="O269" t="n">
         <v>0</v>
@@ -32515,7 +32515,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -32525,12 +32525,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G270" t="n">
@@ -32551,13 +32551,13 @@
         </is>
       </c>
       <c r="L270" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M270" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N270" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="O270" t="n">
         <v>0</v>
@@ -32634,22 +32634,22 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="G271" t="n">
@@ -32753,22 +32753,22 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G272" t="n">
@@ -32789,13 +32789,13 @@
         </is>
       </c>
       <c r="L272" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M272" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N272" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="O272" t="n">
         <v>0</v>
@@ -32908,13 +32908,13 @@
         </is>
       </c>
       <c r="L273" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M273" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N273" t="n">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="O273" t="n">
         <v>0</v>
@@ -32991,22 +32991,22 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G274" t="n">
@@ -33027,13 +33027,13 @@
         </is>
       </c>
       <c r="L274" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="M274" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="N274" t="n">
-        <v>6.39</v>
+        <v>0</v>
       </c>
       <c r="O274" t="n">
         <v>0</v>
@@ -33078,10 +33078,10 @@
         <v>0</v>
       </c>
       <c r="AC274" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD274" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE274" t="n">
         <v>0</v>
@@ -33120,12 +33120,12 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G275" t="n">
@@ -33229,7 +33229,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -33239,12 +33239,12 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G276" t="n">
@@ -33265,13 +33265,13 @@
         </is>
       </c>
       <c r="L276" t="n">
-        <v>2.2</v>
+        <v>1.51</v>
       </c>
       <c r="M276" t="n">
-        <v>3.2</v>
+        <v>4.75</v>
       </c>
       <c r="N276" t="n">
-        <v>3.25</v>
+        <v>6.39</v>
       </c>
       <c r="O276" t="n">
         <v>0</v>
@@ -33316,10 +33316,10 @@
         <v>0</v>
       </c>
       <c r="AC276" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD276" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE276" t="n">
         <v>0</v>
@@ -33384,13 +33384,13 @@
         </is>
       </c>
       <c r="L277" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="M277" t="n">
-        <v>0</v>
+        <v>7.33</v>
       </c>
       <c r="N277" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="O277" t="n">
         <v>0</v>
@@ -33467,22 +33467,22 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G278" t="n">
@@ -33503,13 +33503,13 @@
         </is>
       </c>
       <c r="L278" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M278" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N278" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O278" t="n">
         <v>0</v>
@@ -33596,12 +33596,12 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G279" t="n">
@@ -33715,12 +33715,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G280" t="n">
@@ -34538,7 +34538,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -34548,12 +34548,12 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="G287" t="n">
@@ -34574,13 +34574,13 @@
         </is>
       </c>
       <c r="L287" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="M287" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="N287" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="O287" t="n">
         <v>0</v>
@@ -34619,10 +34619,10 @@
         <v>0</v>
       </c>
       <c r="AA287" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB287" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AC287" t="n">
         <v>0</v>
@@ -34657,7 +34657,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -34667,12 +34667,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G288" t="n">
@@ -34693,13 +34693,13 @@
         </is>
       </c>
       <c r="L288" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M288" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N288" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O288" t="n">
         <v>0</v>
@@ -34738,10 +34738,10 @@
         <v>0</v>
       </c>
       <c r="AA288" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB288" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC288" t="n">
         <v>0</v>
@@ -34786,12 +34786,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G289" t="n">
@@ -34905,12 +34905,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Atlanta United II</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="G290" t="n">
@@ -35014,7 +35014,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -35024,12 +35024,12 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G291" t="n">
@@ -35050,13 +35050,13 @@
         </is>
       </c>
       <c r="L291" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="M291" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="N291" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="O291" t="n">
         <v>0</v>
@@ -35095,10 +35095,10 @@
         <v>0</v>
       </c>
       <c r="AA291" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB291" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AC291" t="n">
         <v>0</v>
@@ -35133,7 +35133,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -35143,12 +35143,12 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Atlanta United II</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="G292" t="n">
@@ -35371,7 +35371,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -35381,12 +35381,12 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G294" t="n">
@@ -35490,7 +35490,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -35500,12 +35500,12 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G295" t="n">
@@ -35526,13 +35526,13 @@
         </is>
       </c>
       <c r="L295" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="M295" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N295" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="O295" t="n">
         <v>0</v>
@@ -35571,10 +35571,10 @@
         <v>0</v>
       </c>
       <c r="AA295" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB295" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC295" t="n">
         <v>0</v>
@@ -35728,7 +35728,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -35738,12 +35738,12 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G297" t="n">
@@ -35764,13 +35764,13 @@
         </is>
       </c>
       <c r="L297" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="M297" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N297" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="O297" t="n">
         <v>0</v>
@@ -35809,10 +35809,10 @@
         <v>0</v>
       </c>
       <c r="AA297" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB297" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC297" t="n">
         <v>0</v>
@@ -35857,12 +35857,12 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="G298" t="n">
@@ -35976,12 +35976,12 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="G299" t="n">

--- a/jogos_2026-03-15.xlsx
+++ b/jogos_2026-03-15.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.77</v>
+        <v>2.05</v>
       </c>
       <c r="M9" t="n">
-        <v>4.07</v>
+        <v>3.22</v>
       </c>
       <c r="N9" t="n">
-        <v>4.22</v>
+        <v>3.72</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>4.07</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1932,22 +1932,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Melbourne Victory FC</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Macarthur</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>4.08</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2051,22 +2051,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Melbourne Victory FC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Macarthur</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3241,22 +3241,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>5.21</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>6.82</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3598,22 +3598,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,22 +4193,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Port FC</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5026,22 +5026,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Port FC</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.99</v>
+        <v>2.09</v>
       </c>
       <c r="M43" t="n">
-        <v>3.62</v>
+        <v>3.42</v>
       </c>
       <c r="N43" t="n">
-        <v>2.48</v>
+        <v>3.02</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5859,22 +5859,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>5.21</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>6.82</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>4.48</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>6.17</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>4.48</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>6.17</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Kanchanaburi</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>4.53</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6692,22 +6692,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6767,10 +6767,10 @@
         <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z53" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA53" t="n">
         <v>0</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>NorthEast United</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Jamshedpur</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>NorthEast United</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Jamshedpur</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7124,10 +7124,10 @@
         <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z56" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA56" t="n">
         <v>0</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Kanchanaburi</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7287,22 +7287,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.48</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="M61" t="n">
-        <v>3.94</v>
+        <v>5.25</v>
       </c>
       <c r="N61" t="n">
-        <v>5.86</v>
+        <v>1.24</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7725,10 +7725,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.57</v>
+        <v>10.9</v>
       </c>
       <c r="M62" t="n">
-        <v>3.84</v>
+        <v>6.3</v>
       </c>
       <c r="N62" t="n">
-        <v>4.96</v>
+        <v>1.18</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7844,10 +7844,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>9.699999999999999</v>
+        <v>1.48</v>
       </c>
       <c r="M63" t="n">
-        <v>5.25</v>
+        <v>3.94</v>
       </c>
       <c r="N63" t="n">
-        <v>1.24</v>
+        <v>5.86</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7963,10 +7963,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB63" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>10.9</v>
+        <v>1.57</v>
       </c>
       <c r="M64" t="n">
-        <v>6.3</v>
+        <v>3.84</v>
       </c>
       <c r="N64" t="n">
-        <v>1.18</v>
+        <v>4.96</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8082,10 +8082,10 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB64" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Ayutthaya United</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>4.97</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ayutthaya United</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>4.97</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>2.17</v>
+        <v>1.4</v>
       </c>
       <c r="M77" t="n">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="N77" t="n">
-        <v>3</v>
+        <v>7.9</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9667,22 +9667,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Balestier Khalsa</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Home United</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9786,22 +9786,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Balestier Khalsa</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Home United</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9905,22 +9905,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10024,22 +10024,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10143,22 +10143,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10224,10 +10224,10 @@
         <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB82" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC82" t="n">
         <v>0</v>
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>1.9</v>
+        <v>2.33</v>
       </c>
       <c r="M83" t="n">
-        <v>3.84</v>
+        <v>3.42</v>
       </c>
       <c r="N83" t="n">
-        <v>3.57</v>
+        <v>2.89</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10343,10 +10343,10 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>1.55</v>
+        <v>1.86</v>
       </c>
       <c r="AB83" t="n">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10417,13 +10417,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>1.4</v>
+        <v>2.06</v>
       </c>
       <c r="M84" t="n">
-        <v>4.3</v>
+        <v>3.56</v>
       </c>
       <c r="N84" t="n">
-        <v>7.9</v>
+        <v>3.32</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -10462,10 +10462,10 @@
         <v>0</v>
       </c>
       <c r="AA84" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB84" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC84" t="n">
         <v>0</v>
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10581,10 +10581,10 @@
         <v>0</v>
       </c>
       <c r="AA85" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB85" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC85" t="n">
         <v>0</v>
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11131,13 +11131,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>4.03</v>
+        <v>0</v>
       </c>
       <c r="N90" t="n">
-        <v>5.01</v>
+        <v>0</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11250,13 +11250,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="M91" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>4.81</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>2.02</v>
+        <v>3.24</v>
       </c>
       <c r="M93" t="n">
-        <v>3.6</v>
+        <v>3.72</v>
       </c>
       <c r="N93" t="n">
-        <v>3.31</v>
+        <v>2.04</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,13 +11607,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M94" t="n">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>5.01</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="N97" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>4.81</v>
+        <v>0</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12166,22 +12166,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="M99" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>1.85</v>
+        <v>1.35</v>
       </c>
       <c r="M100" t="n">
-        <v>2.9</v>
+        <v>5.58</v>
       </c>
       <c r="N100" t="n">
-        <v>4.59</v>
+        <v>8.1</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Johor Darul Ta'zim</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13392,13 +13392,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="M109" t="n">
-        <v>5.58</v>
+        <v>0</v>
       </c>
       <c r="N109" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13630,13 +13630,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="M111" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N111" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13749,13 +13749,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>2.57</v>
+        <v>1.85</v>
       </c>
       <c r="M112" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="N112" t="n">
-        <v>3.1</v>
+        <v>4.59</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -13832,22 +13832,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13868,13 +13868,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="M113" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="N113" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -13951,7 +13951,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Johor Darul Ta'zim</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Inter Kashi</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Mumbai City</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M116" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="N116" t="n">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -14270,10 +14270,10 @@
         <v>0</v>
       </c>
       <c r="AA116" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB116" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC116" t="n">
         <v>0</v>
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14344,13 +14344,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M117" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="N117" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -14389,10 +14389,10 @@
         <v>0</v>
       </c>
       <c r="AA117" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB117" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC117" t="n">
         <v>0</v>
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14463,13 +14463,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="M118" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N118" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14582,13 +14582,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="M119" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="N119" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -14627,10 +14627,10 @@
         <v>0</v>
       </c>
       <c r="AA119" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB119" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC119" t="n">
         <v>0</v>
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14701,13 +14701,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M120" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="N120" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -14746,10 +14746,10 @@
         <v>0</v>
       </c>
       <c r="AA120" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB120" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC120" t="n">
         <v>0</v>
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Inter Kashi</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Mumbai City</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14903,22 +14903,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -15022,22 +15022,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15296,13 +15296,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>2.64</v>
+        <v>2.48</v>
       </c>
       <c r="M125" t="n">
-        <v>3.38</v>
+        <v>3.29</v>
       </c>
       <c r="N125" t="n">
-        <v>2.52</v>
+        <v>3.25</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -15341,10 +15341,10 @@
         <v>0</v>
       </c>
       <c r="AA125" t="n">
-        <v>2.03</v>
+        <v>2.3</v>
       </c>
       <c r="AB125" t="n">
-        <v>1.83</v>
+        <v>1.55</v>
       </c>
       <c r="AC125" t="n">
         <v>0</v>
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15415,13 +15415,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="M126" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="N126" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15534,13 +15534,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M127" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="N127" t="n">
-        <v>0</v>
+        <v>4.77</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -15579,10 +15579,10 @@
         <v>0</v>
       </c>
       <c r="AA127" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB127" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC127" t="n">
         <v>0</v>
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15653,13 +15653,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="M128" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="N128" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -15698,10 +15698,10 @@
         <v>0</v>
       </c>
       <c r="AA128" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB128" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC128" t="n">
         <v>0</v>
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15772,13 +15772,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M129" t="n">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="N129" t="n">
-        <v>4.77</v>
+        <v>0</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -15817,10 +15817,10 @@
         <v>0</v>
       </c>
       <c r="AA129" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB129" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AC129" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M130" t="n">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="N130" t="n">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -15936,10 +15936,10 @@
         <v>0</v>
       </c>
       <c r="AA130" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB130" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC130" t="n">
         <v>0</v>
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16010,13 +16010,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="M131" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="N131" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -16055,10 +16055,10 @@
         <v>0</v>
       </c>
       <c r="AA131" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB131" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC131" t="n">
         <v>0</v>
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16129,13 +16129,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="M132" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N132" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -16174,10 +16174,10 @@
         <v>0</v>
       </c>
       <c r="AA132" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB132" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC132" t="n">
         <v>0</v>
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16248,13 +16248,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="M133" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="N133" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16367,13 +16367,13 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="M134" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N134" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -16412,10 +16412,10 @@
         <v>0</v>
       </c>
       <c r="AA134" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB134" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC134" t="n">
         <v>0</v>
@@ -16450,7 +16450,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16486,13 +16486,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>2.48</v>
+        <v>2.64</v>
       </c>
       <c r="M135" t="n">
-        <v>3.29</v>
+        <v>3.38</v>
       </c>
       <c r="N135" t="n">
-        <v>3.25</v>
+        <v>2.52</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -16531,10 +16531,10 @@
         <v>0</v>
       </c>
       <c r="AA135" t="n">
-        <v>2.3</v>
+        <v>2.03</v>
       </c>
       <c r="AB135" t="n">
-        <v>1.55</v>
+        <v>1.83</v>
       </c>
       <c r="AC135" t="n">
         <v>0</v>
@@ -16569,7 +16569,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16605,13 +16605,13 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="M136" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N136" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O136" t="n">
         <v>0</v>
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16724,13 +16724,13 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M137" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="N137" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="O137" t="n">
         <v>0</v>
@@ -16769,10 +16769,10 @@
         <v>0</v>
       </c>
       <c r="AA137" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB137" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC137" t="n">
         <v>0</v>
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16843,13 +16843,13 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="M138" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N138" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -16888,10 +16888,10 @@
         <v>0</v>
       </c>
       <c r="AA138" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB138" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC138" t="n">
         <v>0</v>
@@ -16926,7 +16926,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -16962,13 +16962,13 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="M139" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N139" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="O139" t="n">
         <v>0</v>
@@ -17007,10 +17007,10 @@
         <v>0</v>
       </c>
       <c r="AA139" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB139" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC139" t="n">
         <v>0</v>
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -17174,12 +17174,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Lajense</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -17283,7 +17283,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17402,7 +17402,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17521,7 +17521,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17640,7 +17640,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17676,13 +17676,13 @@
         </is>
       </c>
       <c r="L145" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="M145" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="N145" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O145" t="n">
         <v>0</v>
@@ -17759,7 +17759,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17878,7 +17878,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -18116,7 +18116,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Gouveia</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18235,7 +18235,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -18245,12 +18245,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Eléctrico</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -18354,22 +18354,22 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -18473,22 +18473,22 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Monção</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -18592,7 +18592,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -18602,12 +18602,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>AR São Martinho</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -18711,7 +18711,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -18721,12 +18721,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Machico</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -18840,12 +18840,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Chaves II</t>
+          <t>Machico</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Mirandela</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -18949,22 +18949,22 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Eléctrico</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -19068,7 +19068,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -19078,12 +19078,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -19104,13 +19104,13 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>1.73</v>
+        <v>1.87</v>
       </c>
       <c r="M157" t="n">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="N157" t="n">
-        <v>3.8</v>
+        <v>4.21</v>
       </c>
       <c r="O157" t="n">
         <v>0</v>
@@ -19187,7 +19187,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -19306,7 +19306,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -19316,12 +19316,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -19342,13 +19342,13 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="M159" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N159" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O159" t="n">
         <v>0</v>
@@ -19425,22 +19425,22 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19544,7 +19544,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -19554,12 +19554,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Chaves II</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>Mirandela</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -19663,7 +19663,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -19673,12 +19673,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Monção</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -19782,7 +19782,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -19792,12 +19792,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -19901,7 +19901,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -19911,12 +19911,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -20020,22 +20020,22 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -20139,7 +20139,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -20149,12 +20149,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -20175,13 +20175,13 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="M166" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N166" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="O166" t="n">
         <v>0</v>
@@ -20258,22 +20258,22 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -20377,22 +20377,22 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -20496,22 +20496,22 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -20615,7 +20615,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -20625,12 +20625,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -20651,13 +20651,13 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="M170" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N170" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="O170" t="n">
         <v>0</v>
@@ -20734,7 +20734,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -20744,12 +20744,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -20770,13 +20770,13 @@
         </is>
       </c>
       <c r="L171" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M171" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N171" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O171" t="n">
         <v>0</v>
@@ -20853,22 +20853,22 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -20889,13 +20889,13 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="M172" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N172" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O172" t="n">
         <v>0</v>
@@ -20972,7 +20972,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -20982,12 +20982,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>AR São Martinho</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -21008,13 +21008,13 @@
         </is>
       </c>
       <c r="L173" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="M173" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N173" t="n">
-        <v>4.21</v>
+        <v>0</v>
       </c>
       <c r="O173" t="n">
         <v>0</v>
@@ -21091,7 +21091,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -21101,12 +21101,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -21127,13 +21127,13 @@
         </is>
       </c>
       <c r="L174" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M174" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N174" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O174" t="n">
         <v>0</v>
@@ -21210,7 +21210,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -21220,12 +21220,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -21329,7 +21329,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -21339,12 +21339,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -21365,13 +21365,13 @@
         </is>
       </c>
       <c r="L176" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="M176" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="N176" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O176" t="n">
         <v>0</v>
@@ -21448,22 +21448,22 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -21567,22 +21567,22 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -21686,7 +21686,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -21696,12 +21696,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -21805,7 +21805,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -21815,12 +21815,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -21841,13 +21841,13 @@
         </is>
       </c>
       <c r="L180" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="M180" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N180" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="O180" t="n">
         <v>0</v>
@@ -21924,22 +21924,22 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -22043,7 +22043,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -22053,12 +22053,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -22400,7 +22400,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -22410,12 +22410,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -22436,13 +22436,13 @@
         </is>
       </c>
       <c r="L185" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="M185" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N185" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="O185" t="n">
         <v>0</v>
@@ -22638,7 +22638,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -22648,12 +22648,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -22670,17 +22670,17 @@
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L187" t="n">
-        <v>0</v>
+        <v>5.04</v>
       </c>
       <c r="M187" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="N187" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O187" t="n">
         <v>0</v>
@@ -22757,7 +22757,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -22767,12 +22767,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -22793,13 +22793,13 @@
         </is>
       </c>
       <c r="L188" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="M188" t="n">
-        <v>5.35</v>
+        <v>0</v>
       </c>
       <c r="N188" t="n">
-        <v>6.57</v>
+        <v>0</v>
       </c>
       <c r="O188" t="n">
         <v>0</v>
@@ -22844,10 +22844,10 @@
         <v>0</v>
       </c>
       <c r="AC188" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AD188" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AE188" t="n">
         <v>0</v>
@@ -22886,12 +22886,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -22912,13 +22912,13 @@
         </is>
       </c>
       <c r="L189" t="n">
-        <v>2.06</v>
+        <v>1.37</v>
       </c>
       <c r="M189" t="n">
-        <v>3.76</v>
+        <v>5.35</v>
       </c>
       <c r="N189" t="n">
-        <v>3.16</v>
+        <v>6.57</v>
       </c>
       <c r="O189" t="n">
         <v>0</v>
@@ -22963,10 +22963,10 @@
         <v>0</v>
       </c>
       <c r="AC189" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD189" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AE189" t="n">
         <v>0</v>
@@ -22995,7 +22995,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -23005,12 +23005,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -23031,13 +23031,13 @@
         </is>
       </c>
       <c r="L190" t="n">
-        <v>2.56</v>
+        <v>2.06</v>
       </c>
       <c r="M190" t="n">
-        <v>3.64</v>
+        <v>3.76</v>
       </c>
       <c r="N190" t="n">
-        <v>2.74</v>
+        <v>3.16</v>
       </c>
       <c r="O190" t="n">
         <v>0</v>
@@ -23114,7 +23114,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -23124,12 +23124,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -23146,17 +23146,17 @@
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L191" t="n">
-        <v>5.04</v>
+        <v>0</v>
       </c>
       <c r="M191" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="N191" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O191" t="n">
         <v>0</v>
@@ -23233,7 +23233,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -23243,12 +23243,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -23269,13 +23269,13 @@
         </is>
       </c>
       <c r="L192" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="M192" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N192" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O192" t="n">
         <v>0</v>
@@ -23314,10 +23314,10 @@
         <v>0</v>
       </c>
       <c r="AA192" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB192" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC192" t="n">
         <v>0</v>
@@ -23352,7 +23352,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -23362,12 +23362,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -23384,7 +23384,7 @@
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L193" t="n">
@@ -23590,7 +23590,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -23600,12 +23600,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -23626,13 +23626,13 @@
         </is>
       </c>
       <c r="L195" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="M195" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N195" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O195" t="n">
         <v>0</v>
@@ -23671,10 +23671,10 @@
         <v>0</v>
       </c>
       <c r="AA195" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB195" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC195" t="n">
         <v>0</v>
@@ -23709,7 +23709,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -23719,12 +23719,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -23741,7 +23741,7 @@
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L196" t="n">
@@ -23947,22 +23947,22 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -23983,13 +23983,13 @@
         </is>
       </c>
       <c r="L198" t="n">
-        <v>1.42</v>
+        <v>1.95</v>
       </c>
       <c r="M198" t="n">
-        <v>4.45</v>
+        <v>3.65</v>
       </c>
       <c r="N198" t="n">
-        <v>7.19</v>
+        <v>3.85</v>
       </c>
       <c r="O198" t="n">
         <v>0</v>
@@ -24066,7 +24066,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -24076,12 +24076,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -24098,7 +24098,7 @@
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L199" t="n">
@@ -24185,22 +24185,22 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -24221,13 +24221,13 @@
         </is>
       </c>
       <c r="L200" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M200" t="n">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="N200" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="O200" t="n">
         <v>0</v>
@@ -24272,10 +24272,10 @@
         <v>0</v>
       </c>
       <c r="AC200" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD200" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE200" t="n">
         <v>0</v>
@@ -24304,22 +24304,22 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -24340,13 +24340,13 @@
         </is>
       </c>
       <c r="L201" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="M201" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="N201" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O201" t="n">
         <v>0</v>
@@ -24423,7 +24423,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -24433,12 +24433,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -24542,7 +24542,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -24552,12 +24552,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -24671,12 +24671,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -24780,7 +24780,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -24790,12 +24790,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -24899,7 +24899,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -24909,12 +24909,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -25018,22 +25018,22 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -25054,13 +25054,13 @@
         </is>
       </c>
       <c r="L207" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M207" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N207" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O207" t="n">
         <v>0</v>
@@ -25137,7 +25137,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -25147,12 +25147,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -25169,7 +25169,7 @@
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L208" t="n">
@@ -25256,7 +25256,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -25266,12 +25266,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -25375,7 +25375,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -25385,12 +25385,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -25411,13 +25411,13 @@
         </is>
       </c>
       <c r="L210" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="M210" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="N210" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O210" t="n">
         <v>0</v>
@@ -25494,22 +25494,22 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -25530,13 +25530,13 @@
         </is>
       </c>
       <c r="L211" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M211" t="n">
-        <v>4.19</v>
+        <v>0</v>
       </c>
       <c r="N211" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="O211" t="n">
         <v>0</v>
@@ -25581,10 +25581,10 @@
         <v>0</v>
       </c>
       <c r="AC211" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD211" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE211" t="n">
         <v>0</v>
@@ -25613,22 +25613,22 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -25649,13 +25649,13 @@
         </is>
       </c>
       <c r="L212" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="M212" t="n">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="N212" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="O212" t="n">
         <v>0</v>
@@ -25732,7 +25732,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -25742,12 +25742,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -25768,13 +25768,13 @@
         </is>
       </c>
       <c r="L213" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="M213" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="N213" t="n">
-        <v>0</v>
+        <v>7.19</v>
       </c>
       <c r="O213" t="n">
         <v>0</v>
@@ -25851,7 +25851,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -25861,12 +25861,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -25970,7 +25970,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -25980,12 +25980,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -26006,13 +26006,13 @@
         </is>
       </c>
       <c r="L215" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="M215" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="N215" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O215" t="n">
         <v>0</v>
@@ -26089,7 +26089,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -26099,12 +26099,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -26218,12 +26218,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -26244,13 +26244,13 @@
         </is>
       </c>
       <c r="L217" t="n">
-        <v>4.57</v>
+        <v>4.11</v>
       </c>
       <c r="M217" t="n">
-        <v>3.78</v>
+        <v>3.49</v>
       </c>
       <c r="N217" t="n">
-        <v>1.88</v>
+        <v>2.06</v>
       </c>
       <c r="O217" t="n">
         <v>0</v>
@@ -26289,10 +26289,10 @@
         <v>0</v>
       </c>
       <c r="AA217" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="AB217" t="n">
-        <v>1.79</v>
+        <v>1.66</v>
       </c>
       <c r="AC217" t="n">
         <v>0</v>
@@ -26337,12 +26337,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -26363,13 +26363,13 @@
         </is>
       </c>
       <c r="L218" t="n">
-        <v>4.11</v>
+        <v>4.57</v>
       </c>
       <c r="M218" t="n">
-        <v>3.49</v>
+        <v>3.78</v>
       </c>
       <c r="N218" t="n">
-        <v>2.06</v>
+        <v>1.88</v>
       </c>
       <c r="O218" t="n">
         <v>0</v>
@@ -26408,10 +26408,10 @@
         <v>0</v>
       </c>
       <c r="AA218" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AB218" t="n">
-        <v>1.66</v>
+        <v>1.79</v>
       </c>
       <c r="AC218" t="n">
         <v>0</v>
@@ -26575,12 +26575,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -26684,7 +26684,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -26694,12 +26694,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -26803,7 +26803,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -26813,12 +26813,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -26922,7 +26922,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -26932,12 +26932,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -26958,13 +26958,13 @@
         </is>
       </c>
       <c r="L223" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M223" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N223" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="O223" t="n">
         <v>0</v>
@@ -27041,7 +27041,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -27051,12 +27051,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -27160,7 +27160,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -27170,12 +27170,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -27196,13 +27196,13 @@
         </is>
       </c>
       <c r="L225" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="M225" t="n">
-        <v>0</v>
+        <v>5.28</v>
       </c>
       <c r="N225" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="O225" t="n">
         <v>0</v>
@@ -27247,10 +27247,10 @@
         <v>0</v>
       </c>
       <c r="AC225" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD225" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE225" t="n">
         <v>0</v>
@@ -27398,7 +27398,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -27408,12 +27408,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -27517,7 +27517,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -27527,12 +27527,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -27553,13 +27553,13 @@
         </is>
       </c>
       <c r="L228" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="M228" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="N228" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="O228" t="n">
         <v>0</v>
@@ -27598,10 +27598,10 @@
         <v>0</v>
       </c>
       <c r="AA228" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB228" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AC228" t="n">
         <v>0</v>
@@ -27636,7 +27636,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -27646,12 +27646,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -27672,13 +27672,13 @@
         </is>
       </c>
       <c r="L229" t="n">
-        <v>1.42</v>
+        <v>2.22</v>
       </c>
       <c r="M229" t="n">
-        <v>5.28</v>
+        <v>3.44</v>
       </c>
       <c r="N229" t="n">
-        <v>8.1</v>
+        <v>3.66</v>
       </c>
       <c r="O229" t="n">
         <v>0</v>
@@ -27717,16 +27717,16 @@
         <v>0</v>
       </c>
       <c r="AA229" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB229" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC229" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD229" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE229" t="n">
         <v>0</v>
@@ -27755,7 +27755,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -27765,12 +27765,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -27791,13 +27791,13 @@
         </is>
       </c>
       <c r="L230" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M230" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N230" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="O230" t="n">
         <v>0</v>
@@ -27993,22 +27993,22 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -28029,13 +28029,13 @@
         </is>
       </c>
       <c r="L232" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="M232" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="N232" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O232" t="n">
         <v>0</v>
@@ -28074,10 +28074,10 @@
         <v>0</v>
       </c>
       <c r="AA232" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB232" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC232" t="n">
         <v>0</v>
@@ -28112,7 +28112,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -28122,12 +28122,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -28148,13 +28148,13 @@
         </is>
       </c>
       <c r="L233" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="M233" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="N233" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="O233" t="n">
         <v>0</v>
@@ -28231,22 +28231,22 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -28350,7 +28350,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -28360,12 +28360,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -28386,13 +28386,13 @@
         </is>
       </c>
       <c r="L235" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="M235" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N235" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="O235" t="n">
         <v>0</v>
@@ -28469,22 +28469,22 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -28505,13 +28505,13 @@
         </is>
       </c>
       <c r="L236" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="M236" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="N236" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="O236" t="n">
         <v>0</v>
@@ -28707,22 +28707,22 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -28826,7 +28826,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -28836,12 +28836,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -28945,7 +28945,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -28955,12 +28955,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -28981,13 +28981,13 @@
         </is>
       </c>
       <c r="L240" t="n">
-        <v>2.33</v>
+        <v>2.22</v>
       </c>
       <c r="M240" t="n">
-        <v>3.42</v>
+        <v>3.3</v>
       </c>
       <c r="N240" t="n">
-        <v>3.4</v>
+        <v>3.03</v>
       </c>
       <c r="O240" t="n">
         <v>0</v>
@@ -29026,10 +29026,10 @@
         <v>0</v>
       </c>
       <c r="AA240" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB240" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC240" t="n">
         <v>0</v>
@@ -29302,7 +29302,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -29312,12 +29312,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -29338,13 +29338,13 @@
         </is>
       </c>
       <c r="L243" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="M243" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="N243" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="O243" t="n">
         <v>0</v>
@@ -29421,7 +29421,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -29431,12 +29431,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -29457,13 +29457,13 @@
         </is>
       </c>
       <c r="L244" t="n">
-        <v>1.99</v>
+        <v>3.41</v>
       </c>
       <c r="M244" t="n">
-        <v>2.97</v>
+        <v>3.61</v>
       </c>
       <c r="N244" t="n">
-        <v>4.06</v>
+        <v>2.03</v>
       </c>
       <c r="O244" t="n">
         <v>0</v>
@@ -29659,7 +29659,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -29669,12 +29669,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -29695,13 +29695,13 @@
         </is>
       </c>
       <c r="L246" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="M246" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="N246" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="O246" t="n">
         <v>0</v>
@@ -29897,22 +29897,22 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -29933,13 +29933,13 @@
         </is>
       </c>
       <c r="L248" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M248" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N248" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O248" t="n">
         <v>0</v>
@@ -30016,7 +30016,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -30026,12 +30026,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -30135,22 +30135,22 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -30171,13 +30171,13 @@
         </is>
       </c>
       <c r="L250" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M250" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N250" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O250" t="n">
         <v>0</v>
@@ -30492,22 +30492,22 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -30528,13 +30528,13 @@
         </is>
       </c>
       <c r="L253" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M253" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N253" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="O253" t="n">
         <v>0</v>
@@ -30573,10 +30573,10 @@
         <v>0</v>
       </c>
       <c r="AA253" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB253" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC253" t="n">
         <v>0</v>
@@ -30730,7 +30730,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -30740,12 +30740,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -30766,13 +30766,13 @@
         </is>
       </c>
       <c r="L255" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="M255" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="N255" t="n">
-        <v>9.85</v>
+        <v>0</v>
       </c>
       <c r="O255" t="n">
         <v>0</v>
@@ -30849,7 +30849,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -30859,12 +30859,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -30885,13 +30885,13 @@
         </is>
       </c>
       <c r="L256" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="M256" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="N256" t="n">
-        <v>0</v>
+        <v>9.85</v>
       </c>
       <c r="O256" t="n">
         <v>0</v>
@@ -31087,7 +31087,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -31097,12 +31097,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -31206,22 +31206,22 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -31242,13 +31242,13 @@
         </is>
       </c>
       <c r="L259" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M259" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N259" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="O259" t="n">
         <v>0</v>
@@ -31287,10 +31287,10 @@
         <v>0</v>
       </c>
       <c r="AA259" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB259" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC259" t="n">
         <v>0</v>
@@ -31325,22 +31325,22 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -31361,13 +31361,13 @@
         </is>
       </c>
       <c r="L260" t="n">
-        <v>1.29</v>
+        <v>2.35</v>
       </c>
       <c r="M260" t="n">
-        <v>5.1</v>
+        <v>3.25</v>
       </c>
       <c r="N260" t="n">
-        <v>10.5</v>
+        <v>3.24</v>
       </c>
       <c r="O260" t="n">
         <v>0</v>
@@ -31406,10 +31406,10 @@
         <v>0</v>
       </c>
       <c r="AA260" t="n">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="AB260" t="n">
-        <v>1.98</v>
+        <v>1.63</v>
       </c>
       <c r="AC260" t="n">
         <v>0</v>
@@ -31444,7 +31444,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -31454,12 +31454,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -31480,13 +31480,13 @@
         </is>
       </c>
       <c r="L261" t="n">
-        <v>1.75</v>
+        <v>2.3</v>
       </c>
       <c r="M261" t="n">
-        <v>3.74</v>
+        <v>2.88</v>
       </c>
       <c r="N261" t="n">
-        <v>4.94</v>
+        <v>3.4</v>
       </c>
       <c r="O261" t="n">
         <v>0</v>
@@ -31525,10 +31525,10 @@
         <v>0</v>
       </c>
       <c r="AA261" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB261" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC261" t="n">
         <v>0</v>
@@ -31563,7 +31563,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -31573,12 +31573,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -31599,13 +31599,13 @@
         </is>
       </c>
       <c r="L262" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M262" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="N262" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O262" t="n">
         <v>0</v>
@@ -31682,7 +31682,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -31692,12 +31692,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -31718,13 +31718,13 @@
         </is>
       </c>
       <c r="L263" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M263" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="N263" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O263" t="n">
         <v>0</v>
@@ -31763,10 +31763,10 @@
         <v>0</v>
       </c>
       <c r="AA263" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB263" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC263" t="n">
         <v>0</v>
@@ -31801,7 +31801,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -31811,12 +31811,12 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Connecticut United</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G264" t="n">
@@ -31837,13 +31837,13 @@
         </is>
       </c>
       <c r="L264" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M264" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="N264" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O264" t="n">
         <v>0</v>
@@ -31882,10 +31882,10 @@
         <v>0</v>
       </c>
       <c r="AA264" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB264" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC264" t="n">
         <v>0</v>
@@ -31920,22 +31920,22 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="G265" t="n">
@@ -31956,13 +31956,13 @@
         </is>
       </c>
       <c r="L265" t="n">
-        <v>2.35</v>
+        <v>1.29</v>
       </c>
       <c r="M265" t="n">
-        <v>3.25</v>
+        <v>5.1</v>
       </c>
       <c r="N265" t="n">
-        <v>3.24</v>
+        <v>10.5</v>
       </c>
       <c r="O265" t="n">
         <v>0</v>
@@ -32001,10 +32001,10 @@
         <v>0</v>
       </c>
       <c r="AA265" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AB265" t="n">
-        <v>1.63</v>
+        <v>1.98</v>
       </c>
       <c r="AC265" t="n">
         <v>0</v>
@@ -32039,7 +32039,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -32049,12 +32049,12 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Connecticut United</t>
         </is>
       </c>
       <c r="G266" t="n">
@@ -32075,13 +32075,13 @@
         </is>
       </c>
       <c r="L266" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M266" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="N266" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O266" t="n">
         <v>0</v>
@@ -32158,7 +32158,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -32168,12 +32168,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G267" t="n">
@@ -32194,13 +32194,13 @@
         </is>
       </c>
       <c r="L267" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="M267" t="n">
-        <v>2.88</v>
+        <v>3.74</v>
       </c>
       <c r="N267" t="n">
-        <v>4.2</v>
+        <v>4.94</v>
       </c>
       <c r="O267" t="n">
         <v>0</v>
@@ -32239,10 +32239,10 @@
         <v>0</v>
       </c>
       <c r="AA267" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB267" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC267" t="n">
         <v>0</v>
@@ -32515,7 +32515,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -32525,12 +32525,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="G270" t="n">
@@ -32551,13 +32551,13 @@
         </is>
       </c>
       <c r="L270" t="n">
-        <v>3.79</v>
+        <v>2.67</v>
       </c>
       <c r="M270" t="n">
         <v>3.38</v>
       </c>
       <c r="N270" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="O270" t="n">
         <v>0</v>
@@ -32596,10 +32596,10 @@
         <v>0</v>
       </c>
       <c r="AA270" t="n">
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="AB270" t="n">
-        <v>1.57</v>
+        <v>1.95</v>
       </c>
       <c r="AC270" t="n">
         <v>0</v>
@@ -32634,7 +32634,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -32644,12 +32644,12 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G271" t="n">
@@ -32670,13 +32670,13 @@
         </is>
       </c>
       <c r="L271" t="n">
-        <v>2.67</v>
+        <v>3.79</v>
       </c>
       <c r="M271" t="n">
         <v>3.38</v>
       </c>
       <c r="N271" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="O271" t="n">
         <v>0</v>
@@ -32715,10 +32715,10 @@
         <v>0</v>
       </c>
       <c r="AA271" t="n">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="AB271" t="n">
-        <v>1.95</v>
+        <v>1.57</v>
       </c>
       <c r="AC271" t="n">
         <v>0</v>
@@ -32753,22 +32753,22 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G272" t="n">
@@ -32789,13 +32789,13 @@
         </is>
       </c>
       <c r="L272" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="M272" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="N272" t="n">
-        <v>2.5</v>
+        <v>5.75</v>
       </c>
       <c r="O272" t="n">
         <v>0</v>
@@ -32834,10 +32834,10 @@
         <v>0</v>
       </c>
       <c r="AA272" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB272" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC272" t="n">
         <v>0</v>
@@ -32872,22 +32872,22 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G273" t="n">
@@ -32991,7 +32991,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -33001,12 +33001,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="G274" t="n">
@@ -33027,13 +33027,13 @@
         </is>
       </c>
       <c r="L274" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M274" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N274" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="O274" t="n">
         <v>0</v>
@@ -33110,22 +33110,22 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G275" t="n">
@@ -33146,13 +33146,13 @@
         </is>
       </c>
       <c r="L275" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M275" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N275" t="n">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="O275" t="n">
         <v>0</v>
@@ -33229,22 +33229,22 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G276" t="n">
@@ -33265,13 +33265,13 @@
         </is>
       </c>
       <c r="L276" t="n">
-        <v>1.72</v>
+        <v>2.5</v>
       </c>
       <c r="M276" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="N276" t="n">
-        <v>4.53</v>
+        <v>2.5</v>
       </c>
       <c r="O276" t="n">
         <v>0</v>
@@ -33310,10 +33310,10 @@
         <v>0</v>
       </c>
       <c r="AA276" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB276" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC276" t="n">
         <v>0</v>
@@ -33586,22 +33586,22 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G279" t="n">
@@ -33622,13 +33622,13 @@
         </is>
       </c>
       <c r="L279" t="n">
-        <v>1.19</v>
+        <v>2.2</v>
       </c>
       <c r="M279" t="n">
-        <v>7.33</v>
+        <v>3.2</v>
       </c>
       <c r="N279" t="n">
-        <v>18.5</v>
+        <v>3.25</v>
       </c>
       <c r="O279" t="n">
         <v>0</v>
@@ -33705,22 +33705,22 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G280" t="n">
@@ -33741,13 +33741,13 @@
         </is>
       </c>
       <c r="L280" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="M280" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="N280" t="n">
-        <v>6.39</v>
+        <v>0</v>
       </c>
       <c r="O280" t="n">
         <v>0</v>
@@ -33792,10 +33792,10 @@
         <v>0</v>
       </c>
       <c r="AC280" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD280" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE280" t="n">
         <v>0</v>
@@ -33834,12 +33834,12 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G281" t="n">
@@ -33953,12 +33953,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G282" t="n">
@@ -34062,22 +34062,22 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G283" t="n">
@@ -34098,13 +34098,13 @@
         </is>
       </c>
       <c r="L283" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="M283" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="N283" t="n">
-        <v>0</v>
+        <v>6.39</v>
       </c>
       <c r="O283" t="n">
         <v>0</v>
@@ -34149,10 +34149,10 @@
         <v>0</v>
       </c>
       <c r="AC283" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD283" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE283" t="n">
         <v>0</v>
@@ -34181,22 +34181,22 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="G284" t="n">
@@ -34217,13 +34217,13 @@
         </is>
       </c>
       <c r="L284" t="n">
-        <v>2.2</v>
+        <v>1.19</v>
       </c>
       <c r="M284" t="n">
-        <v>3.2</v>
+        <v>7.33</v>
       </c>
       <c r="N284" t="n">
-        <v>3.25</v>
+        <v>18.5</v>
       </c>
       <c r="O284" t="n">
         <v>0</v>
@@ -34300,7 +34300,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -34310,12 +34310,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G285" t="n">
@@ -34336,13 +34336,13 @@
         </is>
       </c>
       <c r="L285" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M285" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="N285" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O285" t="n">
         <v>0</v>
@@ -34419,7 +34419,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -34429,12 +34429,12 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G286" t="n">
@@ -34455,13 +34455,13 @@
         </is>
       </c>
       <c r="L286" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M286" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="N286" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O286" t="n">
         <v>0</v>
@@ -34538,7 +34538,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -34548,12 +34548,12 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="G287" t="n">
@@ -34657,7 +34657,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -34667,12 +34667,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Real Monarchs</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Los Angeles II</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G288" t="n">
@@ -34693,13 +34693,13 @@
         </is>
       </c>
       <c r="L288" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="M288" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="N288" t="n">
-        <v>0</v>
+        <v>6.69</v>
       </c>
       <c r="O288" t="n">
         <v>0</v>
@@ -34738,10 +34738,10 @@
         <v>0</v>
       </c>
       <c r="AA288" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB288" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC288" t="n">
         <v>0</v>
@@ -34776,7 +34776,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -34786,12 +34786,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Real Monarchs</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Los Angeles II</t>
         </is>
       </c>
       <c r="G289" t="n">
@@ -34812,13 +34812,13 @@
         </is>
       </c>
       <c r="L289" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="M289" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="N289" t="n">
-        <v>6.69</v>
+        <v>0</v>
       </c>
       <c r="O289" t="n">
         <v>0</v>
@@ -34857,10 +34857,10 @@
         <v>0</v>
       </c>
       <c r="AA289" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB289" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC289" t="n">
         <v>0</v>
@@ -35024,12 +35024,12 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>Atlanta United II</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="G291" t="n">
@@ -35133,7 +35133,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -35143,12 +35143,12 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G292" t="n">
@@ -35169,13 +35169,13 @@
         </is>
       </c>
       <c r="L292" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="M292" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="N292" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="O292" t="n">
         <v>0</v>
@@ -35214,10 +35214,10 @@
         <v>0</v>
       </c>
       <c r="AA292" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB292" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AC292" t="n">
         <v>0</v>
@@ -35262,12 +35262,12 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Atlanta United II</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="G293" t="n">
@@ -35381,12 +35381,12 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="G294" t="n">
@@ -35490,7 +35490,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -35500,12 +35500,12 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G295" t="n">
@@ -35526,13 +35526,13 @@
         </is>
       </c>
       <c r="L295" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="M295" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="N295" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="O295" t="n">
         <v>0</v>
@@ -35571,10 +35571,10 @@
         <v>0</v>
       </c>
       <c r="AA295" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB295" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AC295" t="n">
         <v>0</v>
@@ -35857,12 +35857,12 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G298" t="n">
@@ -35883,13 +35883,13 @@
         </is>
       </c>
       <c r="L298" t="n">
-        <v>1.7</v>
+        <v>2.61</v>
       </c>
       <c r="M298" t="n">
-        <v>3.79</v>
+        <v>3.23</v>
       </c>
       <c r="N298" t="n">
-        <v>5.3</v>
+        <v>2.86</v>
       </c>
       <c r="O298" t="n">
         <v>0</v>
@@ -35928,10 +35928,10 @@
         <v>0</v>
       </c>
       <c r="AA298" t="n">
-        <v>1.93</v>
+        <v>2.3</v>
       </c>
       <c r="AB298" t="n">
-        <v>1.75</v>
+        <v>1.55</v>
       </c>
       <c r="AC298" t="n">
         <v>0</v>
@@ -35966,7 +35966,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -35976,12 +35976,12 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G299" t="n">
@@ -36002,13 +36002,13 @@
         </is>
       </c>
       <c r="L299" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M299" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="N299" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="O299" t="n">
         <v>0</v>
@@ -36047,10 +36047,10 @@
         <v>0</v>
       </c>
       <c r="AA299" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB299" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC299" t="n">
         <v>0</v>
@@ -36085,7 +36085,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -36095,12 +36095,12 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G300" t="n">
@@ -36204,7 +36204,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -36214,12 +36214,12 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G301" t="n">
@@ -36240,13 +36240,13 @@
         </is>
       </c>
       <c r="L301" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="M301" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N301" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="O301" t="n">
         <v>0</v>
@@ -36285,10 +36285,10 @@
         <v>0</v>
       </c>
       <c r="AA301" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB301" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC301" t="n">
         <v>0</v>

--- a/jogos_2026-03-15.xlsx
+++ b/jogos_2026-03-15.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2.05</v>
+        <v>1.77</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.22</v>
+        <v>4.07</v>
       </c>
       <c r="R9" t="n">
-        <v>3.72</v>
+        <v>4.22</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.07</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>5.21</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>6.82</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>5.21</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>6.82</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>2.99</v>
+        <v>2.09</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.62</v>
+        <v>3.25</v>
       </c>
       <c r="R40" t="n">
-        <v>2.48</v>
+        <v>3.19</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Port FC</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1.9</v>
+        <v>2.09</v>
       </c>
       <c r="Q41" t="n">
         <v>3.42</v>
       </c>
       <c r="R41" t="n">
-        <v>3.92</v>
+        <v>3.02</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8726,10 +8726,10 @@
         <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Port FC</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>4.48</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>6.17</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>4.48</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>6.17</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Kanchanaburi</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>4.53</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>NorthEast United</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Jamshedpur</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11084,10 +11084,10 @@
         <v>0</v>
       </c>
       <c r="AC54" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD54" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE54" t="n">
         <v>0</v>
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11281,10 +11281,10 @@
         <v>0</v>
       </c>
       <c r="AC55" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD55" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AE55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,22 +11588,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Kanchanaburi</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>NorthEast United</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Jamshedpur</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>9.699999999999999</v>
+        <v>1.48</v>
       </c>
       <c r="Q61" t="n">
-        <v>5.25</v>
+        <v>3.94</v>
       </c>
       <c r="R61" t="n">
-        <v>1.24</v>
+        <v>5.86</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12469,10 +12469,10 @@
         <v>0</v>
       </c>
       <c r="AE61" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF61" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG61" t="n">
         <v>0</v>
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>1.57</v>
+        <v>10.9</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.84</v>
+        <v>6.3</v>
       </c>
       <c r="R62" t="n">
-        <v>4.96</v>
+        <v>1.18</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12666,10 +12666,10 @@
         <v>0</v>
       </c>
       <c r="AE62" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AF62" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG62" t="n">
         <v>0</v>
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>10.9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="Q63" t="n">
-        <v>6.3</v>
+        <v>5.25</v>
       </c>
       <c r="R63" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.94</v>
+        <v>3.84</v>
       </c>
       <c r="R64" t="n">
-        <v>5.86</v>
+        <v>4.96</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13060,10 +13060,10 @@
         <v>0</v>
       </c>
       <c r="AE64" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AF64" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AG64" t="n">
         <v>0</v>
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23456,13 +23456,13 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>2.19</v>
+        <v>3.06</v>
       </c>
       <c r="Q117" t="n">
-        <v>3.58</v>
+        <v>3.25</v>
       </c>
       <c r="R117" t="n">
-        <v>3.58</v>
+        <v>2.28</v>
       </c>
       <c r="S117" t="n">
         <v>0</v>
@@ -23501,10 +23501,10 @@
         <v>0</v>
       </c>
       <c r="AE117" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AF117" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG117" t="n">
         <v>0</v>
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23653,13 +23653,13 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>3.06</v>
+        <v>2.19</v>
       </c>
       <c r="Q118" t="n">
-        <v>3.25</v>
+        <v>3.58</v>
       </c>
       <c r="R118" t="n">
-        <v>2.28</v>
+        <v>3.58</v>
       </c>
       <c r="S118" t="n">
         <v>0</v>
@@ -23698,10 +23698,10 @@
         <v>0</v>
       </c>
       <c r="AE118" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AF118" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG118" t="n">
         <v>0</v>
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26166,7 +26166,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26214,13 +26214,13 @@
         </is>
       </c>
       <c r="P131" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="Q131" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R131" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="S131" t="n">
         <v>0</v>
@@ -26259,10 +26259,10 @@
         <v>0</v>
       </c>
       <c r="AE131" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF131" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG131" t="n">
         <v>0</v>
@@ -26363,7 +26363,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26411,13 +26411,13 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>2.96</v>
+        <v>2.64</v>
       </c>
       <c r="Q132" t="n">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="R132" t="n">
-        <v>2.61</v>
+        <v>2.52</v>
       </c>
       <c r="S132" t="n">
         <v>0</v>
@@ -26456,10 +26456,10 @@
         <v>0</v>
       </c>
       <c r="AE132" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AF132" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AG132" t="n">
         <v>0</v>
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26954,7 +26954,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27002,13 +27002,13 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="Q135" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R135" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="S135" t="n">
         <v>0</v>
@@ -27047,10 +27047,10 @@
         <v>0</v>
       </c>
       <c r="AE135" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AF135" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG135" t="n">
         <v>0</v>
@@ -27151,7 +27151,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27348,7 +27348,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -29131,12 +29131,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29712,7 +29712,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29760,13 +29760,13 @@
         </is>
       </c>
       <c r="P149" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Q149" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R149" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="S149" t="n">
         <v>0</v>
@@ -30510,12 +30510,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -31288,7 +31288,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -31298,12 +31298,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -31336,13 +31336,13 @@
         </is>
       </c>
       <c r="P157" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Q157" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R157" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="S157" t="n">
         <v>0</v>
@@ -34637,7 +34637,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -34647,12 +34647,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -34685,13 +34685,13 @@
         </is>
       </c>
       <c r="P174" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q174" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R174" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="S174" t="n">
         <v>0</v>
@@ -34834,7 +34834,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -34844,12 +34844,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -34882,13 +34882,13 @@
         </is>
       </c>
       <c r="P175" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q175" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R175" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S175" t="n">
         <v>0</v>
@@ -35031,7 +35031,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -35041,12 +35041,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -35079,13 +35079,13 @@
         </is>
       </c>
       <c r="P176" t="n">
-        <v>2.26</v>
+        <v>3.32</v>
       </c>
       <c r="Q176" t="n">
-        <v>3.16</v>
+        <v>3.4</v>
       </c>
       <c r="R176" t="n">
-        <v>3.3</v>
+        <v>2.09</v>
       </c>
       <c r="S176" t="n">
         <v>0</v>
@@ -35228,22 +35228,22 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -35622,7 +35622,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -35632,12 +35632,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -35819,7 +35819,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -35829,12 +35829,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -35867,13 +35867,13 @@
         </is>
       </c>
       <c r="P180" t="n">
-        <v>3.32</v>
+        <v>2.11</v>
       </c>
       <c r="Q180" t="n">
-        <v>3.4</v>
+        <v>3.44</v>
       </c>
       <c r="R180" t="n">
-        <v>2.09</v>
+        <v>2.99</v>
       </c>
       <c r="S180" t="n">
         <v>0</v>
@@ -36016,22 +36016,22 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -36064,13 +36064,13 @@
         </is>
       </c>
       <c r="P181" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q181" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="R181" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S181" t="n">
         <v>0</v>
@@ -36213,7 +36213,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -36223,12 +36223,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -36261,13 +36261,13 @@
         </is>
       </c>
       <c r="P182" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Q182" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R182" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="S182" t="n">
         <v>0</v>
@@ -36804,7 +36804,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -36814,12 +36814,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -36852,13 +36852,13 @@
         </is>
       </c>
       <c r="P185" t="n">
-        <v>2.07</v>
+        <v>5.04</v>
       </c>
       <c r="Q185" t="n">
-        <v>3.24</v>
+        <v>3.62</v>
       </c>
       <c r="R185" t="n">
-        <v>3.62</v>
+        <v>1.8</v>
       </c>
       <c r="S185" t="n">
         <v>0</v>
@@ -37198,7 +37198,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -37208,12 +37208,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -37246,13 +37246,13 @@
         </is>
       </c>
       <c r="P187" t="n">
-        <v>5.04</v>
+        <v>2.07</v>
       </c>
       <c r="Q187" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="R187" t="n">
         <v>3.62</v>
-      </c>
-      <c r="R187" t="n">
-        <v>1.8</v>
       </c>
       <c r="S187" t="n">
         <v>0</v>
@@ -37395,7 +37395,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -37405,12 +37405,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -37443,13 +37443,13 @@
         </is>
       </c>
       <c r="P188" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q188" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="R188" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="S188" t="n">
         <v>0</v>
@@ -37592,7 +37592,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -37602,12 +37602,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -37640,13 +37640,13 @@
         </is>
       </c>
       <c r="P189" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Q189" t="n">
-        <v>5.35</v>
+        <v>0</v>
       </c>
       <c r="R189" t="n">
-        <v>6.57</v>
+        <v>0</v>
       </c>
       <c r="S189" t="n">
         <v>0</v>
@@ -37691,10 +37691,10 @@
         <v>0</v>
       </c>
       <c r="AG189" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AH189" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AI189" t="n">
         <v>0</v>
@@ -37799,12 +37799,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -37837,13 +37837,13 @@
         </is>
       </c>
       <c r="P190" t="n">
-        <v>2.06</v>
+        <v>1.37</v>
       </c>
       <c r="Q190" t="n">
-        <v>3.76</v>
+        <v>5.35</v>
       </c>
       <c r="R190" t="n">
-        <v>3.16</v>
+        <v>6.57</v>
       </c>
       <c r="S190" t="n">
         <v>0</v>
@@ -37888,10 +37888,10 @@
         <v>0</v>
       </c>
       <c r="AG190" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AH190" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AI190" t="n">
         <v>0</v>
@@ -38183,7 +38183,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -38193,12 +38193,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -38231,13 +38231,13 @@
         </is>
       </c>
       <c r="P192" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Q192" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R192" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="S192" t="n">
         <v>0</v>
@@ -38276,10 +38276,10 @@
         <v>0</v>
       </c>
       <c r="AE192" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF192" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG192" t="n">
         <v>0</v>
@@ -38587,12 +38587,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -38774,7 +38774,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -38784,12 +38784,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -38818,7 +38818,7 @@
       </c>
       <c r="O195" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P195" t="n">
@@ -38971,7 +38971,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -38981,12 +38981,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -39015,17 +39015,17 @@
       </c>
       <c r="O196" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P196" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q196" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R196" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S196" t="n">
         <v>0</v>
@@ -39064,10 +39064,10 @@
         <v>0</v>
       </c>
       <c r="AE196" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF196" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG196" t="n">
         <v>0</v>
@@ -39168,7 +39168,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -39178,12 +39178,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -39212,7 +39212,7 @@
       </c>
       <c r="O197" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P197" t="n">
@@ -39365,22 +39365,22 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -39413,13 +39413,13 @@
         </is>
       </c>
       <c r="P198" t="n">
-        <v>1.95</v>
+        <v>3.16</v>
       </c>
       <c r="Q198" t="n">
-        <v>3.65</v>
+        <v>3.44</v>
       </c>
       <c r="R198" t="n">
-        <v>3.85</v>
+        <v>2.45</v>
       </c>
       <c r="S198" t="n">
         <v>0</v>
@@ -39562,7 +39562,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -39572,12 +39572,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -39759,22 +39759,22 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -39807,13 +39807,13 @@
         </is>
       </c>
       <c r="P200" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="Q200" t="n">
-        <v>4.19</v>
+        <v>0</v>
       </c>
       <c r="R200" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="S200" t="n">
         <v>0</v>
@@ -39858,10 +39858,10 @@
         <v>0</v>
       </c>
       <c r="AG200" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH200" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AI200" t="n">
         <v>0</v>
@@ -39966,12 +39966,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -40004,13 +40004,13 @@
         </is>
       </c>
       <c r="P201" t="n">
-        <v>3.35</v>
+        <v>1.95</v>
       </c>
       <c r="Q201" t="n">
-        <v>4.14</v>
+        <v>3.65</v>
       </c>
       <c r="R201" t="n">
-        <v>1.97</v>
+        <v>3.85</v>
       </c>
       <c r="S201" t="n">
         <v>0</v>
@@ -40153,7 +40153,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -40163,12 +40163,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -40350,22 +40350,22 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -40398,13 +40398,13 @@
         </is>
       </c>
       <c r="P203" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Q203" t="n">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="R203" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="S203" t="n">
         <v>0</v>
@@ -40449,10 +40449,10 @@
         <v>0</v>
       </c>
       <c r="AG203" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH203" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AI203" t="n">
         <v>0</v>
@@ -40547,22 +40547,22 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -40595,13 +40595,13 @@
         </is>
       </c>
       <c r="P204" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="Q204" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="R204" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S204" t="n">
         <v>0</v>
@@ -40744,7 +40744,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -40754,12 +40754,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -40941,7 +40941,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -40951,12 +40951,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -41138,7 +41138,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -41148,12 +41148,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -41335,7 +41335,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -41345,12 +41345,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -41379,7 +41379,7 @@
       </c>
       <c r="O208" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P208" t="n">
@@ -41532,7 +41532,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -41542,12 +41542,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -41729,7 +41729,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -41739,12 +41739,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -41926,7 +41926,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -41936,12 +41936,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -42123,7 +42123,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -42133,12 +42133,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -42320,7 +42320,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -42330,12 +42330,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -42368,13 +42368,13 @@
         </is>
       </c>
       <c r="P213" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Q213" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="R213" t="n">
-        <v>7.19</v>
+        <v>0</v>
       </c>
       <c r="S213" t="n">
         <v>0</v>
@@ -42527,12 +42527,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -42714,7 +42714,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -42724,12 +42724,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -42762,13 +42762,13 @@
         </is>
       </c>
       <c r="P215" t="n">
-        <v>3.16</v>
+        <v>1.42</v>
       </c>
       <c r="Q215" t="n">
-        <v>3.44</v>
+        <v>4.45</v>
       </c>
       <c r="R215" t="n">
-        <v>2.45</v>
+        <v>7.19</v>
       </c>
       <c r="S215" t="n">
         <v>0</v>
@@ -42911,7 +42911,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -42921,12 +42921,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -43118,12 +43118,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -43156,13 +43156,13 @@
         </is>
       </c>
       <c r="P217" t="n">
-        <v>4.11</v>
+        <v>4.57</v>
       </c>
       <c r="Q217" t="n">
-        <v>3.49</v>
+        <v>3.78</v>
       </c>
       <c r="R217" t="n">
-        <v>2.06</v>
+        <v>1.88</v>
       </c>
       <c r="S217" t="n">
         <v>0</v>
@@ -43201,10 +43201,10 @@
         <v>0</v>
       </c>
       <c r="AE217" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AF217" t="n">
-        <v>1.66</v>
+        <v>1.79</v>
       </c>
       <c r="AG217" t="n">
         <v>0</v>
@@ -43315,12 +43315,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -43353,13 +43353,13 @@
         </is>
       </c>
       <c r="P218" t="n">
-        <v>4.57</v>
+        <v>4.11</v>
       </c>
       <c r="Q218" t="n">
-        <v>3.78</v>
+        <v>3.49</v>
       </c>
       <c r="R218" t="n">
-        <v>1.88</v>
+        <v>2.06</v>
       </c>
       <c r="S218" t="n">
         <v>0</v>
@@ -43398,10 +43398,10 @@
         <v>0</v>
       </c>
       <c r="AE218" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="AF218" t="n">
-        <v>1.79</v>
+        <v>1.66</v>
       </c>
       <c r="AG218" t="n">
         <v>0</v>
@@ -43709,12 +43709,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -43896,7 +43896,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -43906,12 +43906,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -44103,12 +44103,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -44290,7 +44290,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -44300,12 +44300,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -44338,13 +44338,13 @@
         </is>
       </c>
       <c r="P223" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q223" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R223" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="S223" t="n">
         <v>0</v>
@@ -44383,10 +44383,10 @@
         <v>0</v>
       </c>
       <c r="AE223" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF223" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG223" t="n">
         <v>0</v>
@@ -44487,7 +44487,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -44497,12 +44497,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -44684,7 +44684,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -44694,12 +44694,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -44732,13 +44732,13 @@
         </is>
       </c>
       <c r="P225" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Q225" t="n">
-        <v>5.28</v>
+        <v>0</v>
       </c>
       <c r="R225" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="S225" t="n">
         <v>0</v>
@@ -44783,10 +44783,10 @@
         <v>0</v>
       </c>
       <c r="AG225" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AH225" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AI225" t="n">
         <v>0</v>
@@ -44881,7 +44881,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -44891,12 +44891,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -44929,13 +44929,13 @@
         </is>
       </c>
       <c r="P226" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Q226" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R226" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="S226" t="n">
         <v>0</v>
@@ -45078,7 +45078,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -45088,12 +45088,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -45126,13 +45126,13 @@
         </is>
       </c>
       <c r="P227" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q227" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R227" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="S227" t="n">
         <v>0</v>
@@ -45275,7 +45275,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -45285,12 +45285,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -45323,13 +45323,13 @@
         </is>
       </c>
       <c r="P228" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Q228" t="n">
-        <v>0</v>
+        <v>5.28</v>
       </c>
       <c r="R228" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="S228" t="n">
         <v>0</v>
@@ -45374,10 +45374,10 @@
         <v>0</v>
       </c>
       <c r="AG228" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH228" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AI228" t="n">
         <v>0</v>
@@ -45472,7 +45472,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -45482,12 +45482,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -45520,13 +45520,13 @@
         </is>
       </c>
       <c r="P229" t="n">
-        <v>2.22</v>
+        <v>2.63</v>
       </c>
       <c r="Q229" t="n">
-        <v>3.44</v>
+        <v>3.45</v>
       </c>
       <c r="R229" t="n">
-        <v>3.66</v>
+        <v>2.32</v>
       </c>
       <c r="S229" t="n">
         <v>0</v>
@@ -45565,10 +45565,10 @@
         <v>0</v>
       </c>
       <c r="AE229" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF229" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AG229" t="n">
         <v>0</v>
@@ -45669,7 +45669,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -45679,12 +45679,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -45717,13 +45717,13 @@
         </is>
       </c>
       <c r="P230" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q230" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R230" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="S230" t="n">
         <v>0</v>
@@ -46063,7 +46063,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -46073,12 +46073,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -46111,13 +46111,13 @@
         </is>
       </c>
       <c r="P232" t="n">
-        <v>2.33</v>
+        <v>2.24</v>
       </c>
       <c r="Q232" t="n">
-        <v>3.42</v>
+        <v>3.32</v>
       </c>
       <c r="R232" t="n">
-        <v>3.4</v>
+        <v>3.08</v>
       </c>
       <c r="S232" t="n">
         <v>0</v>
@@ -46156,10 +46156,10 @@
         <v>0</v>
       </c>
       <c r="AE232" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AF232" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG232" t="n">
         <v>0</v>
@@ -46260,7 +46260,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -46270,12 +46270,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -46308,13 +46308,13 @@
         </is>
       </c>
       <c r="P233" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q233" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R233" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="S233" t="n">
         <v>0</v>
@@ -46457,7 +46457,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -46467,12 +46467,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -46654,22 +46654,22 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -46851,22 +46851,22 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -46899,13 +46899,13 @@
         </is>
       </c>
       <c r="P236" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Q236" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="R236" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="S236" t="n">
         <v>0</v>
@@ -47048,7 +47048,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -47058,12 +47058,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -47245,7 +47245,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -47255,12 +47255,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -47293,13 +47293,13 @@
         </is>
       </c>
       <c r="P238" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q238" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R238" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="S238" t="n">
         <v>0</v>
@@ -47338,10 +47338,10 @@
         <v>0</v>
       </c>
       <c r="AE238" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF238" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG238" t="n">
         <v>0</v>
@@ -47442,7 +47442,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -47452,12 +47452,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -47490,13 +47490,13 @@
         </is>
       </c>
       <c r="P239" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q239" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R239" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="S239" t="n">
         <v>0</v>
@@ -47639,7 +47639,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -47649,12 +47649,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -48033,7 +48033,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -48043,12 +48043,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -48230,7 +48230,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -48240,12 +48240,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -48278,13 +48278,13 @@
         </is>
       </c>
       <c r="P243" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="Q243" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="R243" t="n">
-        <v>4.08</v>
+        <v>0</v>
       </c>
       <c r="S243" t="n">
         <v>0</v>
@@ -48427,7 +48427,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -48437,12 +48437,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -48475,13 +48475,13 @@
         </is>
       </c>
       <c r="P244" t="n">
-        <v>3.41</v>
+        <v>1.99</v>
       </c>
       <c r="Q244" t="n">
-        <v>3.61</v>
+        <v>2.97</v>
       </c>
       <c r="R244" t="n">
-        <v>2.03</v>
+        <v>4.06</v>
       </c>
       <c r="S244" t="n">
         <v>0</v>
@@ -48624,7 +48624,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -48634,12 +48634,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -48672,13 +48672,13 @@
         </is>
       </c>
       <c r="P245" t="n">
-        <v>1.99</v>
+        <v>3.41</v>
       </c>
       <c r="Q245" t="n">
-        <v>2.97</v>
+        <v>3.61</v>
       </c>
       <c r="R245" t="n">
-        <v>4.06</v>
+        <v>2.03</v>
       </c>
       <c r="S245" t="n">
         <v>0</v>
@@ -48821,7 +48821,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -48831,12 +48831,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -48869,13 +48869,13 @@
         </is>
       </c>
       <c r="P246" t="n">
-        <v>6.71</v>
+        <v>1.89</v>
       </c>
       <c r="Q246" t="n">
-        <v>4.05</v>
+        <v>3.22</v>
       </c>
       <c r="R246" t="n">
-        <v>1.49</v>
+        <v>4.08</v>
       </c>
       <c r="S246" t="n">
         <v>0</v>
@@ -49018,7 +49018,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -49028,12 +49028,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -49066,13 +49066,13 @@
         </is>
       </c>
       <c r="P247" t="n">
-        <v>0</v>
+        <v>6.71</v>
       </c>
       <c r="Q247" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R247" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="S247" t="n">
         <v>0</v>
@@ -49215,22 +49215,22 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -49263,13 +49263,13 @@
         </is>
       </c>
       <c r="P248" t="n">
-        <v>2.2</v>
+        <v>2.44</v>
       </c>
       <c r="Q248" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="R248" t="n">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="S248" t="n">
         <v>0</v>
@@ -49412,22 +49412,22 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -49460,13 +49460,13 @@
         </is>
       </c>
       <c r="P249" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q249" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R249" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="S249" t="n">
         <v>0</v>
@@ -49609,7 +49609,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -49619,12 +49619,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -49657,13 +49657,13 @@
         </is>
       </c>
       <c r="P250" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="Q250" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R250" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="S250" t="n">
         <v>0</v>
@@ -50200,7 +50200,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -50210,12 +50210,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -50397,22 +50397,22 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -50445,13 +50445,13 @@
         </is>
       </c>
       <c r="P254" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q254" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R254" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="S254" t="n">
         <v>0</v>
@@ -50490,10 +50490,10 @@
         <v>0</v>
       </c>
       <c r="AE254" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF254" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG254" t="n">
         <v>0</v>
@@ -50594,7 +50594,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -50604,12 +50604,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -50642,13 +50642,13 @@
         </is>
       </c>
       <c r="P255" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Q255" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="R255" t="n">
-        <v>9.85</v>
+        <v>0</v>
       </c>
       <c r="S255" t="n">
         <v>0</v>
@@ -50791,7 +50791,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -50801,12 +50801,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -50839,13 +50839,13 @@
         </is>
       </c>
       <c r="P256" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q256" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="R256" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="S256" t="n">
         <v>0</v>
@@ -50890,10 +50890,10 @@
         <v>0</v>
       </c>
       <c r="AG256" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH256" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AI256" t="n">
         <v>0</v>
@@ -50988,7 +50988,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -50998,12 +50998,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -51036,13 +51036,13 @@
         </is>
       </c>
       <c r="P257" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Q257" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="R257" t="n">
-        <v>0</v>
+        <v>9.85</v>
       </c>
       <c r="S257" t="n">
         <v>0</v>
@@ -51185,22 +51185,22 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -51233,13 +51233,13 @@
         </is>
       </c>
       <c r="P258" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q258" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R258" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="S258" t="n">
         <v>0</v>
@@ -51278,10 +51278,10 @@
         <v>0</v>
       </c>
       <c r="AE258" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF258" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG258" t="n">
         <v>0</v>
@@ -51382,7 +51382,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -51392,12 +51392,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -51430,13 +51430,13 @@
         </is>
       </c>
       <c r="P259" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Q259" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="R259" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="S259" t="n">
         <v>0</v>
@@ -51481,10 +51481,10 @@
         <v>0</v>
       </c>
       <c r="AG259" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH259" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AI259" t="n">
         <v>0</v>
@@ -51579,7 +51579,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -51589,12 +51589,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -51627,13 +51627,13 @@
         </is>
       </c>
       <c r="P260" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q260" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="R260" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="S260" t="n">
         <v>0</v>
@@ -51776,7 +51776,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -51786,12 +51786,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -51824,13 +51824,13 @@
         </is>
       </c>
       <c r="P261" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q261" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R261" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="S261" t="n">
         <v>0</v>
@@ -52170,7 +52170,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -52180,12 +52180,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Connecticut United</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -52218,13 +52218,13 @@
         </is>
       </c>
       <c r="P263" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q263" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="R263" t="n">
-        <v>4.94</v>
+        <v>0</v>
       </c>
       <c r="S263" t="n">
         <v>0</v>
@@ -52263,10 +52263,10 @@
         <v>0</v>
       </c>
       <c r="AE263" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF263" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG263" t="n">
         <v>0</v>
@@ -52377,12 +52377,12 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G264" t="n">
@@ -52415,13 +52415,13 @@
         </is>
       </c>
       <c r="P264" t="n">
-        <v>2.2</v>
+        <v>1.75</v>
       </c>
       <c r="Q264" t="n">
-        <v>3.42</v>
+        <v>3.74</v>
       </c>
       <c r="R264" t="n">
-        <v>3.4</v>
+        <v>4.94</v>
       </c>
       <c r="S264" t="n">
         <v>0</v>
@@ -52460,10 +52460,10 @@
         <v>0</v>
       </c>
       <c r="AE264" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AF264" t="n">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="AG264" t="n">
         <v>0</v>
@@ -52564,22 +52564,22 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G265" t="n">
@@ -52612,13 +52612,13 @@
         </is>
       </c>
       <c r="P265" t="n">
-        <v>1.29</v>
+        <v>2.2</v>
       </c>
       <c r="Q265" t="n">
-        <v>5.1</v>
+        <v>3.42</v>
       </c>
       <c r="R265" t="n">
-        <v>10.5</v>
+        <v>3.4</v>
       </c>
       <c r="S265" t="n">
         <v>0</v>
@@ -52657,10 +52657,10 @@
         <v>0</v>
       </c>
       <c r="AE265" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AF265" t="n">
-        <v>1.98</v>
+        <v>1.68</v>
       </c>
       <c r="AG265" t="n">
         <v>0</v>
@@ -52761,22 +52761,22 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Connecticut United</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="G266" t="n">
@@ -52809,13 +52809,13 @@
         </is>
       </c>
       <c r="P266" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Q266" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="R266" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="S266" t="n">
         <v>0</v>
@@ -52854,10 +52854,10 @@
         <v>0</v>
       </c>
       <c r="AE266" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF266" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG266" t="n">
         <v>0</v>
@@ -53549,7 +53549,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -53559,12 +53559,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="G270" t="n">
@@ -53597,13 +53597,13 @@
         </is>
       </c>
       <c r="P270" t="n">
-        <v>3.79</v>
+        <v>2.67</v>
       </c>
       <c r="Q270" t="n">
         <v>3.38</v>
       </c>
       <c r="R270" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="S270" t="n">
         <v>0</v>
@@ -53642,10 +53642,10 @@
         <v>0</v>
       </c>
       <c r="AE270" t="n">
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="AF270" t="n">
-        <v>1.57</v>
+        <v>1.95</v>
       </c>
       <c r="AG270" t="n">
         <v>0</v>
@@ -53746,7 +53746,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -53756,12 +53756,12 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G271" t="n">
@@ -53794,13 +53794,13 @@
         </is>
       </c>
       <c r="P271" t="n">
-        <v>2.67</v>
+        <v>3.79</v>
       </c>
       <c r="Q271" t="n">
         <v>3.38</v>
       </c>
       <c r="R271" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="S271" t="n">
         <v>0</v>
@@ -53839,10 +53839,10 @@
         <v>0</v>
       </c>
       <c r="AE271" t="n">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="AF271" t="n">
-        <v>1.95</v>
+        <v>1.57</v>
       </c>
       <c r="AG271" t="n">
         <v>0</v>
@@ -53943,7 +53943,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -53953,12 +53953,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G272" t="n">
@@ -53991,13 +53991,13 @@
         </is>
       </c>
       <c r="P272" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="Q272" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="R272" t="n">
-        <v>4.53</v>
+        <v>5.75</v>
       </c>
       <c r="S272" t="n">
         <v>0</v>
@@ -54140,22 +54140,22 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G273" t="n">
@@ -54188,13 +54188,13 @@
         </is>
       </c>
       <c r="P273" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Q273" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R273" t="n">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="S273" t="n">
         <v>0</v>
@@ -54534,22 +54534,22 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G275" t="n">
@@ -54582,13 +54582,13 @@
         </is>
       </c>
       <c r="P275" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="Q275" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="R275" t="n">
-        <v>5.75</v>
+        <v>2.5</v>
       </c>
       <c r="S275" t="n">
         <v>0</v>
@@ -54627,10 +54627,10 @@
         <v>0</v>
       </c>
       <c r="AE275" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF275" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG275" t="n">
         <v>0</v>
@@ -54731,7 +54731,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -54741,12 +54741,12 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G276" t="n">
@@ -54779,13 +54779,13 @@
         </is>
       </c>
       <c r="P276" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q276" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R276" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S276" t="n">
         <v>0</v>
@@ -54824,10 +54824,10 @@
         <v>0</v>
       </c>
       <c r="AE276" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF276" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG276" t="n">
         <v>0</v>
@@ -55125,22 +55125,22 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G278" t="n">
@@ -55173,13 +55173,13 @@
         </is>
       </c>
       <c r="P278" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="Q278" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="R278" t="n">
-        <v>6.39</v>
+        <v>0</v>
       </c>
       <c r="S278" t="n">
         <v>0</v>
@@ -55224,10 +55224,10 @@
         <v>0</v>
       </c>
       <c r="AG278" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AH278" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI278" t="n">
         <v>0</v>
@@ -55322,7 +55322,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -55332,12 +55332,12 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G279" t="n">
@@ -55370,13 +55370,13 @@
         </is>
       </c>
       <c r="P279" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Q279" t="n">
-        <v>7.33</v>
+        <v>0</v>
       </c>
       <c r="R279" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="S279" t="n">
         <v>0</v>
@@ -55529,12 +55529,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G280" t="n">
@@ -55716,22 +55716,22 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G281" t="n">
@@ -55764,13 +55764,13 @@
         </is>
       </c>
       <c r="P281" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q281" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R281" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="S281" t="n">
         <v>0</v>
@@ -55913,7 +55913,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -55923,12 +55923,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G282" t="n">
@@ -55961,13 +55961,13 @@
         </is>
       </c>
       <c r="P282" t="n">
-        <v>2.2</v>
+        <v>1.51</v>
       </c>
       <c r="Q282" t="n">
-        <v>3.2</v>
+        <v>4.75</v>
       </c>
       <c r="R282" t="n">
-        <v>3.25</v>
+        <v>6.39</v>
       </c>
       <c r="S282" t="n">
         <v>0</v>
@@ -56012,10 +56012,10 @@
         <v>0</v>
       </c>
       <c r="AG282" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH282" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI282" t="n">
         <v>0</v>
@@ -56110,7 +56110,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -56120,12 +56120,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="G283" t="n">
@@ -56158,13 +56158,13 @@
         </is>
       </c>
       <c r="P283" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Q283" t="n">
-        <v>0</v>
+        <v>7.33</v>
       </c>
       <c r="R283" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="S283" t="n">
         <v>0</v>
@@ -56317,12 +56317,12 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G284" t="n">
@@ -56701,7 +56701,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -56711,12 +56711,12 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G286" t="n">
@@ -56898,7 +56898,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -56908,12 +56908,12 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="G287" t="n">
@@ -58090,12 +58090,12 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="G293" t="n">
@@ -58287,12 +58287,12 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Atlanta United II</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="G294" t="n">
@@ -58484,12 +58484,12 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Atlanta United II</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="G295" t="n">
@@ -58681,12 +58681,12 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G296" t="n">
@@ -59065,7 +59065,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -59075,12 +59075,12 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G298" t="n">
@@ -59272,12 +59272,12 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G299" t="n">
@@ -59310,13 +59310,13 @@
         </is>
       </c>
       <c r="P299" t="n">
-        <v>1.7</v>
+        <v>2.61</v>
       </c>
       <c r="Q299" t="n">
-        <v>3.79</v>
+        <v>3.23</v>
       </c>
       <c r="R299" t="n">
-        <v>5.3</v>
+        <v>2.86</v>
       </c>
       <c r="S299" t="n">
         <v>0</v>
@@ -59355,10 +59355,10 @@
         <v>0</v>
       </c>
       <c r="AE299" t="n">
-        <v>1.93</v>
+        <v>2.3</v>
       </c>
       <c r="AF299" t="n">
-        <v>1.75</v>
+        <v>1.55</v>
       </c>
       <c r="AG299" t="n">
         <v>0</v>
@@ -59469,12 +59469,12 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G300" t="n">
@@ -59507,13 +59507,13 @@
         </is>
       </c>
       <c r="P300" t="n">
-        <v>2.61</v>
+        <v>1.7</v>
       </c>
       <c r="Q300" t="n">
-        <v>3.23</v>
+        <v>3.79</v>
       </c>
       <c r="R300" t="n">
-        <v>2.86</v>
+        <v>5.3</v>
       </c>
       <c r="S300" t="n">
         <v>0</v>
@@ -59552,10 +59552,10 @@
         <v>0</v>
       </c>
       <c r="AE300" t="n">
-        <v>2.3</v>
+        <v>1.93</v>
       </c>
       <c r="AF300" t="n">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="AG300" t="n">
         <v>0</v>
@@ -59656,7 +59656,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -59666,12 +59666,12 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G301" t="n">

--- a/jogos_2026-03-15.xlsx
+++ b/jogos_2026-03-15.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Marconi Stallions</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Marconi Stallions</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="R11" t="n">
-        <v>3.37</v>
+        <v>3.72</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>5.21</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>6.82</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Port FC</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Port FC</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -8923,10 +8923,10 @@
         <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG43" t="n">
         <v>0</v>
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>5.21</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>6.82</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>4.48</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>6.17</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>4.48</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>6.17</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10887,10 +10887,10 @@
         <v>0</v>
       </c>
       <c r="AC53" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD53" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE53" t="n">
         <v>0</v>
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11084,10 +11084,10 @@
         <v>0</v>
       </c>
       <c r="AC54" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD54" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AE54" t="n">
         <v>0</v>
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Kanchanaburi</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Kanchanaburi</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>4.53</v>
+        <v>0</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ayutthaya United</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="R65" t="n">
-        <v>4.97</v>
+        <v>0</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Ayutthaya United</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R66" t="n">
-        <v>0</v>
+        <v>4.97</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="R67" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="R68" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="R69" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>2.12</v>
+        <v>4.56</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.09</v>
+        <v>3.64</v>
       </c>
       <c r="R70" t="n">
-        <v>3.6</v>
+        <v>1.75</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R71" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="R77" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>2.17</v>
+        <v>1.4</v>
       </c>
       <c r="Q78" t="n">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="R78" t="n">
-        <v>3</v>
+        <v>7.9</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15922,22 +15922,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Balestier Khalsa</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Home United</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q79" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R79" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16119,22 +16119,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Balestier Khalsa</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Home United</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16513,22 +16513,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="Q82" t="n">
-        <v>3.48</v>
+        <v>3.75</v>
       </c>
       <c r="R82" t="n">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>2.33</v>
+        <v>1.9</v>
       </c>
       <c r="Q83" t="n">
-        <v>3.42</v>
+        <v>3.84</v>
       </c>
       <c r="R83" t="n">
-        <v>2.89</v>
+        <v>3.57</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16803,10 +16803,10 @@
         <v>0</v>
       </c>
       <c r="AE83" t="n">
-        <v>1.86</v>
+        <v>1.55</v>
       </c>
       <c r="AF83" t="n">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="AG83" t="n">
         <v>0</v>
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>1.9</v>
+        <v>2.33</v>
       </c>
       <c r="Q85" t="n">
-        <v>3.84</v>
+        <v>3.42</v>
       </c>
       <c r="R85" t="n">
-        <v>3.57</v>
+        <v>2.89</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17197,10 +17197,10 @@
         <v>0</v>
       </c>
       <c r="AE85" t="n">
-        <v>1.55</v>
+        <v>1.86</v>
       </c>
       <c r="AF85" t="n">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="AG85" t="n">
         <v>0</v>
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Q86" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R86" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Q87" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="R87" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q88" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R88" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="Q89" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="R89" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Q90" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R90" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Q91" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="R91" t="n">
-        <v>4.81</v>
+        <v>0</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Q92" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R92" t="n">
-        <v>0</v>
+        <v>4.81</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="Q93" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="R93" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Q94" t="n">
-        <v>4.03</v>
+        <v>0</v>
       </c>
       <c r="R94" t="n">
-        <v>5.01</v>
+        <v>0</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q95" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R95" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Q96" t="n">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="R96" t="n">
-        <v>0</v>
+        <v>5.01</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Q97" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="R97" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19862,22 +19862,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19910,13 +19910,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>4.3</v>
+        <v>3.41</v>
       </c>
       <c r="Q99" t="n">
-        <v>3.94</v>
+        <v>3.64</v>
       </c>
       <c r="R99" t="n">
-        <v>1.78</v>
+        <v>1.88</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,13 +20107,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Q100" t="n">
-        <v>5.58</v>
+        <v>0</v>
       </c>
       <c r="R100" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Q101" t="n">
-        <v>0</v>
+        <v>5.97</v>
       </c>
       <c r="R101" t="n">
-        <v>0</v>
+        <v>10.3</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Q102" t="n">
-        <v>0</v>
+        <v>5.58</v>
       </c>
       <c r="R102" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20698,13 +20698,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>3.41</v>
+        <v>1.85</v>
       </c>
       <c r="Q103" t="n">
-        <v>3.64</v>
+        <v>2.9</v>
       </c>
       <c r="R103" t="n">
-        <v>1.88</v>
+        <v>4.59</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="Q106" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R106" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Johor Darul Ta'zim</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21683,13 +21683,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Q108" t="n">
-        <v>5.97</v>
+        <v>0</v>
       </c>
       <c r="R108" t="n">
-        <v>10.3</v>
+        <v>0</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="Q111" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R111" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22471,13 +22471,13 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q112" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R112" t="n">
-        <v>4.59</v>
+        <v>0</v>
       </c>
       <c r="S112" t="n">
         <v>0</v>
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,22 +22817,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Johor Darul Ta'zim</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -22865,13 +22865,13 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="Q114" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="R114" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="S114" t="n">
         <v>0</v>
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23259,13 +23259,13 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q116" t="n">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="R116" t="n">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="S116" t="n">
         <v>0</v>
@@ -23304,10 +23304,10 @@
         <v>0</v>
       </c>
       <c r="AE116" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF116" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG116" t="n">
         <v>0</v>
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23456,13 +23456,13 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="Q117" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R117" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="S117" t="n">
         <v>0</v>
@@ -23605,22 +23605,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23653,13 +23653,13 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Q118" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="R118" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="S118" t="n">
         <v>0</v>
@@ -23698,10 +23698,10 @@
         <v>0</v>
       </c>
       <c r="AE118" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AF118" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG118" t="n">
         <v>0</v>
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23850,13 +23850,13 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>2.29</v>
+        <v>2.96</v>
       </c>
       <c r="Q119" t="n">
-        <v>3.62</v>
+        <v>3.4</v>
       </c>
       <c r="R119" t="n">
-        <v>3.31</v>
+        <v>2.61</v>
       </c>
       <c r="S119" t="n">
         <v>0</v>
@@ -23895,10 +23895,10 @@
         <v>0</v>
       </c>
       <c r="AE119" t="n">
-        <v>1.79</v>
+        <v>2</v>
       </c>
       <c r="AF119" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AG119" t="n">
         <v>0</v>
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Inter Kashi</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Mumbai City</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24393,22 +24393,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24638,13 +24638,13 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q123" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="R123" t="n">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="S123" t="n">
         <v>0</v>
@@ -24683,10 +24683,10 @@
         <v>0</v>
       </c>
       <c r="AE123" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF123" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG123" t="n">
         <v>0</v>
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Inter Kashi</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Mumbai City</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24984,7 +24984,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25032,13 +25032,13 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Q125" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="R125" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="S125" t="n">
         <v>0</v>
@@ -25077,10 +25077,10 @@
         <v>0</v>
       </c>
       <c r="AE125" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AF125" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AG125" t="n">
         <v>0</v>
@@ -25181,7 +25181,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25229,13 +25229,13 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>3.51</v>
+        <v>3.06</v>
       </c>
       <c r="Q126" t="n">
-        <v>3.38</v>
+        <v>3.25</v>
       </c>
       <c r="R126" t="n">
-        <v>2.03</v>
+        <v>2.28</v>
       </c>
       <c r="S126" t="n">
         <v>0</v>
@@ -25378,7 +25378,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25426,13 +25426,13 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Q127" t="n">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="R127" t="n">
-        <v>4.77</v>
+        <v>0</v>
       </c>
       <c r="S127" t="n">
         <v>0</v>
@@ -25471,10 +25471,10 @@
         <v>0</v>
       </c>
       <c r="AE127" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF127" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG127" t="n">
         <v>0</v>
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25623,13 +25623,13 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q128" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="R128" t="n">
-        <v>0</v>
+        <v>4.77</v>
       </c>
       <c r="S128" t="n">
         <v>0</v>
@@ -25668,10 +25668,10 @@
         <v>0</v>
       </c>
       <c r="AE128" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF128" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG128" t="n">
         <v>0</v>
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25820,13 +25820,13 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Q129" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="R129" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="S129" t="n">
         <v>0</v>
@@ -25865,10 +25865,10 @@
         <v>0</v>
       </c>
       <c r="AE129" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AF129" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG129" t="n">
         <v>0</v>
@@ -25969,7 +25969,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26166,7 +26166,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26214,13 +26214,13 @@
         </is>
       </c>
       <c r="P131" t="n">
-        <v>2.96</v>
+        <v>2.64</v>
       </c>
       <c r="Q131" t="n">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="R131" t="n">
-        <v>2.61</v>
+        <v>2.52</v>
       </c>
       <c r="S131" t="n">
         <v>0</v>
@@ -26259,10 +26259,10 @@
         <v>0</v>
       </c>
       <c r="AE131" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AF131" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AG131" t="n">
         <v>0</v>
@@ -26363,7 +26363,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26411,13 +26411,13 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>2.64</v>
+        <v>3.51</v>
       </c>
       <c r="Q132" t="n">
         <v>3.38</v>
       </c>
       <c r="R132" t="n">
-        <v>2.52</v>
+        <v>2.03</v>
       </c>
       <c r="S132" t="n">
         <v>0</v>
@@ -26456,10 +26456,10 @@
         <v>0</v>
       </c>
       <c r="AE132" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AF132" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG132" t="n">
         <v>0</v>
@@ -26560,7 +26560,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26757,7 +26757,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26805,13 +26805,13 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="Q134" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="R134" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="S134" t="n">
         <v>0</v>
@@ -26850,10 +26850,10 @@
         <v>0</v>
       </c>
       <c r="AE134" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF134" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG134" t="n">
         <v>0</v>
@@ -26954,7 +26954,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27002,13 +27002,13 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q135" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R135" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="S135" t="n">
         <v>0</v>
@@ -27047,10 +27047,10 @@
         <v>0</v>
       </c>
       <c r="AE135" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AF135" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG135" t="n">
         <v>0</v>
@@ -27151,7 +27151,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -28136,22 +28136,22 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28333,7 +28333,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28381,13 +28381,13 @@
         </is>
       </c>
       <c r="P142" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q142" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R142" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="S142" t="n">
         <v>0</v>
@@ -28530,7 +28530,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28727,22 +28727,22 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28924,7 +28924,7 @@
       </c>
       <